--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
@@ -1237,7 +1237,7 @@
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>**年報 様式2から29のサービス区分について令和3〜7年度の件数・単位数・費用額・給付費を取り出し、サービス別の単価と見込量を試算した。**正規化後の合計は様式2の総計と全年度・介護／予防別に一致しており、取りこぼしも二重計上もない。推計の分母は第1号被保険者数とした。給付件数総計を各分母で割ったときの変動係数が**第1号被保険者数1.63％に対し認定者数5.18％**であり、認定者数は令和7年9月の計上変更で断層があるためである。**認定者ベースで組むと総給付費が3年計で312,871千円（10.2％）低く出る。**</t>
+          <t>**年報 様式2から29のサービス区分について令和3〜7年度の件数・単位数・費用額・給付費を取り出し、サービス別の単価と見込量を試算した。**正規化後の合計は様式2の総計と全年度・介護／予防別に一致しており、取りこぼしも二重計上もない。推計の分母は第1号被保険者数とした。給付件数総計を各分母で割ったときの変動係数が**第1号被保険者数1.63％に対し認定者数5.18％**であり、認定者数は令和7年9月の計上変更で断層があるためである。**令和7年9月審査分の断層は認定者数にだけ現れ、受給者数は連続している（認定者▲11.4％に対し受給者計▲3.9％、利用率＋8.4％）。**見える化の3段連鎖（第1号×認定率×利用率）に組み替えると、断層後にそろえた場合の差は3年計で▲1.0％（月額59円）にとどまる。</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="N38" s="16" t="inlineStr">
         <is>
-          <t>**サービス別単価・見込量試算（04_算定・見込量・10シート）を作成し、算定シートの05・06に投入済み。**年報 様式2から29区分の令和3〜7年度の件数・単位数・費用額・給付費を取り出し（正規化後の合計は様式2の総計と全年度一致）、第1号被保険者1人当たりの利用率で令和9〜11年度を試算した。総給付費は3年計3,048,418千円、標準給付費は3,286,398千円（第9期見込の92.1％）。**分母の変動係数は第1号被保険者数1.63％に対し認定者数5.18％で、認定者ベースだと3年計で312,871千円（10.2％）低く出ることを定量化した。****9月15日に、量と利用者数の水準を見える化ワークシートの令和7年度実績（給付実績情報の回数・受給者数）に切り替えた。**国保連月報の実日数を回数に読み替えていたため、訪問介護で26％、訪問看護で32％、回数を少なく見ていた。給付費は年報 様式2 のまま（施設サービスは月報・見える化の額に特定入所者介護サービス費が乗っているため採らない）。**サービス見込量（11シート）と算定結果（成果品②の素材）にまとめた**</t>
+          <t>**サービス別単価・見込量試算（04_算定・見込量・10シート）を作成し、算定シートの05・06に投入済み。**年報 様式2から29区分の令和3〜7年度の件数・単位数・費用額・給付費を取り出し（正規化後の合計は様式2の総計と全年度一致）、第1号被保険者1人当たりの利用率で令和9〜11年度を試算した。総給付費は3年計3,048,418千円、標準給付費は3,286,398千円（第9期見込の92.1％）。**分母の変動係数は第1号被保険者数1.63％に対し認定者数5.18％で、認定者ベースだと基準期間が断層をまたぐため10.5％低く出る。****9月15日に、量と利用者数の水準を見える化ワークシートの令和7年度実績（給付実績情報の回数・受給者数）に切り替えた。**国保連月報の実日数を回数に読み替えていたため、訪問介護で26％、訪問看護で32％、回数を少なく見ていた。給付費は年報 様式2 のまま（施設サービスは月報・見える化の額に特定入所者介護サービス費が乗っているため採らない）。**サービス見込量（11シート）と算定結果（成果品②の素材）にまとめた**</t>
         </is>
       </c>
       <c r="O38" s="16" t="inlineStr">

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
@@ -3366,7 +3366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P64"/>
+  <dimension ref="A1:Q64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3536,6 +3536,7 @@
         </is>
       </c>
       <c r="P2" s="21" t="n"/>
+      <c r="Q2" s="21" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
@@ -3610,6 +3611,7 @@
         </is>
       </c>
       <c r="P3" s="21" t="n"/>
+      <c r="Q3" s="21" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
@@ -3684,6 +3686,7 @@
         </is>
       </c>
       <c r="P4" s="21" t="n"/>
+      <c r="Q4" s="21" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -3758,6 +3761,7 @@
         </is>
       </c>
       <c r="P5" s="21" t="n"/>
+      <c r="Q5" s="21" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -3832,6 +3836,7 @@
         </is>
       </c>
       <c r="P6" s="21" t="n"/>
+      <c r="Q6" s="21" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -3906,6 +3911,7 @@
         </is>
       </c>
       <c r="P7" s="21" t="n"/>
+      <c r="Q7" s="21" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
@@ -3980,6 +3986,7 @@
         </is>
       </c>
       <c r="P8" s="21" t="n"/>
+      <c r="Q8" s="21" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
@@ -4054,6 +4061,7 @@
         </is>
       </c>
       <c r="P9" s="21" t="n"/>
+      <c r="Q9" s="21" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
@@ -4128,6 +4136,7 @@
         </is>
       </c>
       <c r="P10" s="21" t="n"/>
+      <c r="Q10" s="21" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
@@ -4202,6 +4211,7 @@
         </is>
       </c>
       <c r="P11" s="21" t="n"/>
+      <c r="Q11" s="21" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
@@ -4276,6 +4286,7 @@
         </is>
       </c>
       <c r="P12" s="21" t="n"/>
+      <c r="Q12" s="21" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
@@ -4350,6 +4361,7 @@
         </is>
       </c>
       <c r="P13" s="21" t="n"/>
+      <c r="Q13" s="21" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
@@ -4424,6 +4436,7 @@
         </is>
       </c>
       <c r="P14" s="21" t="n"/>
+      <c r="Q14" s="21" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
@@ -4498,6 +4511,7 @@
         </is>
       </c>
       <c r="P15" s="21" t="n"/>
+      <c r="Q15" s="21" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
@@ -4573,6 +4587,7 @@
         </is>
       </c>
       <c r="P16" s="21" t="n"/>
+      <c r="Q16" s="21" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
@@ -4647,6 +4662,7 @@
         </is>
       </c>
       <c r="P17" s="21" t="n"/>
+      <c r="Q17" s="21" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
@@ -4721,6 +4737,7 @@
         </is>
       </c>
       <c r="P18" s="21" t="n"/>
+      <c r="Q18" s="21" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
@@ -4795,6 +4812,7 @@
         </is>
       </c>
       <c r="P19" s="21" t="n"/>
+      <c r="Q19" s="21" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
@@ -4870,6 +4888,7 @@
         </is>
       </c>
       <c r="P20" s="21" t="n"/>
+      <c r="Q20" s="21" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
@@ -4944,6 +4963,7 @@
         </is>
       </c>
       <c r="P21" s="21" t="n"/>
+      <c r="Q21" s="21" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
@@ -5018,6 +5038,7 @@
         </is>
       </c>
       <c r="P22" s="21" t="n"/>
+      <c r="Q22" s="21" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
@@ -5092,6 +5113,7 @@
         </is>
       </c>
       <c r="P23" s="21" t="n"/>
+      <c r="Q23" s="21" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
@@ -5166,6 +5188,7 @@
         </is>
       </c>
       <c r="P24" s="21" t="n"/>
+      <c r="Q24" s="21" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
@@ -5240,6 +5263,7 @@
         </is>
       </c>
       <c r="P25" s="21" t="n"/>
+      <c r="Q25" s="21" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
@@ -5314,6 +5338,7 @@
         </is>
       </c>
       <c r="P26" s="21" t="n"/>
+      <c r="Q26" s="21" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
@@ -5388,6 +5413,7 @@
         </is>
       </c>
       <c r="P27" s="21" t="n"/>
+      <c r="Q27" s="21" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
@@ -5462,6 +5488,7 @@
         </is>
       </c>
       <c r="P28" s="21" t="n"/>
+      <c r="Q28" s="21" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
@@ -5537,6 +5564,7 @@
         </is>
       </c>
       <c r="P29" s="21" t="n"/>
+      <c r="Q29" s="21" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
@@ -5611,6 +5639,7 @@
         </is>
       </c>
       <c r="P30" s="21" t="n"/>
+      <c r="Q30" s="21" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
@@ -5685,6 +5714,7 @@
         </is>
       </c>
       <c r="P31" s="21" t="n"/>
+      <c r="Q31" s="21" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
@@ -5760,6 +5790,7 @@
         </is>
       </c>
       <c r="P32" s="21" t="n"/>
+      <c r="Q32" s="21" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
@@ -5835,6 +5866,7 @@
         </is>
       </c>
       <c r="P33" s="21" t="n"/>
+      <c r="Q33" s="21" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
@@ -5909,6 +5941,7 @@
         </is>
       </c>
       <c r="P34" s="21" t="n"/>
+      <c r="Q34" s="21" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
@@ -5983,6 +6016,7 @@
         </is>
       </c>
       <c r="P35" s="21" t="n"/>
+      <c r="Q35" s="21" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
@@ -6057,6 +6091,7 @@
         </is>
       </c>
       <c r="P36" s="21" t="n"/>
+      <c r="Q36" s="21" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
@@ -6122,15 +6157,16 @@
       </c>
       <c r="N37" s="16" t="inlineStr">
         <is>
-          <t>**算定シートに実績を投入済み。**第10期将来推計用推計人口（令和9〜11年）と、令和7年度の年齢階層別認定率（65〜74歳3.92％／75〜84歳18.72％／85歳以上71.63％）を入力した。85歳以上の認定率は令和6年度82.8％から11.2ポイント下がっている</t>
+          <t>**算定シートに実績を投入済み。**第10期将来推計用推計人口（令和9〜11年）と、令和7年度の年齢階層別認定率（65〜74歳3.92％／75〜84歳18.72％／85歳以上71.63％）を入力した。85歳以上の認定率は令和6年度82.8％から11.2ポイント下がっている。**認定者数の見込みは令和9年度782人・令和10年度781人・令和11年度780人。見える化ワークシートの849人・850人・841人より8.4％低い。**見える化の基点は令和7年9月の865人（断層の直後）で、その後866人→794人へ減っていく動きを織り込んでいない。計画書には令和8年3月末の実績783人と接続する当方の系列を載せる。**なお見込量そのものへの影響は小さい。**見える化の見込量は第1号被保険者数×認定率×利用率の3段の掛け算で、利用率の分母は認定者数（在宅は認定者数から施設・居住系の利用者数を引いたもの）であり、認定率が高く出れば利用率が同じだけ低く出るため積は変わらない</t>
         </is>
       </c>
       <c r="O37" s="16" t="inlineStr">
         <is>
-          <t>**認定率をどの水準で置くか（令和7年度実績か、計上変更前の令和6年度水準か）。2-4の確認結果しだいで前提が変わる**</t>
+          <t>**認定率をどの水準で置くか（令和7年度実績か、計上変更前の令和6年度水準か）。2-4の確認結果しだいで前提が変わる。**あわせて、認定率の分子に第2号被保険者の認定者を含むかを見える化の画面で確認する（確認事項No.125）</t>
         </is>
       </c>
       <c r="P37" s="21" t="n"/>
+      <c r="Q37" s="21" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
@@ -6206,6 +6242,11 @@
       </c>
       <c r="P38" s="17" t="inlineStr">
         <is>
+          <t>**9月15日に、推計方法そのものをバックテストで検証した（推計方法のバックテスト・04_算定・見込量）。**令和5年度・令和6年度を起点に1〜2年先を予測し、実績との絶対誤差を給付費で加重して比べた。総給付費の誤差は、当方の方式（利用率・分母＝第1号被保険者数・窓3年）が3.31％で最も小さい。窓2年3.54％、分母を75歳以上とすると4.24％、直近年度の据え置き5.26％、全サービス一律の伸び5.28％、**大雪地区広域連合の手引きの偏り補正（φ0.5・上限±3％）は5.39％で一律に劣る。**同手引きの判定基準「一律より良いことを示せなければ補正しない」により採らない。分母を認定者数とすると6.39％で、起点年度によって2.20％〜9.60％と振れ幅が大きい</t>
+        </is>
+      </c>
+      <c r="Q38" s="17" t="inlineStr">
+        <is>
           <t>**報酬改定率（令和9年度）の確定。**あわせて、訪問介護の基準期間（3年平均だと令和9年度の見込件数が令和7年度実績の1.27倍。令和7年度単年なら月額▲47円）を協議会にお諮りする</t>
         </is>
       </c>
@@ -6283,6 +6324,7 @@
         </is>
       </c>
       <c r="P39" s="21" t="n"/>
+      <c r="Q39" s="21" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
@@ -6348,7 +6390,7 @@
       </c>
       <c r="N40" s="16" t="inlineStr">
         <is>
-          <t>**所得段階別被保険者数（13段階）、小野町が定める保険料率（第1〜3段階は0.285／0.486／0.685で国の標準より低い）、収納率99.35％、基金保有額12,000千円を投入済み。地域支援事業費は年報 様式4 の令和6年度決算63,916千円（3年計191,749千円）を事業別に割り付けて投入した。総合事業の内訳は国保連月報の総合事業コード（A2・A6・AF）による。**7-4の見込量で算式を通したところ、保険料基準額は月額6,569円（基金取崩なし）、6,467円（保有額12,000千円を全額取崩）、6,270円（第9期と同じ35,000千円を取崩）となった。第9期は6,600円。負担割合が24％になると6,867円。**調整交付金の見込交付割合は第9期計画の公表値から逆算して5.963％。標準の5％ではない（小野町は後期高齢者加入割合が高く低所得層が厚い）**</t>
+          <t>**所得段階別被保険者数（13段階）、小野町が定める保険料率（第1〜3段階は0.285／0.486／0.685で国の標準より低い）、収納率99.35％、基金保有額12,000千円を投入済み。地域支援事業費は年報 様式4 の令和6年度決算63,916千円（3年計191,749千円）を事業別に割り付けて投入した。総合事業の内訳は国保連月報の総合事業コード（A2・A6・AF）による。**7-4の見込量で算式を通したところ、保険料基準額は月額6,570円（基金取崩なし）、6,467円（保有額12,000千円を全額取崩）、6,270円（第9期と同じ35,000千円を取崩）となった。第9期は6,600円。負担割合が24％になると6,867円。**調整交付金の見込交付割合は第9期計画の公表値から逆算して6.148％。標準の5％ではない（小野町は後期高齢者加入割合が高く低所得層が厚い）**※ 逆算される調整交付金見込額219,272千円は基数の取り方によらない。見える化システムは標準給付費見込額のみを基数とするため6.148％、総合事業費を含めると5.963％となる（本件は前者にそろえた）</t>
         </is>
       </c>
       <c r="O40" s="16" t="inlineStr">
@@ -6357,6 +6399,7 @@
         </is>
       </c>
       <c r="P40" s="21" t="n"/>
+      <c r="Q40" s="21" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
@@ -6431,6 +6474,7 @@
         </is>
       </c>
       <c r="P41" s="21" t="n"/>
+      <c r="Q41" s="21" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
@@ -6505,6 +6549,7 @@
         </is>
       </c>
       <c r="P42" s="21" t="n"/>
+      <c r="Q42" s="21" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
@@ -6571,7 +6616,7 @@
       </c>
       <c r="N43" s="16" t="inlineStr">
         <is>
-          <t>**第4版（5章＋資料編・74表）。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定158箇所のうち61箇所が解消し97箇所となった。**第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量・給付費・標準給付費・地域支援事業費の事業別内訳・保険料基準額（月額6,569円）を入れた</t>
+          <t>**第4版（5章＋資料編・74表）。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定158箇所のうち61箇所が解消し97箇所となった。**第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量・給付費・標準給付費・地域支援事業費の事業別内訳・保険料基準額（月額6,570円）を入れた</t>
         </is>
       </c>
       <c r="O43" s="16" t="inlineStr">
@@ -6580,6 +6625,7 @@
         </is>
       </c>
       <c r="P43" s="21" t="n"/>
+      <c r="Q43" s="21" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
@@ -6654,6 +6700,7 @@
         </is>
       </c>
       <c r="P44" s="21" t="n"/>
+      <c r="Q44" s="21" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
@@ -6728,6 +6775,7 @@
         </is>
       </c>
       <c r="P45" s="21" t="n"/>
+      <c r="Q45" s="21" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
@@ -6802,6 +6850,7 @@
         </is>
       </c>
       <c r="P46" s="21" t="n"/>
+      <c r="Q46" s="21" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
@@ -6877,6 +6926,7 @@
         </is>
       </c>
       <c r="P47" s="21" t="n"/>
+      <c r="Q47" s="21" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
@@ -6951,6 +7001,7 @@
         </is>
       </c>
       <c r="P48" s="21" t="n"/>
+      <c r="Q48" s="21" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
@@ -7025,6 +7076,7 @@
         </is>
       </c>
       <c r="P49" s="21" t="n"/>
+      <c r="Q49" s="21" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
@@ -7099,6 +7151,7 @@
         </is>
       </c>
       <c r="P50" s="21" t="n"/>
+      <c r="Q50" s="21" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
@@ -7173,6 +7226,7 @@
         </is>
       </c>
       <c r="P51" s="21" t="n"/>
+      <c r="Q51" s="21" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
@@ -7247,6 +7301,7 @@
         </is>
       </c>
       <c r="P52" s="21" t="n"/>
+      <c r="Q52" s="21" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
@@ -7321,6 +7376,7 @@
         </is>
       </c>
       <c r="P53" s="21" t="n"/>
+      <c r="Q53" s="21" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
@@ -7395,6 +7451,7 @@
         </is>
       </c>
       <c r="P54" s="21" t="n"/>
+      <c r="Q54" s="21" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
@@ -7469,6 +7526,7 @@
         </is>
       </c>
       <c r="P55" s="21" t="n"/>
+      <c r="Q55" s="21" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
@@ -7543,6 +7601,7 @@
         </is>
       </c>
       <c r="P56" s="21" t="n"/>
+      <c r="Q56" s="21" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
@@ -7617,6 +7676,7 @@
         </is>
       </c>
       <c r="P57" s="21" t="n"/>
+      <c r="Q57" s="21" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
@@ -7691,6 +7751,7 @@
         </is>
       </c>
       <c r="P58" s="21" t="n"/>
+      <c r="Q58" s="21" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
@@ -7765,6 +7826,7 @@
         </is>
       </c>
       <c r="P59" s="21" t="n"/>
+      <c r="Q59" s="21" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
@@ -7839,6 +7901,7 @@
         </is>
       </c>
       <c r="P60" s="21" t="n"/>
+      <c r="Q60" s="21" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
@@ -7913,6 +7976,7 @@
         </is>
       </c>
       <c r="P61" s="21" t="n"/>
+      <c r="Q61" s="21" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
@@ -7988,6 +8052,7 @@
         </is>
       </c>
       <c r="P62" s="21" t="n"/>
+      <c r="Q62" s="21" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
@@ -8062,6 +8127,7 @@
         </is>
       </c>
       <c r="P63" s="21" t="n"/>
+      <c r="Q63" s="21" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
@@ -8136,6 +8202,7 @@
         </is>
       </c>
       <c r="P64" s="21" t="n"/>
+      <c r="Q64" s="21" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O64"/>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
@@ -3366,7 +3366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:R64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3537,6 +3537,7 @@
       </c>
       <c r="P2" s="21" t="n"/>
       <c r="Q2" s="21" t="n"/>
+      <c r="R2" s="21" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
@@ -3612,6 +3613,7 @@
       </c>
       <c r="P3" s="21" t="n"/>
       <c r="Q3" s="21" t="n"/>
+      <c r="R3" s="21" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
@@ -3687,6 +3689,7 @@
       </c>
       <c r="P4" s="21" t="n"/>
       <c r="Q4" s="21" t="n"/>
+      <c r="R4" s="21" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -3762,6 +3765,7 @@
       </c>
       <c r="P5" s="21" t="n"/>
       <c r="Q5" s="21" t="n"/>
+      <c r="R5" s="21" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -3837,6 +3841,7 @@
       </c>
       <c r="P6" s="21" t="n"/>
       <c r="Q6" s="21" t="n"/>
+      <c r="R6" s="21" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -3912,6 +3917,7 @@
       </c>
       <c r="P7" s="21" t="n"/>
       <c r="Q7" s="21" t="n"/>
+      <c r="R7" s="21" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
@@ -3987,6 +3993,7 @@
       </c>
       <c r="P8" s="21" t="n"/>
       <c r="Q8" s="21" t="n"/>
+      <c r="R8" s="21" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
@@ -4062,6 +4069,7 @@
       </c>
       <c r="P9" s="21" t="n"/>
       <c r="Q9" s="21" t="n"/>
+      <c r="R9" s="21" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
@@ -4137,6 +4145,7 @@
       </c>
       <c r="P10" s="21" t="n"/>
       <c r="Q10" s="21" t="n"/>
+      <c r="R10" s="21" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
@@ -4212,6 +4221,7 @@
       </c>
       <c r="P11" s="21" t="n"/>
       <c r="Q11" s="21" t="n"/>
+      <c r="R11" s="21" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
@@ -4287,6 +4297,7 @@
       </c>
       <c r="P12" s="21" t="n"/>
       <c r="Q12" s="21" t="n"/>
+      <c r="R12" s="21" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
@@ -4362,6 +4373,7 @@
       </c>
       <c r="P13" s="21" t="n"/>
       <c r="Q13" s="21" t="n"/>
+      <c r="R13" s="21" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
@@ -4437,6 +4449,7 @@
       </c>
       <c r="P14" s="21" t="n"/>
       <c r="Q14" s="21" t="n"/>
+      <c r="R14" s="21" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
@@ -4512,6 +4525,7 @@
       </c>
       <c r="P15" s="21" t="n"/>
       <c r="Q15" s="21" t="n"/>
+      <c r="R15" s="21" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
@@ -4578,16 +4592,17 @@
       </c>
       <c r="N16" s="16" t="inlineStr">
         <is>
-          <t>J16〜J18を取得。自立度Ⅱa 68→148人、M 7→29人</t>
+          <t>**J16〜J18を取得し、9月16日に基準日と県内59市町村での位置を確定した（認知症基本法への対応の点検・03_計画素案）。**自立度Ⅱaは平成24年4月末68人→令和6年10月末148人だが、**同じ期間に認定者数が635人→936人と1.47倍になっており、対認定者ではⅡaが10.7％→15.8％、Ⅱbは23.1％→18.9％と下がる。**推進員は令和3年3月1人→令和6年3月4人（降順19位・中央値3人）、初期集中支援チームの訪問は令和5年度0件（59市町村のうち30団体が0件・中央値0件）、カフェは令和6年4月1か所（中央値1か所）。**体制は県内の標準を満たしており、課題は体制ではなく活動実績である**</t>
         </is>
       </c>
       <c r="O16" s="16" t="inlineStr">
         <is>
-          <t>研修系（J1〜J15）は本町の値が未公表。町の実績で代替する（依頼票H9）</t>
+          <t>**自立度Ⅲa・Ⅲbが受領資料になく、「自立度Ⅱ以上」の合計が出せない（見える化Ｂ7）。**このため認知症高齢者数の見込みは下限（令和9年度335人）にとどまる。研修系（J1〜J15）は本町の値が未公表。町の実績で代替する（依頼票H9）。初期集中支援チームの令和6・7年度の実績も要る（見える化の直近値は令和5年度）</t>
         </is>
       </c>
       <c r="P16" s="21" t="n"/>
       <c r="Q16" s="21" t="n"/>
+      <c r="R16" s="21" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
@@ -4663,6 +4678,7 @@
       </c>
       <c r="P17" s="21" t="n"/>
       <c r="Q17" s="21" t="n"/>
+      <c r="R17" s="21" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
@@ -4738,6 +4754,7 @@
       </c>
       <c r="P18" s="21" t="n"/>
       <c r="Q18" s="21" t="n"/>
+      <c r="R18" s="21" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
@@ -4813,6 +4830,7 @@
       </c>
       <c r="P19" s="21" t="n"/>
       <c r="Q19" s="21" t="n"/>
+      <c r="R19" s="21" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
@@ -4889,6 +4907,7 @@
       </c>
       <c r="P20" s="21" t="n"/>
       <c r="Q20" s="21" t="n"/>
+      <c r="R20" s="21" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
@@ -4964,6 +4983,7 @@
       </c>
       <c r="P21" s="21" t="n"/>
       <c r="Q21" s="21" t="n"/>
+      <c r="R21" s="21" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
@@ -5039,6 +5059,7 @@
       </c>
       <c r="P22" s="21" t="n"/>
       <c r="Q22" s="21" t="n"/>
+      <c r="R22" s="21" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
@@ -5114,6 +5135,7 @@
       </c>
       <c r="P23" s="21" t="n"/>
       <c r="Q23" s="21" t="n"/>
+      <c r="R23" s="21" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
@@ -5189,6 +5211,7 @@
       </c>
       <c r="P24" s="21" t="n"/>
       <c r="Q24" s="21" t="n"/>
+      <c r="R24" s="21" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
@@ -5264,6 +5287,7 @@
       </c>
       <c r="P25" s="21" t="n"/>
       <c r="Q25" s="21" t="n"/>
+      <c r="R25" s="21" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
@@ -5339,6 +5363,7 @@
       </c>
       <c r="P26" s="21" t="n"/>
       <c r="Q26" s="21" t="n"/>
+      <c r="R26" s="21" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
@@ -5414,6 +5439,7 @@
       </c>
       <c r="P27" s="21" t="n"/>
       <c r="Q27" s="21" t="n"/>
+      <c r="R27" s="21" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
@@ -5489,6 +5515,7 @@
       </c>
       <c r="P28" s="21" t="n"/>
       <c r="Q28" s="21" t="n"/>
+      <c r="R28" s="21" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
@@ -5565,6 +5592,7 @@
       </c>
       <c r="P29" s="21" t="n"/>
       <c r="Q29" s="21" t="n"/>
+      <c r="R29" s="21" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
@@ -5640,6 +5668,7 @@
       </c>
       <c r="P30" s="21" t="n"/>
       <c r="Q30" s="21" t="n"/>
+      <c r="R30" s="21" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
@@ -5715,6 +5744,7 @@
       </c>
       <c r="P31" s="21" t="n"/>
       <c r="Q31" s="21" t="n"/>
+      <c r="R31" s="21" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
@@ -5791,6 +5821,7 @@
       </c>
       <c r="P32" s="21" t="n"/>
       <c r="Q32" s="21" t="n"/>
+      <c r="R32" s="21" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
@@ -5867,6 +5898,7 @@
       </c>
       <c r="P33" s="21" t="n"/>
       <c r="Q33" s="21" t="n"/>
+      <c r="R33" s="21" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
@@ -5942,6 +5974,7 @@
       </c>
       <c r="P34" s="21" t="n"/>
       <c r="Q34" s="21" t="n"/>
+      <c r="R34" s="21" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
@@ -6017,6 +6050,7 @@
       </c>
       <c r="P35" s="21" t="n"/>
       <c r="Q35" s="21" t="n"/>
+      <c r="R35" s="21" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
@@ -6092,6 +6126,7 @@
       </c>
       <c r="P36" s="21" t="n"/>
       <c r="Q36" s="21" t="n"/>
+      <c r="R36" s="21" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
@@ -6167,6 +6202,7 @@
       </c>
       <c r="P37" s="21" t="n"/>
       <c r="Q37" s="21" t="n"/>
+      <c r="R37" s="21" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
@@ -6247,7 +6283,12 @@
       </c>
       <c r="Q38" s="17" t="inlineStr">
         <is>
-          <t>**報酬改定率（令和9年度）の確定。**あわせて、訪問介護の基準期間（3年平均だと令和9年度の見込件数が令和7年度実績の1.27倍。令和7年度単年なら月額▲47円）を協議会にお諮りする</t>
+          <t>**9月16日に、認知症基本法の点検にあわせて必要利用定員総数を追加した（介護保険法117条2項1号。10_必要利用定員総数）。**認知症対応型共同生活介護・地域密着型特定施設入居者生活介護・地域密着型介護老人福祉施設入所者生活介護の3サービスについて各年度の必要利用定員総数を定めることは**努力義務ではなく必須記載事項**であり、第9期計画にも当初の見込量算定にもなかった。**いずれも見込量に対し定員に余力があるため現行定員を維持する案（認知症対応型共同生活介護98人・地域密着型特養58人・地域密着型特定施設0人）**</t>
+        </is>
+      </c>
+      <c r="R38" s="17" t="inlineStr">
+        <is>
+          <t>**報酬改定率（令和9年度）の確定。**あわせて、訪問介護の基準期間（3年平均だと令和9年度の見込件数が令和7年度実績の1.27倍。令和7年度単年なら月額▲47円）を協議会にお諮りする。**必要利用定員総数は、認知症対応型共同生活介護の定員が令和4年度71人から令和6年度98人へ増えた経緯と町外の方の利用割合を町に確認したうえで確定する**</t>
         </is>
       </c>
     </row>
@@ -6325,6 +6366,7 @@
       </c>
       <c r="P39" s="21" t="n"/>
       <c r="Q39" s="21" t="n"/>
+      <c r="R39" s="21" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
@@ -6400,6 +6442,7 @@
       </c>
       <c r="P40" s="21" t="n"/>
       <c r="Q40" s="21" t="n"/>
+      <c r="R40" s="21" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
@@ -6475,6 +6518,7 @@
       </c>
       <c r="P41" s="21" t="n"/>
       <c r="Q41" s="21" t="n"/>
+      <c r="R41" s="21" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
@@ -6550,6 +6594,7 @@
       </c>
       <c r="P42" s="21" t="n"/>
       <c r="Q42" s="21" t="n"/>
+      <c r="R42" s="21" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
@@ -6626,6 +6671,7 @@
       </c>
       <c r="P43" s="21" t="n"/>
       <c r="Q43" s="21" t="n"/>
+      <c r="R43" s="21" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
@@ -6701,6 +6747,7 @@
       </c>
       <c r="P44" s="21" t="n"/>
       <c r="Q44" s="21" t="n"/>
+      <c r="R44" s="21" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
@@ -6766,16 +6813,17 @@
       </c>
       <c r="N45" s="16" t="inlineStr">
         <is>
-          <t>計画策定業務設計書 第1章（02_キックオフ・業務計画）。分散＋対応表方式を提案</t>
+          <t>計画策定業務設計書 第1章（02_キックオフ・業務計画）。分散＋対応表方式を提案。**9月16日に認知症基本法の条文により市町村計画の根拠を第13条第1項（努力義務）、調和規定を第2項、策定手続（意見聴取・公表・評価・5年ごとの検討）を第3項が準用する第12条第3〜7項と確定し、素案に反映した（認知症基本法への対応の点検・03_計画素案）。****施策の柱を認知症施策推進大綱の5本柱から法の基本的施策（第14〜21条）に組み替え、大綱では落ちていた若年性認知症・移動のための交通手段の確保・消費生活被害の防止・孤立の防止を追加した。**北塩原村の法定記載事項チェックと川崎町の骨子案を参照している</t>
         </is>
       </c>
       <c r="O45" s="16" t="inlineStr">
         <is>
-          <t>町の意思決定（方式A／B）</t>
+          <t>**認知症の人及びその家族等の意見をどう聴くか（同法13条3項→12条3項）。記述の追加では埋まらず策定過程に関わるため、協議会の委員構成を確認したうえで家族会・認知症カフェでの意見聴取の機会を設けるかを町と協議する。**あわせて福島県の認知症施策推進計画の策定状況、町の意思決定（方式A／B）</t>
         </is>
       </c>
       <c r="P45" s="21" t="n"/>
       <c r="Q45" s="21" t="n"/>
+      <c r="R45" s="21" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
@@ -6851,6 +6899,7 @@
       </c>
       <c r="P46" s="21" t="n"/>
       <c r="Q46" s="21" t="n"/>
+      <c r="R46" s="21" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
@@ -6927,6 +6976,7 @@
       </c>
       <c r="P47" s="21" t="n"/>
       <c r="Q47" s="21" t="n"/>
+      <c r="R47" s="21" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
@@ -7002,6 +7052,7 @@
       </c>
       <c r="P48" s="21" t="n"/>
       <c r="Q48" s="21" t="n"/>
+      <c r="R48" s="21" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
@@ -7077,6 +7128,7 @@
       </c>
       <c r="P49" s="21" t="n"/>
       <c r="Q49" s="21" t="n"/>
+      <c r="R49" s="21" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
@@ -7152,6 +7204,7 @@
       </c>
       <c r="P50" s="21" t="n"/>
       <c r="Q50" s="21" t="n"/>
+      <c r="R50" s="21" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
@@ -7227,6 +7280,7 @@
       </c>
       <c r="P51" s="21" t="n"/>
       <c r="Q51" s="21" t="n"/>
+      <c r="R51" s="21" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
@@ -7302,6 +7356,7 @@
       </c>
       <c r="P52" s="21" t="n"/>
       <c r="Q52" s="21" t="n"/>
+      <c r="R52" s="21" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
@@ -7377,6 +7432,7 @@
       </c>
       <c r="P53" s="21" t="n"/>
       <c r="Q53" s="21" t="n"/>
+      <c r="R53" s="21" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
@@ -7452,6 +7508,7 @@
       </c>
       <c r="P54" s="21" t="n"/>
       <c r="Q54" s="21" t="n"/>
+      <c r="R54" s="21" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
@@ -7527,6 +7584,7 @@
       </c>
       <c r="P55" s="21" t="n"/>
       <c r="Q55" s="21" t="n"/>
+      <c r="R55" s="21" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
@@ -7602,6 +7660,7 @@
       </c>
       <c r="P56" s="21" t="n"/>
       <c r="Q56" s="21" t="n"/>
+      <c r="R56" s="21" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
@@ -7677,6 +7736,7 @@
       </c>
       <c r="P57" s="21" t="n"/>
       <c r="Q57" s="21" t="n"/>
+      <c r="R57" s="21" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
@@ -7752,6 +7812,7 @@
       </c>
       <c r="P58" s="21" t="n"/>
       <c r="Q58" s="21" t="n"/>
+      <c r="R58" s="21" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
@@ -7827,6 +7888,7 @@
       </c>
       <c r="P59" s="21" t="n"/>
       <c r="Q59" s="21" t="n"/>
+      <c r="R59" s="21" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
@@ -7902,6 +7964,7 @@
       </c>
       <c r="P60" s="21" t="n"/>
       <c r="Q60" s="21" t="n"/>
+      <c r="R60" s="21" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
@@ -7977,6 +8040,7 @@
       </c>
       <c r="P61" s="21" t="n"/>
       <c r="Q61" s="21" t="n"/>
+      <c r="R61" s="21" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
@@ -8053,6 +8117,7 @@
       </c>
       <c r="P62" s="21" t="n"/>
       <c r="Q62" s="21" t="n"/>
+      <c r="R62" s="21" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
@@ -8128,6 +8193,7 @@
       </c>
       <c r="P63" s="21" t="n"/>
       <c r="Q63" s="21" t="n"/>
+      <c r="R63" s="21" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
@@ -8203,6 +8269,7 @@
       </c>
       <c r="P64" s="21" t="n"/>
       <c r="Q64" s="21" t="n"/>
+      <c r="R64" s="21" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O64"/>
@@ -10371,7 +10438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10716,59 +10783,119 @@
     </row>
     <row r="12">
       <c r="A12" s="17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>認知症施策推進基本計画の包含の形式が未決</t>
+          <t>**認知症の人及びその家族等の意見聴取の方法が未決**</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>仕様書2(3)は包含を計画の構成要件と定める</t>
+          <t>**認知症基本法13条3項が準用する12条3項は、市町村計画の案の作成にあたり認知症の人及び家族等の意見を聴くよう努めることを求めている**</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>章立てが変わるため、素案の確定前に決める必要がある</t>
+          <t>**記述の追加では埋まらず、策定過程そのものに関わる。協議会の日程から逆算すると、素案の確定前に方針を決める必要がある**</t>
         </is>
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
-          <t>**基本的施策12項目との対応表を作成済み。分散＋対応表方式を提案**</t>
-        </is>
-      </c>
-      <c r="F12" s="20" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>協議会の委員構成に認知症の人又は家族が含まれるかを確認し、含まれない場合は家族会・認知症カフェでの意見聴取の機会を設けるかを町と協議する</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>**地域密着型3サービスの必要利用定員総数が第9期計画にない**</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>介護保険法117条2項1号は3サービスの各年度の必要利用定員総数を計画に定めることを求めている（必須記載事項）</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>**第10期では9月16日に追加済み。**ただし認知症対応型共同生活介護の定員が第9期の方針に反して令和4年度71人から令和6年度98人へ27人増えた経緯が確認できていない</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>増床の事実関係と町外の方の利用割合を町に確認する</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>認知症施策推進基本計画の包含の形式が未決</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>仕様書2(3)は包含を計画の構成要件と定める</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>章立てが変わるため、素案の確定前に決める必要がある</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>**基本的施策12項目との対応表を作成済み。分散＋対応表方式を提案**</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>成果品欄の「（７）」への参照</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>成果品は（１）〜（６）だが、納品仕様欄に「※（７）のデータ（ＣＤ－Ｒ）１部、概要版印刷50部」との記載がある</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>概要版の納品部数の解釈に関わる</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>町に確認する（依頼票C2）</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
@@ -3366,7 +3366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R64"/>
+  <dimension ref="A1:U64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3538,6 +3538,9 @@
       <c r="P2" s="21" t="n"/>
       <c r="Q2" s="21" t="n"/>
       <c r="R2" s="21" t="n"/>
+      <c r="S2" s="21" t="n"/>
+      <c r="T2" s="21" t="n"/>
+      <c r="U2" s="21" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
@@ -3614,6 +3617,9 @@
       <c r="P3" s="21" t="n"/>
       <c r="Q3" s="21" t="n"/>
       <c r="R3" s="21" t="n"/>
+      <c r="S3" s="21" t="n"/>
+      <c r="T3" s="21" t="n"/>
+      <c r="U3" s="21" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
@@ -3690,6 +3696,9 @@
       <c r="P4" s="21" t="n"/>
       <c r="Q4" s="21" t="n"/>
       <c r="R4" s="21" t="n"/>
+      <c r="S4" s="21" t="n"/>
+      <c r="T4" s="21" t="n"/>
+      <c r="U4" s="21" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -3766,6 +3775,9 @@
       <c r="P5" s="21" t="n"/>
       <c r="Q5" s="21" t="n"/>
       <c r="R5" s="21" t="n"/>
+      <c r="S5" s="21" t="n"/>
+      <c r="T5" s="21" t="n"/>
+      <c r="U5" s="21" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -3842,6 +3854,9 @@
       <c r="P6" s="21" t="n"/>
       <c r="Q6" s="21" t="n"/>
       <c r="R6" s="21" t="n"/>
+      <c r="S6" s="21" t="n"/>
+      <c r="T6" s="21" t="n"/>
+      <c r="U6" s="21" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -3918,6 +3933,9 @@
       <c r="P7" s="21" t="n"/>
       <c r="Q7" s="21" t="n"/>
       <c r="R7" s="21" t="n"/>
+      <c r="S7" s="21" t="n"/>
+      <c r="T7" s="21" t="n"/>
+      <c r="U7" s="21" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
@@ -3994,6 +4012,9 @@
       <c r="P8" s="21" t="n"/>
       <c r="Q8" s="21" t="n"/>
       <c r="R8" s="21" t="n"/>
+      <c r="S8" s="21" t="n"/>
+      <c r="T8" s="21" t="n"/>
+      <c r="U8" s="21" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
@@ -4070,6 +4091,9 @@
       <c r="P9" s="21" t="n"/>
       <c r="Q9" s="21" t="n"/>
       <c r="R9" s="21" t="n"/>
+      <c r="S9" s="21" t="n"/>
+      <c r="T9" s="21" t="n"/>
+      <c r="U9" s="21" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
@@ -4146,6 +4170,9 @@
       <c r="P10" s="21" t="n"/>
       <c r="Q10" s="21" t="n"/>
       <c r="R10" s="21" t="n"/>
+      <c r="S10" s="21" t="n"/>
+      <c r="T10" s="21" t="n"/>
+      <c r="U10" s="21" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
@@ -4222,6 +4249,9 @@
       <c r="P11" s="21" t="n"/>
       <c r="Q11" s="21" t="n"/>
       <c r="R11" s="21" t="n"/>
+      <c r="S11" s="21" t="n"/>
+      <c r="T11" s="21" t="n"/>
+      <c r="U11" s="21" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
@@ -4298,6 +4328,9 @@
       <c r="P12" s="21" t="n"/>
       <c r="Q12" s="21" t="n"/>
       <c r="R12" s="21" t="n"/>
+      <c r="S12" s="21" t="n"/>
+      <c r="T12" s="21" t="n"/>
+      <c r="U12" s="21" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
@@ -4374,6 +4407,9 @@
       <c r="P13" s="21" t="n"/>
       <c r="Q13" s="21" t="n"/>
       <c r="R13" s="21" t="n"/>
+      <c r="S13" s="21" t="n"/>
+      <c r="T13" s="21" t="n"/>
+      <c r="U13" s="21" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
@@ -4450,6 +4486,9 @@
       <c r="P14" s="21" t="n"/>
       <c r="Q14" s="21" t="n"/>
       <c r="R14" s="21" t="n"/>
+      <c r="S14" s="21" t="n"/>
+      <c r="T14" s="21" t="n"/>
+      <c r="U14" s="21" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
@@ -4526,6 +4565,9 @@
       <c r="P15" s="21" t="n"/>
       <c r="Q15" s="21" t="n"/>
       <c r="R15" s="21" t="n"/>
+      <c r="S15" s="21" t="n"/>
+      <c r="T15" s="21" t="n"/>
+      <c r="U15" s="21" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
@@ -4603,6 +4645,9 @@
       <c r="P16" s="21" t="n"/>
       <c r="Q16" s="21" t="n"/>
       <c r="R16" s="21" t="n"/>
+      <c r="S16" s="21" t="n"/>
+      <c r="T16" s="21" t="n"/>
+      <c r="U16" s="21" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
@@ -4679,6 +4724,9 @@
       <c r="P17" s="21" t="n"/>
       <c r="Q17" s="21" t="n"/>
       <c r="R17" s="21" t="n"/>
+      <c r="S17" s="21" t="n"/>
+      <c r="T17" s="21" t="n"/>
+      <c r="U17" s="21" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
@@ -4755,6 +4803,9 @@
       <c r="P18" s="21" t="n"/>
       <c r="Q18" s="21" t="n"/>
       <c r="R18" s="21" t="n"/>
+      <c r="S18" s="21" t="n"/>
+      <c r="T18" s="21" t="n"/>
+      <c r="U18" s="21" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
@@ -4831,6 +4882,9 @@
       <c r="P19" s="21" t="n"/>
       <c r="Q19" s="21" t="n"/>
       <c r="R19" s="21" t="n"/>
+      <c r="S19" s="21" t="n"/>
+      <c r="T19" s="21" t="n"/>
+      <c r="U19" s="21" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
@@ -4908,6 +4962,9 @@
       <c r="P20" s="21" t="n"/>
       <c r="Q20" s="21" t="n"/>
       <c r="R20" s="21" t="n"/>
+      <c r="S20" s="21" t="n"/>
+      <c r="T20" s="21" t="n"/>
+      <c r="U20" s="21" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
@@ -4984,6 +5041,9 @@
       <c r="P21" s="21" t="n"/>
       <c r="Q21" s="21" t="n"/>
       <c r="R21" s="21" t="n"/>
+      <c r="S21" s="21" t="n"/>
+      <c r="T21" s="21" t="n"/>
+      <c r="U21" s="21" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
@@ -5060,6 +5120,9 @@
       <c r="P22" s="21" t="n"/>
       <c r="Q22" s="21" t="n"/>
       <c r="R22" s="21" t="n"/>
+      <c r="S22" s="21" t="n"/>
+      <c r="T22" s="21" t="n"/>
+      <c r="U22" s="21" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
@@ -5136,6 +5199,9 @@
       <c r="P23" s="21" t="n"/>
       <c r="Q23" s="21" t="n"/>
       <c r="R23" s="21" t="n"/>
+      <c r="S23" s="21" t="n"/>
+      <c r="T23" s="21" t="n"/>
+      <c r="U23" s="21" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
@@ -5212,6 +5278,9 @@
       <c r="P24" s="21" t="n"/>
       <c r="Q24" s="21" t="n"/>
       <c r="R24" s="21" t="n"/>
+      <c r="S24" s="21" t="n"/>
+      <c r="T24" s="21" t="n"/>
+      <c r="U24" s="21" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
@@ -5288,6 +5357,9 @@
       <c r="P25" s="21" t="n"/>
       <c r="Q25" s="21" t="n"/>
       <c r="R25" s="21" t="n"/>
+      <c r="S25" s="21" t="n"/>
+      <c r="T25" s="21" t="n"/>
+      <c r="U25" s="21" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
@@ -5364,6 +5436,9 @@
       <c r="P26" s="21" t="n"/>
       <c r="Q26" s="21" t="n"/>
       <c r="R26" s="21" t="n"/>
+      <c r="S26" s="21" t="n"/>
+      <c r="T26" s="21" t="n"/>
+      <c r="U26" s="21" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
@@ -5440,6 +5515,9 @@
       <c r="P27" s="21" t="n"/>
       <c r="Q27" s="21" t="n"/>
       <c r="R27" s="21" t="n"/>
+      <c r="S27" s="21" t="n"/>
+      <c r="T27" s="21" t="n"/>
+      <c r="U27" s="21" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
@@ -5516,6 +5594,9 @@
       <c r="P28" s="21" t="n"/>
       <c r="Q28" s="21" t="n"/>
       <c r="R28" s="21" t="n"/>
+      <c r="S28" s="21" t="n"/>
+      <c r="T28" s="21" t="n"/>
+      <c r="U28" s="21" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
@@ -5593,6 +5674,9 @@
       <c r="P29" s="21" t="n"/>
       <c r="Q29" s="21" t="n"/>
       <c r="R29" s="21" t="n"/>
+      <c r="S29" s="21" t="n"/>
+      <c r="T29" s="21" t="n"/>
+      <c r="U29" s="21" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
@@ -5669,6 +5753,9 @@
       <c r="P30" s="21" t="n"/>
       <c r="Q30" s="21" t="n"/>
       <c r="R30" s="21" t="n"/>
+      <c r="S30" s="21" t="n"/>
+      <c r="T30" s="21" t="n"/>
+      <c r="U30" s="21" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
@@ -5745,6 +5832,9 @@
       <c r="P31" s="21" t="n"/>
       <c r="Q31" s="21" t="n"/>
       <c r="R31" s="21" t="n"/>
+      <c r="S31" s="21" t="n"/>
+      <c r="T31" s="21" t="n"/>
+      <c r="U31" s="21" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
@@ -5822,6 +5912,9 @@
       <c r="P32" s="21" t="n"/>
       <c r="Q32" s="21" t="n"/>
       <c r="R32" s="21" t="n"/>
+      <c r="S32" s="21" t="n"/>
+      <c r="T32" s="21" t="n"/>
+      <c r="U32" s="21" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
@@ -5899,6 +5992,9 @@
       <c r="P33" s="21" t="n"/>
       <c r="Q33" s="21" t="n"/>
       <c r="R33" s="21" t="n"/>
+      <c r="S33" s="21" t="n"/>
+      <c r="T33" s="21" t="n"/>
+      <c r="U33" s="21" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
@@ -5975,6 +6071,9 @@
       <c r="P34" s="21" t="n"/>
       <c r="Q34" s="21" t="n"/>
       <c r="R34" s="21" t="n"/>
+      <c r="S34" s="21" t="n"/>
+      <c r="T34" s="21" t="n"/>
+      <c r="U34" s="21" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
@@ -6051,6 +6150,9 @@
       <c r="P35" s="21" t="n"/>
       <c r="Q35" s="21" t="n"/>
       <c r="R35" s="21" t="n"/>
+      <c r="S35" s="21" t="n"/>
+      <c r="T35" s="21" t="n"/>
+      <c r="U35" s="21" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
@@ -6127,6 +6229,9 @@
       <c r="P36" s="21" t="n"/>
       <c r="Q36" s="21" t="n"/>
       <c r="R36" s="21" t="n"/>
+      <c r="S36" s="21" t="n"/>
+      <c r="T36" s="21" t="n"/>
+      <c r="U36" s="21" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
@@ -6203,6 +6308,9 @@
       <c r="P37" s="21" t="n"/>
       <c r="Q37" s="21" t="n"/>
       <c r="R37" s="21" t="n"/>
+      <c r="S37" s="21" t="n"/>
+      <c r="T37" s="21" t="n"/>
+      <c r="U37" s="21" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
@@ -6283,12 +6391,27 @@
       </c>
       <c r="Q38" s="17" t="inlineStr">
         <is>
+          <t>**9月24日に、他町村の手引きの14段階で自己点検した（見込量算定の手引き適合点検・04_算定・見込量）。**済んでいなかった6段階（内的整合・季節性・施策反映・趨勢外の要因・記載事項・自己点検）を埋めた。**新たに分かったことが3つある。**①**単価は報酬改定のない年でも年率＋1.09％伸びており、改定のあった令和6年度の＋1.25％と差がない。**当方は単価を令和7年度で固定しているため、実績の趨勢（年率＋1.13％）で置くと標準給付費が3.43％・保険料が月額211円上がる。固定は過小側の置き方である。②**季節性は、居宅・地域密着型が年度で向きが逆になり再現しない。**施設（冬季が高い）と受給者計（冬季が低い）は再現するが差は2％前後で向きが逆であり相殺される。基準年度が完結年度のため補正は不要。③**施策反映は、当方の式で変数になっているのが第1号被保険者数だけであり、成果指標40件のうち目標値が確定しているものが0件であるため、現時点で反映できるものがない。**歯止めを先に定めた。**自己点検12項目を算定に組み込み、変異試験3件すべてで止まることを確かめた。**</t>
+        </is>
+      </c>
+      <c r="R38" s="17" t="inlineStr">
+        <is>
+          <t>**川崎町の方式（基準年度の要介護度別給付費に要介護度別の認定者数の伸びを乗じる）を小野町のデータで測った。**断層をまたがない令和5年度→令和6年度では誤差▲1.06％と全方式のなかで最も当たる一方、令和7年度を予測先に置く2通りでは▲14.66％・▲13.47％となり、3通りの平均では50設定中49位に落ちる。**令和6年度→令和7年度の認定者数は要介護4が0.755倍・要介護5が0.626倍で、給付費の実績が7.4％しか下がっていないのと合わない。**断層の原因が確認できるまでは採らない。解消すれば要介護度の構成の変化を織り込める点で当方より優れる可能性がある</t>
+        </is>
+      </c>
+      <c r="S38" s="17" t="inlineStr">
+        <is>
+          <t>**9月24日に、地域支援事業の「量」の見込みを追加した（介護保険法117条2項2号。11_地域支援事業の量）。**費用の見込みとは別の必須記載事項であり、第9期計画にもなかった。国保連月報から量を出せるのは介護予防・生活支援サービス事業の3事業だけで、**一般介護予防事業・包括的支援事業・任意事業の13事業は町の事業実績を要する**</t>
+        </is>
+      </c>
+      <c r="T38" s="17" t="inlineStr">
+        <is>
           <t>**9月16日に、認知症基本法の点検にあわせて必要利用定員総数を追加した（介護保険法117条2項1号。10_必要利用定員総数）。**認知症対応型共同生活介護・地域密着型特定施設入居者生活介護・地域密着型介護老人福祉施設入所者生活介護の3サービスについて各年度の必要利用定員総数を定めることは**努力義務ではなく必須記載事項**であり、第9期計画にも当初の見込量算定にもなかった。**いずれも見込量に対し定員に余力があるため現行定員を維持する案（認知症対応型共同生活介護98人・地域密着型特養58人・地域密着型特定施設0人）**</t>
         </is>
       </c>
-      <c r="R38" s="17" t="inlineStr">
-        <is>
-          <t>**報酬改定率（令和9年度）の確定。**あわせて、訪問介護の基準期間（3年平均だと令和9年度の見込件数が令和7年度実績の1.27倍。令和7年度単年なら月額▲47円）を協議会にお諮りする。**必要利用定員総数は、認知症対応型共同生活介護の定員が令和4年度71人から令和6年度98人へ増えた経緯と町外の方の利用割合を町に確認したうえで確定する**</t>
+      <c r="U38" s="17" t="inlineStr">
+        <is>
+          <t>**報酬改定率（令和9年度）の確定。**あわせて、訪問介護の基準期間（3年平均だと令和9年度の見込件数が令和7年度実績の1.27倍。令和7年度単年なら月額▲47円）を協議会にお諮りする。**必要利用定員総数は、認知症対応型共同生活介護の定員が令和4年度71人から令和6年度98人へ増えた経緯と町外の方の利用割合を町に確認したうえで確定する。****あわせて、単価を令和7年度で固定していることを協議会にお諮りする（実績の趨勢で置くと月額＋211円）**</t>
         </is>
       </c>
     </row>
@@ -6367,6 +6490,9 @@
       <c r="P39" s="21" t="n"/>
       <c r="Q39" s="21" t="n"/>
       <c r="R39" s="21" t="n"/>
+      <c r="S39" s="21" t="n"/>
+      <c r="T39" s="21" t="n"/>
+      <c r="U39" s="21" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
@@ -6443,6 +6569,9 @@
       <c r="P40" s="21" t="n"/>
       <c r="Q40" s="21" t="n"/>
       <c r="R40" s="21" t="n"/>
+      <c r="S40" s="21" t="n"/>
+      <c r="T40" s="21" t="n"/>
+      <c r="U40" s="21" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
@@ -6519,6 +6648,9 @@
       <c r="P41" s="21" t="n"/>
       <c r="Q41" s="21" t="n"/>
       <c r="R41" s="21" t="n"/>
+      <c r="S41" s="21" t="n"/>
+      <c r="T41" s="21" t="n"/>
+      <c r="U41" s="21" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
@@ -6595,6 +6727,9 @@
       <c r="P42" s="21" t="n"/>
       <c r="Q42" s="21" t="n"/>
       <c r="R42" s="21" t="n"/>
+      <c r="S42" s="21" t="n"/>
+      <c r="T42" s="21" t="n"/>
+      <c r="U42" s="21" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
@@ -6672,6 +6807,9 @@
       <c r="P43" s="21" t="n"/>
       <c r="Q43" s="21" t="n"/>
       <c r="R43" s="21" t="n"/>
+      <c r="S43" s="21" t="n"/>
+      <c r="T43" s="21" t="n"/>
+      <c r="U43" s="21" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
@@ -6748,6 +6886,9 @@
       <c r="P44" s="21" t="n"/>
       <c r="Q44" s="21" t="n"/>
       <c r="R44" s="21" t="n"/>
+      <c r="S44" s="21" t="n"/>
+      <c r="T44" s="21" t="n"/>
+      <c r="U44" s="21" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
@@ -6824,6 +6965,9 @@
       <c r="P45" s="21" t="n"/>
       <c r="Q45" s="21" t="n"/>
       <c r="R45" s="21" t="n"/>
+      <c r="S45" s="21" t="n"/>
+      <c r="T45" s="21" t="n"/>
+      <c r="U45" s="21" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
@@ -6900,6 +7044,9 @@
       <c r="P46" s="21" t="n"/>
       <c r="Q46" s="21" t="n"/>
       <c r="R46" s="21" t="n"/>
+      <c r="S46" s="21" t="n"/>
+      <c r="T46" s="21" t="n"/>
+      <c r="U46" s="21" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
@@ -6977,6 +7124,9 @@
       <c r="P47" s="21" t="n"/>
       <c r="Q47" s="21" t="n"/>
       <c r="R47" s="21" t="n"/>
+      <c r="S47" s="21" t="n"/>
+      <c r="T47" s="21" t="n"/>
+      <c r="U47" s="21" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
@@ -7053,6 +7203,9 @@
       <c r="P48" s="21" t="n"/>
       <c r="Q48" s="21" t="n"/>
       <c r="R48" s="21" t="n"/>
+      <c r="S48" s="21" t="n"/>
+      <c r="T48" s="21" t="n"/>
+      <c r="U48" s="21" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
@@ -7129,6 +7282,9 @@
       <c r="P49" s="21" t="n"/>
       <c r="Q49" s="21" t="n"/>
       <c r="R49" s="21" t="n"/>
+      <c r="S49" s="21" t="n"/>
+      <c r="T49" s="21" t="n"/>
+      <c r="U49" s="21" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
@@ -7205,6 +7361,9 @@
       <c r="P50" s="21" t="n"/>
       <c r="Q50" s="21" t="n"/>
       <c r="R50" s="21" t="n"/>
+      <c r="S50" s="21" t="n"/>
+      <c r="T50" s="21" t="n"/>
+      <c r="U50" s="21" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
@@ -7281,6 +7440,9 @@
       <c r="P51" s="21" t="n"/>
       <c r="Q51" s="21" t="n"/>
       <c r="R51" s="21" t="n"/>
+      <c r="S51" s="21" t="n"/>
+      <c r="T51" s="21" t="n"/>
+      <c r="U51" s="21" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
@@ -7357,6 +7519,9 @@
       <c r="P52" s="21" t="n"/>
       <c r="Q52" s="21" t="n"/>
       <c r="R52" s="21" t="n"/>
+      <c r="S52" s="21" t="n"/>
+      <c r="T52" s="21" t="n"/>
+      <c r="U52" s="21" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
@@ -7433,6 +7598,9 @@
       <c r="P53" s="21" t="n"/>
       <c r="Q53" s="21" t="n"/>
       <c r="R53" s="21" t="n"/>
+      <c r="S53" s="21" t="n"/>
+      <c r="T53" s="21" t="n"/>
+      <c r="U53" s="21" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
@@ -7509,6 +7677,9 @@
       <c r="P54" s="21" t="n"/>
       <c r="Q54" s="21" t="n"/>
       <c r="R54" s="21" t="n"/>
+      <c r="S54" s="21" t="n"/>
+      <c r="T54" s="21" t="n"/>
+      <c r="U54" s="21" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
@@ -7585,6 +7756,9 @@
       <c r="P55" s="21" t="n"/>
       <c r="Q55" s="21" t="n"/>
       <c r="R55" s="21" t="n"/>
+      <c r="S55" s="21" t="n"/>
+      <c r="T55" s="21" t="n"/>
+      <c r="U55" s="21" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
@@ -7661,6 +7835,9 @@
       <c r="P56" s="21" t="n"/>
       <c r="Q56" s="21" t="n"/>
       <c r="R56" s="21" t="n"/>
+      <c r="S56" s="21" t="n"/>
+      <c r="T56" s="21" t="n"/>
+      <c r="U56" s="21" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
@@ -7737,6 +7914,9 @@
       <c r="P57" s="21" t="n"/>
       <c r="Q57" s="21" t="n"/>
       <c r="R57" s="21" t="n"/>
+      <c r="S57" s="21" t="n"/>
+      <c r="T57" s="21" t="n"/>
+      <c r="U57" s="21" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
@@ -7813,6 +7993,9 @@
       <c r="P58" s="21" t="n"/>
       <c r="Q58" s="21" t="n"/>
       <c r="R58" s="21" t="n"/>
+      <c r="S58" s="21" t="n"/>
+      <c r="T58" s="21" t="n"/>
+      <c r="U58" s="21" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
@@ -7889,6 +8072,9 @@
       <c r="P59" s="21" t="n"/>
       <c r="Q59" s="21" t="n"/>
       <c r="R59" s="21" t="n"/>
+      <c r="S59" s="21" t="n"/>
+      <c r="T59" s="21" t="n"/>
+      <c r="U59" s="21" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
@@ -7965,6 +8151,9 @@
       <c r="P60" s="21" t="n"/>
       <c r="Q60" s="21" t="n"/>
       <c r="R60" s="21" t="n"/>
+      <c r="S60" s="21" t="n"/>
+      <c r="T60" s="21" t="n"/>
+      <c r="U60" s="21" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
@@ -8041,6 +8230,9 @@
       <c r="P61" s="21" t="n"/>
       <c r="Q61" s="21" t="n"/>
       <c r="R61" s="21" t="n"/>
+      <c r="S61" s="21" t="n"/>
+      <c r="T61" s="21" t="n"/>
+      <c r="U61" s="21" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
@@ -8118,6 +8310,9 @@
       <c r="P62" s="21" t="n"/>
       <c r="Q62" s="21" t="n"/>
       <c r="R62" s="21" t="n"/>
+      <c r="S62" s="21" t="n"/>
+      <c r="T62" s="21" t="n"/>
+      <c r="U62" s="21" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
@@ -8194,6 +8389,9 @@
       <c r="P63" s="21" t="n"/>
       <c r="Q63" s="21" t="n"/>
       <c r="R63" s="21" t="n"/>
+      <c r="S63" s="21" t="n"/>
+      <c r="T63" s="21" t="n"/>
+      <c r="U63" s="21" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
@@ -8270,6 +8468,9 @@
       <c r="P64" s="21" t="n"/>
       <c r="Q64" s="21" t="n"/>
       <c r="R64" s="21" t="n"/>
+      <c r="S64" s="21" t="n"/>
+      <c r="T64" s="21" t="n"/>
+      <c r="U64" s="21" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O64"/>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
@@ -6801,10 +6801,14 @@
       </c>
       <c r="O43" s="16" t="inlineStr">
         <is>
-          <t>**残る97箇所の内訳は、協議会で設定する目標値39、町データ待ち35、町・国の決定9、算定7、見える化出力6、保険料の算定1。町データ待ちの筆頭は成果指標の現状値と、一般介護予防事業費・包括的支援事業・任意事業費の事業別内訳**</t>
-        </is>
-      </c>
-      <c r="P43" s="21" t="n"/>
+          <t>**9月24日に、受託者が算定すべき未確定箇所をすべて解消した。**所得段階別保険料率を13段階すべてについて算定し（乗率・年額・被保険者数・構成比）、必要利用定員総数・地域支援事業の量・認知症高齢者数を加えた。**未確定は158箇所→94箇所となり、【算定後に記載】は0件になった。****あわせて数値の誤りを2件正した。**①所得第2段階の乗率を0.485としていたが、年報 様式1 所得段階別および第9期の年額38,500円（＝0.486×79,200円）から0.486が正しい（素案・骨子案・給付費等分析の3点）。②所得第1〜3段階の割合を28％としていたが、1,094人÷3,443人で31.8％が正しい。**第2章1の人口（見える化の将来推計・暦年）と第2章6の被保険者数（第10期将来推計用推計人口・年度）が別系列であることを注記した。**従前の注は「保険料算定との整合のため見える化の推計を用いる」と書いていたが、保険料算定は後者を用いており誤りであった</t>
+        </is>
+      </c>
+      <c r="P43" s="17" t="inlineStr">
+        <is>
+          <t>**残る94箇所の内訳は、協議会で設定する目標値39、町データ待ち39、町・国の決定12、見える化出力4。****受託者の算定によるものは残っていない。**町データ待ちの筆頭は成果指標の現状値、一般介護予防事業費・包括的支援事業・任意事業費の事業別内訳、地域支援事業の量（13事業）、認知症対応型共同生活介護の増床の経緯**</t>
+        </is>
+      </c>
       <c r="Q43" s="21" t="n"/>
       <c r="R43" s="21" t="n"/>
       <c r="S43" s="21" t="n"/>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
@@ -6484,10 +6484,14 @@
       </c>
       <c r="O39" s="16" t="inlineStr">
         <is>
-          <t>**アカウント・権限・作業範囲・時期の確認（依頼票C5）。これが決まらないと総括表が出せず、対計画比・供給実現性の検証に進めない**</t>
-        </is>
-      </c>
-      <c r="P39" s="21" t="n"/>
+          <t>**9月24日に、受領したワークシートを1行ずつ読んで入力値を確定した（見える化システム入力値一覧・入力の手順。11_見える化出力依頼）。****入力の前に直す設定が2件ある。**①1人1月あたり給付費の実績値が令和8年度になっている。令和8年度の列は1か月分で、人数・回数・日数の非ゼロ36件のうち31件（86.1％）が整数である（令和6年度は46件中5件、令和7年度は40件中8件で、いずれも12分の1単位の小数）。令和7年度に切り替える。②認定率の伸びが令和6年度→令和7年度になっている。**見える化の認定者数は各年9月末の値で、令和7年度の865人は令和7年9月の断層の直後にあたる。**令和6年度937人は国保連の令和6年10月審査分と一致し、令和7年度865人と令和8年度865人は同値で令和8年度に実績がないことを示す。計上方法の確認が取れるまでこの伸びは使えない。**入力欄は、当方で用意できるものが28欄、町の資料が要るものが26欄。**町の資料が要るのは一般介護予防事業5欄（計5,305千円）、包括的支援事業・任意事業8欄（計29,335千円）、審査支払手数料等2欄（計531千円）、準備基金、令和8年度の当初予算など。**所得段階別加入割合13段階を入れると調整交付金見込交付割合が自動で出るため、当方の逆算値6.148％と突き合わせる**</t>
+        </is>
+      </c>
+      <c r="P39" s="17" t="inlineStr">
+        <is>
+          <t>**アカウント・権限・作業範囲・時期の確認（依頼票C5）。これが決まらないと総括表が出せず、対計画比・供給実現性の検証に進めない。****あわせて、令和7年8〜9月の認定者数の計上方法の確認が最優先。これが決まらないと認定率の伸びを置けない**</t>
+        </is>
+      </c>
       <c r="Q39" s="21" t="n"/>
       <c r="R39" s="21" t="n"/>
       <c r="S39" s="21" t="n"/>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
@@ -3366,7 +3366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U64"/>
+  <dimension ref="A1:W64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3541,6 +3541,8 @@
       <c r="S2" s="21" t="n"/>
       <c r="T2" s="21" t="n"/>
       <c r="U2" s="21" t="n"/>
+      <c r="V2" s="21" t="n"/>
+      <c r="W2" s="21" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
@@ -3620,6 +3622,8 @@
       <c r="S3" s="21" t="n"/>
       <c r="T3" s="21" t="n"/>
       <c r="U3" s="21" t="n"/>
+      <c r="V3" s="21" t="n"/>
+      <c r="W3" s="21" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
@@ -3699,6 +3703,8 @@
       <c r="S4" s="21" t="n"/>
       <c r="T4" s="21" t="n"/>
       <c r="U4" s="21" t="n"/>
+      <c r="V4" s="21" t="n"/>
+      <c r="W4" s="21" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -3778,6 +3784,8 @@
       <c r="S5" s="21" t="n"/>
       <c r="T5" s="21" t="n"/>
       <c r="U5" s="21" t="n"/>
+      <c r="V5" s="21" t="n"/>
+      <c r="W5" s="21" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -3857,6 +3865,8 @@
       <c r="S6" s="21" t="n"/>
       <c r="T6" s="21" t="n"/>
       <c r="U6" s="21" t="n"/>
+      <c r="V6" s="21" t="n"/>
+      <c r="W6" s="21" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -3936,6 +3946,8 @@
       <c r="S7" s="21" t="n"/>
       <c r="T7" s="21" t="n"/>
       <c r="U7" s="21" t="n"/>
+      <c r="V7" s="21" t="n"/>
+      <c r="W7" s="21" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
@@ -4015,6 +4027,8 @@
       <c r="S8" s="21" t="n"/>
       <c r="T8" s="21" t="n"/>
       <c r="U8" s="21" t="n"/>
+      <c r="V8" s="21" t="n"/>
+      <c r="W8" s="21" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
@@ -4094,6 +4108,8 @@
       <c r="S9" s="21" t="n"/>
       <c r="T9" s="21" t="n"/>
       <c r="U9" s="21" t="n"/>
+      <c r="V9" s="21" t="n"/>
+      <c r="W9" s="21" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
@@ -4173,6 +4189,8 @@
       <c r="S10" s="21" t="n"/>
       <c r="T10" s="21" t="n"/>
       <c r="U10" s="21" t="n"/>
+      <c r="V10" s="21" t="n"/>
+      <c r="W10" s="21" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
@@ -4252,6 +4270,8 @@
       <c r="S11" s="21" t="n"/>
       <c r="T11" s="21" t="n"/>
       <c r="U11" s="21" t="n"/>
+      <c r="V11" s="21" t="n"/>
+      <c r="W11" s="21" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
@@ -4331,6 +4351,8 @@
       <c r="S12" s="21" t="n"/>
       <c r="T12" s="21" t="n"/>
       <c r="U12" s="21" t="n"/>
+      <c r="V12" s="21" t="n"/>
+      <c r="W12" s="21" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
@@ -4410,6 +4432,8 @@
       <c r="S13" s="21" t="n"/>
       <c r="T13" s="21" t="n"/>
       <c r="U13" s="21" t="n"/>
+      <c r="V13" s="21" t="n"/>
+      <c r="W13" s="21" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
@@ -4489,6 +4513,8 @@
       <c r="S14" s="21" t="n"/>
       <c r="T14" s="21" t="n"/>
       <c r="U14" s="21" t="n"/>
+      <c r="V14" s="21" t="n"/>
+      <c r="W14" s="21" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
@@ -4568,6 +4594,8 @@
       <c r="S15" s="21" t="n"/>
       <c r="T15" s="21" t="n"/>
       <c r="U15" s="21" t="n"/>
+      <c r="V15" s="21" t="n"/>
+      <c r="W15" s="21" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
@@ -4648,6 +4676,8 @@
       <c r="S16" s="21" t="n"/>
       <c r="T16" s="21" t="n"/>
       <c r="U16" s="21" t="n"/>
+      <c r="V16" s="21" t="n"/>
+      <c r="W16" s="21" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
@@ -4727,6 +4757,8 @@
       <c r="S17" s="21" t="n"/>
       <c r="T17" s="21" t="n"/>
       <c r="U17" s="21" t="n"/>
+      <c r="V17" s="21" t="n"/>
+      <c r="W17" s="21" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
@@ -4806,6 +4838,8 @@
       <c r="S18" s="21" t="n"/>
       <c r="T18" s="21" t="n"/>
       <c r="U18" s="21" t="n"/>
+      <c r="V18" s="21" t="n"/>
+      <c r="W18" s="21" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
@@ -4885,6 +4919,8 @@
       <c r="S19" s="21" t="n"/>
       <c r="T19" s="21" t="n"/>
       <c r="U19" s="21" t="n"/>
+      <c r="V19" s="21" t="n"/>
+      <c r="W19" s="21" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
@@ -4965,6 +5001,8 @@
       <c r="S20" s="21" t="n"/>
       <c r="T20" s="21" t="n"/>
       <c r="U20" s="21" t="n"/>
+      <c r="V20" s="21" t="n"/>
+      <c r="W20" s="21" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
@@ -5044,6 +5082,8 @@
       <c r="S21" s="21" t="n"/>
       <c r="T21" s="21" t="n"/>
       <c r="U21" s="21" t="n"/>
+      <c r="V21" s="21" t="n"/>
+      <c r="W21" s="21" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
@@ -5123,6 +5163,8 @@
       <c r="S22" s="21" t="n"/>
       <c r="T22" s="21" t="n"/>
       <c r="U22" s="21" t="n"/>
+      <c r="V22" s="21" t="n"/>
+      <c r="W22" s="21" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
@@ -5202,6 +5244,8 @@
       <c r="S23" s="21" t="n"/>
       <c r="T23" s="21" t="n"/>
       <c r="U23" s="21" t="n"/>
+      <c r="V23" s="21" t="n"/>
+      <c r="W23" s="21" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
@@ -5281,6 +5325,8 @@
       <c r="S24" s="21" t="n"/>
       <c r="T24" s="21" t="n"/>
       <c r="U24" s="21" t="n"/>
+      <c r="V24" s="21" t="n"/>
+      <c r="W24" s="21" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
@@ -5360,6 +5406,8 @@
       <c r="S25" s="21" t="n"/>
       <c r="T25" s="21" t="n"/>
       <c r="U25" s="21" t="n"/>
+      <c r="V25" s="21" t="n"/>
+      <c r="W25" s="21" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
@@ -5439,6 +5487,8 @@
       <c r="S26" s="21" t="n"/>
       <c r="T26" s="21" t="n"/>
       <c r="U26" s="21" t="n"/>
+      <c r="V26" s="21" t="n"/>
+      <c r="W26" s="21" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
@@ -5518,6 +5568,8 @@
       <c r="S27" s="21" t="n"/>
       <c r="T27" s="21" t="n"/>
       <c r="U27" s="21" t="n"/>
+      <c r="V27" s="21" t="n"/>
+      <c r="W27" s="21" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
@@ -5597,6 +5649,8 @@
       <c r="S28" s="21" t="n"/>
       <c r="T28" s="21" t="n"/>
       <c r="U28" s="21" t="n"/>
+      <c r="V28" s="21" t="n"/>
+      <c r="W28" s="21" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
@@ -5677,6 +5731,8 @@
       <c r="S29" s="21" t="n"/>
       <c r="T29" s="21" t="n"/>
       <c r="U29" s="21" t="n"/>
+      <c r="V29" s="21" t="n"/>
+      <c r="W29" s="21" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
@@ -5756,6 +5812,8 @@
       <c r="S30" s="21" t="n"/>
       <c r="T30" s="21" t="n"/>
       <c r="U30" s="21" t="n"/>
+      <c r="V30" s="21" t="n"/>
+      <c r="W30" s="21" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
@@ -5835,6 +5893,8 @@
       <c r="S31" s="21" t="n"/>
       <c r="T31" s="21" t="n"/>
       <c r="U31" s="21" t="n"/>
+      <c r="V31" s="21" t="n"/>
+      <c r="W31" s="21" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
@@ -5915,6 +5975,8 @@
       <c r="S32" s="21" t="n"/>
       <c r="T32" s="21" t="n"/>
       <c r="U32" s="21" t="n"/>
+      <c r="V32" s="21" t="n"/>
+      <c r="W32" s="21" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
@@ -5995,6 +6057,8 @@
       <c r="S33" s="21" t="n"/>
       <c r="T33" s="21" t="n"/>
       <c r="U33" s="21" t="n"/>
+      <c r="V33" s="21" t="n"/>
+      <c r="W33" s="21" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
@@ -6074,6 +6138,8 @@
       <c r="S34" s="21" t="n"/>
       <c r="T34" s="21" t="n"/>
       <c r="U34" s="21" t="n"/>
+      <c r="V34" s="21" t="n"/>
+      <c r="W34" s="21" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
@@ -6153,6 +6219,8 @@
       <c r="S35" s="21" t="n"/>
       <c r="T35" s="21" t="n"/>
       <c r="U35" s="21" t="n"/>
+      <c r="V35" s="21" t="n"/>
+      <c r="W35" s="21" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
@@ -6232,6 +6300,8 @@
       <c r="S36" s="21" t="n"/>
       <c r="T36" s="21" t="n"/>
       <c r="U36" s="21" t="n"/>
+      <c r="V36" s="21" t="n"/>
+      <c r="W36" s="21" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
@@ -6311,6 +6381,8 @@
       <c r="S37" s="21" t="n"/>
       <c r="T37" s="21" t="n"/>
       <c r="U37" s="21" t="n"/>
+      <c r="V37" s="21" t="n"/>
+      <c r="W37" s="21" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
@@ -6410,6 +6482,16 @@
         </is>
       </c>
       <c r="U38" s="17" t="inlineStr">
+        <is>
+          <t>**9月25日に、令和8年度の置き方を4通りで比べ、国保連月報で裏づけた（12_令和8年度の置き方）。**令和7年度の実績に対する比は、据え置き1.0000／令和6→令和7の動きを1年延長0.9255／当方の現行方式1.0171／**月報3か月の実績0.9598**。**当方の現行方式は実績より6.0％高い。**令和5〜7年度の3年平均が、下がり続けている系列を上に引いているため。令和8年度を月報の実績で置き人口で延ばす自然体推計ケースでは、総給付費の3年計が2,876,614千円（▲5.6％）、保険料が月額6,224円（100円未満切上げで6,300円）となる。**見える化システムの自然体推計と同じ構造であり、保険料のケース比較に加えた。**令和8年度は3か月分しかなく完結年度ではないため、残りの月の実績を見たうえで協議会にお諮りして確定する</t>
+        </is>
+      </c>
+      <c r="V38" s="17" t="inlineStr">
+        <is>
+          <t>**認定者数の見込みを算式に置き換えた。**従前は785／782／781／780とハードコードしていたが、記載の方法（年齢階層別認定率×将来推計人口）で計算すると**787／782／777／772**となり、令和10・11年度で4人・8人ずれていた。**令和6年度→令和7年度の認定率の変化を一定として延ばす置き方は採れない。**65〜74歳▲1.38ポイント・75〜84歳▲1.66ポイント・85歳以上▲11.20ポイントで、毎年加えると令和10年度に65〜74歳の認定率が負になり、令和11年度の認定者数は329人まで落ちる。断層がこの変化に入っているため</t>
+        </is>
+      </c>
+      <c r="W38" s="17" t="inlineStr">
         <is>
           <t>**報酬改定率（令和9年度）の確定。**あわせて、訪問介護の基準期間（3年平均だと令和9年度の見込件数が令和7年度実績の1.27倍。令和7年度単年なら月額▲47円）を協議会にお諮りする。**必要利用定員総数は、認知症対応型共同生活介護の定員が令和4年度71人から令和6年度98人へ増えた経緯と町外の方の利用割合を町に確認したうえで確定する。****あわせて、単価を令和7年度で固定していることを協議会にお諮りする（実績の趨勢で置くと月額＋211円）**</t>
         </is>
@@ -6497,6 +6579,8 @@
       <c r="S39" s="21" t="n"/>
       <c r="T39" s="21" t="n"/>
       <c r="U39" s="21" t="n"/>
+      <c r="V39" s="21" t="n"/>
+      <c r="W39" s="21" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
@@ -6576,6 +6660,8 @@
       <c r="S40" s="21" t="n"/>
       <c r="T40" s="21" t="n"/>
       <c r="U40" s="21" t="n"/>
+      <c r="V40" s="21" t="n"/>
+      <c r="W40" s="21" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
@@ -6655,6 +6741,8 @@
       <c r="S41" s="21" t="n"/>
       <c r="T41" s="21" t="n"/>
       <c r="U41" s="21" t="n"/>
+      <c r="V41" s="21" t="n"/>
+      <c r="W41" s="21" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
@@ -6734,6 +6822,8 @@
       <c r="S42" s="21" t="n"/>
       <c r="T42" s="21" t="n"/>
       <c r="U42" s="21" t="n"/>
+      <c r="V42" s="21" t="n"/>
+      <c r="W42" s="21" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
@@ -6818,6 +6908,8 @@
       <c r="S43" s="21" t="n"/>
       <c r="T43" s="21" t="n"/>
       <c r="U43" s="21" t="n"/>
+      <c r="V43" s="21" t="n"/>
+      <c r="W43" s="21" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
@@ -6897,6 +6989,8 @@
       <c r="S44" s="21" t="n"/>
       <c r="T44" s="21" t="n"/>
       <c r="U44" s="21" t="n"/>
+      <c r="V44" s="21" t="n"/>
+      <c r="W44" s="21" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
@@ -6976,6 +7070,8 @@
       <c r="S45" s="21" t="n"/>
       <c r="T45" s="21" t="n"/>
       <c r="U45" s="21" t="n"/>
+      <c r="V45" s="21" t="n"/>
+      <c r="W45" s="21" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
@@ -7055,6 +7151,8 @@
       <c r="S46" s="21" t="n"/>
       <c r="T46" s="21" t="n"/>
       <c r="U46" s="21" t="n"/>
+      <c r="V46" s="21" t="n"/>
+      <c r="W46" s="21" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
@@ -7135,6 +7233,8 @@
       <c r="S47" s="21" t="n"/>
       <c r="T47" s="21" t="n"/>
       <c r="U47" s="21" t="n"/>
+      <c r="V47" s="21" t="n"/>
+      <c r="W47" s="21" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
@@ -7214,6 +7314,8 @@
       <c r="S48" s="21" t="n"/>
       <c r="T48" s="21" t="n"/>
       <c r="U48" s="21" t="n"/>
+      <c r="V48" s="21" t="n"/>
+      <c r="W48" s="21" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
@@ -7293,6 +7395,8 @@
       <c r="S49" s="21" t="n"/>
       <c r="T49" s="21" t="n"/>
       <c r="U49" s="21" t="n"/>
+      <c r="V49" s="21" t="n"/>
+      <c r="W49" s="21" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
@@ -7372,6 +7476,8 @@
       <c r="S50" s="21" t="n"/>
       <c r="T50" s="21" t="n"/>
       <c r="U50" s="21" t="n"/>
+      <c r="V50" s="21" t="n"/>
+      <c r="W50" s="21" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
@@ -7451,6 +7557,8 @@
       <c r="S51" s="21" t="n"/>
       <c r="T51" s="21" t="n"/>
       <c r="U51" s="21" t="n"/>
+      <c r="V51" s="21" t="n"/>
+      <c r="W51" s="21" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
@@ -7530,6 +7638,8 @@
       <c r="S52" s="21" t="n"/>
       <c r="T52" s="21" t="n"/>
       <c r="U52" s="21" t="n"/>
+      <c r="V52" s="21" t="n"/>
+      <c r="W52" s="21" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
@@ -7609,6 +7719,8 @@
       <c r="S53" s="21" t="n"/>
       <c r="T53" s="21" t="n"/>
       <c r="U53" s="21" t="n"/>
+      <c r="V53" s="21" t="n"/>
+      <c r="W53" s="21" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
@@ -7688,6 +7800,8 @@
       <c r="S54" s="21" t="n"/>
       <c r="T54" s="21" t="n"/>
       <c r="U54" s="21" t="n"/>
+      <c r="V54" s="21" t="n"/>
+      <c r="W54" s="21" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
@@ -7767,6 +7881,8 @@
       <c r="S55" s="21" t="n"/>
       <c r="T55" s="21" t="n"/>
       <c r="U55" s="21" t="n"/>
+      <c r="V55" s="21" t="n"/>
+      <c r="W55" s="21" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
@@ -7846,6 +7962,8 @@
       <c r="S56" s="21" t="n"/>
       <c r="T56" s="21" t="n"/>
       <c r="U56" s="21" t="n"/>
+      <c r="V56" s="21" t="n"/>
+      <c r="W56" s="21" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
@@ -7925,6 +8043,8 @@
       <c r="S57" s="21" t="n"/>
       <c r="T57" s="21" t="n"/>
       <c r="U57" s="21" t="n"/>
+      <c r="V57" s="21" t="n"/>
+      <c r="W57" s="21" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
@@ -8004,6 +8124,8 @@
       <c r="S58" s="21" t="n"/>
       <c r="T58" s="21" t="n"/>
       <c r="U58" s="21" t="n"/>
+      <c r="V58" s="21" t="n"/>
+      <c r="W58" s="21" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
@@ -8083,6 +8205,8 @@
       <c r="S59" s="21" t="n"/>
       <c r="T59" s="21" t="n"/>
       <c r="U59" s="21" t="n"/>
+      <c r="V59" s="21" t="n"/>
+      <c r="W59" s="21" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
@@ -8162,6 +8286,8 @@
       <c r="S60" s="21" t="n"/>
       <c r="T60" s="21" t="n"/>
       <c r="U60" s="21" t="n"/>
+      <c r="V60" s="21" t="n"/>
+      <c r="W60" s="21" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
@@ -8241,6 +8367,8 @@
       <c r="S61" s="21" t="n"/>
       <c r="T61" s="21" t="n"/>
       <c r="U61" s="21" t="n"/>
+      <c r="V61" s="21" t="n"/>
+      <c r="W61" s="21" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
@@ -8321,6 +8449,8 @@
       <c r="S62" s="21" t="n"/>
       <c r="T62" s="21" t="n"/>
       <c r="U62" s="21" t="n"/>
+      <c r="V62" s="21" t="n"/>
+      <c r="W62" s="21" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
@@ -8400,6 +8530,8 @@
       <c r="S63" s="21" t="n"/>
       <c r="T63" s="21" t="n"/>
       <c r="U63" s="21" t="n"/>
+      <c r="V63" s="21" t="n"/>
+      <c r="W63" s="21" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
@@ -8479,6 +8611,8 @@
       <c r="S64" s="21" t="n"/>
       <c r="T64" s="21" t="n"/>
       <c r="U64" s="21" t="n"/>
+      <c r="V64" s="21" t="n"/>
+      <c r="W64" s="21" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O64"/>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
@@ -20,7 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_ブロック別進捗" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_WBS'!$A$1:$O$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_WBS'!$A$1:$O$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2149,11 +2149,12 @@
       <c r="D12" s="16" t="inlineStr">
         <is>
           <t>2-8 サービス自給率の分析
-2-10 見える化 優先度C分野の出力</t>
+2-10 見える化 優先度C分野の出力
+2-11 保険者機能強化推進交付金等の評価結果の整理</t>
         </is>
       </c>
       <c r="E12" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" s="18" t="inlineStr">
         <is>
@@ -2814,31 +2815,31 @@
         </is>
       </c>
       <c r="C2" s="17">
-        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A2)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$65,$A2)</f>
         <v/>
       </c>
       <c r="D2" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A2,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A2,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="E2" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A2,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A2,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="F2" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A2,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A2,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="G2" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A2,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A2,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="H2" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A2,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A2,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="I2" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A2)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A2)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A2)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A2)*'01_WBS'!$M$2:$M$65)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A2)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A2)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="J2" s="16" t="inlineStr">
@@ -2859,31 +2860,31 @@
         </is>
       </c>
       <c r="C3" s="17">
-        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A3)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$65,$A3)</f>
         <v/>
       </c>
       <c r="D3" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A3,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A3,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="E3" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A3,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A3,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="F3" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A3,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A3,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="G3" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A3,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A3,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="H3" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A3,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A3,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="I3" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A3)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A3)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A3)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A3)*'01_WBS'!$M$2:$M$65)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A3)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A3)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="J3" s="16" t="inlineStr">
@@ -2904,31 +2905,31 @@
         </is>
       </c>
       <c r="C4" s="17">
-        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A4)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$65,$A4)</f>
         <v/>
       </c>
       <c r="D4" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A4,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A4,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="E4" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A4,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A4,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="F4" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A4,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A4,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="G4" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A4,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A4,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="H4" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A4,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A4,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="I4" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A4)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A4)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A4)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A4)*'01_WBS'!$M$2:$M$65)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A4)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A4)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="J4" s="16" t="inlineStr">
@@ -2949,31 +2950,31 @@
         </is>
       </c>
       <c r="C5" s="17">
-        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A5)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$65,$A5)</f>
         <v/>
       </c>
       <c r="D5" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A5,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A5,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="E5" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A5,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A5,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="F5" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A5,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A5,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="G5" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A5,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A5,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="H5" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A5,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A5,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="I5" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A5)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A5)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A5)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A5)*'01_WBS'!$M$2:$M$65)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A5)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A5)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="J5" s="16" t="inlineStr">
@@ -2994,31 +2995,31 @@
         </is>
       </c>
       <c r="C6" s="17">
-        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A6)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$65,$A6)</f>
         <v/>
       </c>
       <c r="D6" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A6,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A6,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="E6" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A6,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A6,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="F6" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A6,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A6,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="G6" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A6,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A6,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="H6" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A6,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A6,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="I6" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A6)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A6)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A6)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A6)*'01_WBS'!$M$2:$M$65)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A6)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A6)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="J6" s="16" t="inlineStr">
@@ -3039,31 +3040,31 @@
         </is>
       </c>
       <c r="C7" s="17">
-        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A7)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$65,$A7)</f>
         <v/>
       </c>
       <c r="D7" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A7,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A7,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="E7" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A7,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A7,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="F7" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A7,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A7,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="G7" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A7,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A7,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="H7" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A7,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A7,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="I7" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A7)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A7)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A7)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A7)*'01_WBS'!$M$2:$M$65)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A7)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A7)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="J7" s="16" t="inlineStr">
@@ -3084,31 +3085,31 @@
         </is>
       </c>
       <c r="C8" s="17">
-        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A8)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$65,$A8)</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A8,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A8,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A8,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A8,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A8,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A8,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="G8" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A8,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A8,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="H8" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A8,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A8,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="I8" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A8)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A8)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A8)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A8)*'01_WBS'!$M$2:$M$65)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A8)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A8)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="J8" s="16" t="inlineStr">
@@ -3129,31 +3130,31 @@
         </is>
       </c>
       <c r="C9" s="17">
-        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A9)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$65,$A9)</f>
         <v/>
       </c>
       <c r="D9" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A9,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A9,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="E9" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A9,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A9,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="F9" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A9,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A9,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="G9" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A9,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A9,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="H9" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A9,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A9,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="I9" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A9)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A9)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A9)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A9)*'01_WBS'!$M$2:$M$65)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A9)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A9)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="J9" s="16" t="inlineStr">
@@ -3174,31 +3175,31 @@
         </is>
       </c>
       <c r="C10" s="17">
-        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A10)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$65,$A10)</f>
         <v/>
       </c>
       <c r="D10" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A10,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A10,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="E10" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A10,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A10,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="F10" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A10,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A10,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="G10" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A10,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A10,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="H10" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A10,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A10,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="I10" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A10)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A10)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A10)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A10)*'01_WBS'!$M$2:$M$65)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A10)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A10)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="J10" s="16" t="inlineStr">
@@ -3219,31 +3220,31 @@
         </is>
       </c>
       <c r="C11" s="17">
-        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A11)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$65,$A11)</f>
         <v/>
       </c>
       <c r="D11" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A11,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A11,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="E11" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A11,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A11,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="F11" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A11,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A11,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="G11" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A11,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A11,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="H11" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A11,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A11,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="I11" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A11)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A11)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A11)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A11)*'01_WBS'!$M$2:$M$65)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A11)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A11)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="J11" s="16" t="inlineStr">
@@ -3264,31 +3265,31 @@
         </is>
       </c>
       <c r="C12" s="17">
-        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A12)</f>
+        <f>COUNTIF('01_WBS'!$E$2:$E$65,$A12)</f>
         <v/>
       </c>
       <c r="D12" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A12,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A12,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="E12" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A12,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A12,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="F12" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A12,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A12,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="G12" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A12,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A12,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="H12" s="17">
-        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A12,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$E$2:$E$65,$A12,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="I12" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A12)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A12)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A12)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A12)*'01_WBS'!$M$2:$M$65)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A12)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$E$2:$E$65=$A12)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="J12" s="16" t="inlineStr">
@@ -3329,7 +3330,7 @@
         <v/>
       </c>
       <c r="I13" s="28">
-        <f>IF(SUM('01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT('01_WBS'!$L$2:$L$64,'01_WBS'!$M$2:$M$64)/SUM('01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUM('01_WBS'!$M$2:$M$65)=0,0,SUMPRODUCT('01_WBS'!$L$2:$L$65,'01_WBS'!$M$2:$M$65)/SUM('01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="J13" s="16" t="inlineStr"/>
@@ -3366,7 +3367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W64"/>
+  <dimension ref="A1:W65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4925,38 +4926,37 @@
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>P3 給付費等の分析</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-11</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>給付費等分析結果報告書の作成</t>
+          <t>保険者機能強化推進交付金等の評価結果の整理</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>サービス費目ごとの給付費・地域支援事業の分析、制度改正の影響</t>
+          <t>評価指標に対する該当状況、全国・県内での位置、計画への反映</t>
         </is>
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>B3 介護保険給付費等の分析</t>
+          <t>B2 統計分析</t>
         </is>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>仕様書4(1)②・成果品①</t>
+          <t>仕様書4(1)①オ</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>【4(1)②】介護保険給付費等の分析。介護サービス費目ごとの介護給付費や地域支援事業の利用状況等を分析し、現在の状況や傾向の把握、また、制度改正に伴う影響等を分析し、今後の見通しや具体的施策を検討する。
-【成果品①】（1）介護保険給付費等分析結果報告書　※データ（CD-R）1部、冊子（簡易製本）3部</t>
+          <t>【4(1)①オ】統計分析（オ）その他計画策定に必要な推計</t>
         </is>
       </c>
       <c r="H20" s="17" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="J20" s="17" t="inlineStr">
@@ -4980,19 +4980,19 @@
         </is>
       </c>
       <c r="L20" s="19" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="M20" s="20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N20" s="16" t="inlineStr">
         <is>
-          <t>**第5版（8章・44表・約29,500字）。**第9期計画との対比、施策体系との対応、認定者数20期系列と年齢階層別分解、令和7年度調査による検証まで整理</t>
+          <t>**9月25日に令和8年度の評価指標と全国集計（都道府県分）を受領し、協議会資料として整理した（08_協議会資料）。**福島県は令和7年度468点・42位から令和8年度530点・26位へ上がり、伸び幅＋62点は47都道府県で3位。ただし全国平均535.6点に届かず、東北6県では5番目。**全国の6割以上が得点していて福島県が0点の項目が21件あり、うち認知症施策に関する市町村支援（全国の93.6％が得点）、チームオレンジ設置状況（70.2％）、介護予防等と保健事業の一体的実施に向けた環境整備ウ・エ・オ（80〜83％）は小野町の施策に直に効く。****県の支援が薄い領域として、素案は町が自前で組み立てる前提で書く。****令和8年度に成果指向型配分枠（100点・800点とは別枠）が新設され、対象層の特定とアウトプット／アウトカム指標の分離、目標値の記載を求めている。第4章の成果指標42件のうち38件が目標値未設定であり、整理の仕方が交付金の配分に直に効く。**評価結果は計画本文には載せず毎年度の協議会資料として扱う（評価結果を外部の議論の場で検証すること自体が指標の要件であるため）</t>
         </is>
       </c>
       <c r="O20" s="16" t="inlineStr">
         <is>
-          <t>町の給付実績（依頼票S1・S2）で数値を確定する</t>
+          <t>**市町村分の評価指標と小野町の得点票（令和6〜8年度）。受領したのは都道府県分のみで、町自身の得点分析はできていない**</t>
         </is>
       </c>
       <c r="P20" s="21" t="n"/>
@@ -5012,17 +5012,17 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>町の給付実績との突合</t>
+          <t>給付費等分析結果報告書の作成</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>見える化システムの値と町の給付実績の突合</t>
+          <t>サービス費目ごとの給付費・地域支援事業の分析、制度改正の影響</t>
         </is>
       </c>
       <c r="E21" s="16" t="inlineStr">
@@ -5032,12 +5032,13 @@
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>仕様書4(1)②</t>
+          <t>仕様書4(1)②・成果品①</t>
         </is>
       </c>
       <c r="G21" s="16" t="inlineStr">
         <is>
-          <t>【4(1)②】介護保険給付費等の分析。介護サービス費目ごとの介護給付費や地域支援事業の利用状況等を分析し、現在の状況や傾向の把握、また、制度改正に伴う影響等を分析し、今後の見通しや具体的施策を検討する。</t>
+          <t>【4(1)②】介護保険給付費等の分析。介護サービス費目ごとの介護給付費や地域支援事業の利用状況等を分析し、現在の状況や傾向の把握、また、制度改正に伴う影響等を分析し、今後の見通しや具体的施策を検討する。
+【成果品①】（1）介護保険給付費等分析結果報告書　※データ（CD-R）1部、冊子（簡易製本）3部</t>
         </is>
       </c>
       <c r="H21" s="17" t="inlineStr">
@@ -5047,12 +5048,12 @@
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -5061,19 +5062,19 @@
         </is>
       </c>
       <c r="L21" s="19" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="M21" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N21" s="16" t="inlineStr">
         <is>
-          <t>**年報 様式2によりサービス別給付費（件数・単位数・費用額・給付費）の令和3〜7年度5年分を取得。様式1の6により受給者数も取得。**令和7年度の給付費総計は1,005,144,062円</t>
+          <t>**第5版（8章・44表・約29,500字）。**第9期計画との対比、施策体系との対応、認定者数20期系列と年齢階層別分解、令和7年度調査による検証まで整理</t>
         </is>
       </c>
       <c r="O21" s="16" t="inlineStr">
         <is>
-          <t>見える化システムの値との突合作業</t>
+          <t>町の給付実績（依頼票S1・S2）で数値を確定する</t>
         </is>
       </c>
       <c r="P21" s="21" t="n"/>
@@ -5093,32 +5094,32 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>3-3</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>成果品①の製本・納品</t>
+          <t>町の給付実績との突合</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>データCD-R1部＋冊子（簡易製本）3部</t>
+          <t>見える化システムの値と町の給付実績の突合</t>
         </is>
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>B9 成果品の納品</t>
+          <t>B3 介護保険給付費等の分析</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>仕様書4 成果品①</t>
+          <t>仕様書4(1)②</t>
         </is>
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>【成果品①】（1）介護保険給付費等分析結果報告書　※データ（CD-R）1部、冊子（簡易製本）3部</t>
+          <t>【4(1)②】介護保険給付費等の分析。介護サービス費目ごとの介護給付費や地域支援事業の利用状況等を分析し、現在の状況や傾向の把握、また、制度改正に伴う影響等を分析し、今後の見通しや具体的施策を検討する。</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
@@ -5128,33 +5129,33 @@
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="K22" s="24" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K22" s="20" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="L22" s="19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M22" s="20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N22" s="16" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**年報 様式2によりサービス別給付費（件数・単位数・費用額・給付費）の令和3〜7年度5年分を取得。様式1の6により受給者数も取得。**令和7年度の給付費総計は1,005,144,062円</t>
         </is>
       </c>
       <c r="O22" s="16" t="inlineStr">
         <is>
-          <t>報告書の確定</t>
+          <t>見える化システムの値との突合作業</t>
         </is>
       </c>
       <c r="P22" s="21" t="n"/>
@@ -5169,37 +5170,37 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>P4 調査結果の反映</t>
+          <t>P3 給付費等の分析</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>調査結果報告書の確認</t>
+          <t>成果品①の製本・納品</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>令和8年3月・104頁の報告書の内容確認と妥当性の検証</t>
+          <t>データCD-R1部＋冊子（簡易製本）3部</t>
         </is>
       </c>
       <c r="E23" s="16" t="inlineStr">
         <is>
-          <t>B4 令和7年度調査結果の反映</t>
+          <t>B9 成果品の納品</t>
         </is>
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>仕様書4(1)③</t>
+          <t>仕様書4 成果品①</t>
         </is>
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>【4(1)③】介護予防・日常生活圏域ニーズ調査、在宅介護実態調査結果の反映。令和7年度に実施した調査結果を反映させる。</t>
+          <t>【成果品①】（1）介護保険給付費等分析結果報告書　※データ（CD-R）1部、冊子（簡易製本）3部</t>
         </is>
       </c>
       <c r="H23" s="17" t="inlineStr">
@@ -5209,33 +5210,33 @@
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="K23" s="18" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="L23" s="19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M23" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N23" s="16" t="inlineStr">
         <is>
-          <t>単純集計とリスク分析（年齢階層別・男女別・認定状況別）を取得。報告書内の不整合3件を指摘</t>
+          <t>―</t>
         </is>
       </c>
       <c r="O23" s="16" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>報告書の確定</t>
         </is>
       </c>
       <c r="P23" s="21" t="n"/>
@@ -5255,17 +5256,17 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>集計データの整理</t>
+          <t>調査結果報告書の確認</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>リスク10項目×9区分の保持</t>
+          <t>令和8年3月・104頁の報告書の内容確認と妥当性の検証</t>
         </is>
       </c>
       <c r="E24" s="16" t="inlineStr">
@@ -5307,11 +5308,11 @@
         <v>100</v>
       </c>
       <c r="M24" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N24" s="16" t="inlineStr">
         <is>
-          <t>集計データ整理ブック（14_アンケート集計・9シート）</t>
+          <t>単純集計とリスク分析（年齢階層別・男女別・認定状況別）を取得。報告書内の不整合3件を指摘</t>
         </is>
       </c>
       <c r="O24" s="16" t="inlineStr">
@@ -5336,17 +5337,17 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>集計結果・分析報告書の作成</t>
+          <t>集計データの整理</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>単純集計、リスク分析、前回対比、8つの分析、第9期課題への到達状況、第10期への示唆</t>
+          <t>リスク10項目×9区分の保持</t>
         </is>
       </c>
       <c r="E25" s="16" t="inlineStr">
@@ -5388,11 +5389,11 @@
         <v>100</v>
       </c>
       <c r="M25" s="20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N25" s="16" t="inlineStr">
         <is>
-          <t>**7章・72表・約27,800字（14_アンケート集計）**</t>
+          <t>集計データ整理ブック（14_アンケート集計・9シート）</t>
         </is>
       </c>
       <c r="O25" s="16" t="inlineStr">
@@ -5417,17 +5418,17 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>クロス集計の設計</t>
+          <t>集計結果・分析報告書の作成</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>前回計画の課題に基づくクロス集計25件の設計</t>
+          <t>単純集計、リスク分析、前回対比、8つの分析、第9期課題への到達状況、第10期への示唆</t>
         </is>
       </c>
       <c r="E26" s="16" t="inlineStr">
@@ -5469,11 +5470,11 @@
         <v>100</v>
       </c>
       <c r="M26" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N26" s="16" t="inlineStr">
         <is>
-          <t>クロス集計設計書（8シート・25件）。4件掲載済、17件が個票を要し、4件は設問なし</t>
+          <t>**7章・72表・約27,800字（14_アンケート集計）**</t>
         </is>
       </c>
       <c r="O26" s="16" t="inlineStr">
@@ -5498,17 +5499,17 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>個票によるクロス集計</t>
+          <t>クロス集計の設計</t>
         </is>
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>要介護度別・世帯構成別のクロス集計17件</t>
+          <t>前回計画の課題に基づくクロス集計25件の設計</t>
         </is>
       </c>
       <c r="E27" s="16" t="inlineStr">
@@ -5533,33 +5534,33 @@
       </c>
       <c r="I27" s="17" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="J27" s="17" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="K27" s="23" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K27" s="18" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L27" s="19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27" s="20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N27" s="16" t="inlineStr">
         <is>
+          <t>クロス集計設計書（8シート・25件）。4件掲載済、17件が個票を要し、4件は設問なし</t>
+        </is>
+      </c>
+      <c r="O27" s="16" t="inlineStr">
+        <is>
           <t>―</t>
-        </is>
-      </c>
-      <c r="O27" s="16" t="inlineStr">
-        <is>
-          <t>**令和7年度調査の個票データ（依頼票H16）。地区情報の有無も要確認**</t>
         </is>
       </c>
       <c r="P27" s="21" t="n"/>
@@ -5579,17 +5580,17 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>レッドチームレビュー</t>
+          <t>個票によるクロス集計</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>集計・分析の反証検証</t>
+          <t>要介護度別・世帯構成別のクロス集計17件</t>
         </is>
       </c>
       <c r="E28" s="16" t="inlineStr">
@@ -5614,33 +5615,33 @@
       </c>
       <c r="I28" s="17" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="J28" s="17" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="K28" s="18" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="L28" s="19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M28" s="20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N28" s="16" t="inlineStr">
         <is>
-          <t>REDTEAM 2本（14_アンケート集計）。数値の取り違え1件を自己検出し修正</t>
+          <t>―</t>
         </is>
       </c>
       <c r="O28" s="16" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**令和7年度調査の個票データ（依頼票H16）。地区情報の有無も要確認**</t>
         </is>
       </c>
       <c r="P28" s="21" t="n"/>
@@ -5655,38 +5656,37 @@
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>P5 第9期の評価</t>
+          <t>P4 調査結果の反映</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>協議会資料（第9期評価・調査結果）の作成</t>
+          <t>レッドチームレビュー</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>第9期が第5章2(2)で自ら定める4点検項目に沿って評価</t>
+          <t>集計・分析の反証検証</t>
         </is>
       </c>
       <c r="E29" s="16" t="inlineStr">
         <is>
-          <t>B3 介護保険給付費等の分析</t>
+          <t>B4 令和7年度調査結果の反映</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>仕様書4(1)②・4(5)</t>
+          <t>仕様書4(1)③</t>
         </is>
       </c>
       <c r="G29" s="16" t="inlineStr">
         <is>
-          <t>【4(1)②】介護保険給付費等の分析。介護サービス費目ごとの介護給付費や地域支援事業の利用状況等を分析し、現在の状況や傾向の把握、また、制度改正に伴う影響等を分析し、今後の見通しや具体的施策を検討する。
-【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
+          <t>【4(1)③】介護予防・日常生活圏域ニーズ調査、在宅介護実態調査結果の反映。令和7年度に実施した調査結果を反映させる。</t>
         </is>
       </c>
       <c r="H29" s="17" t="inlineStr">
@@ -5713,11 +5713,11 @@
         <v>100</v>
       </c>
       <c r="M29" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N29" s="16" t="inlineStr">
         <is>
-          <t>**協議会資料（08_協議会資料・42表・約23,500字）**</t>
+          <t>REDTEAM 2本（14_アンケート集計）。数値の取り違え1件を自己検出し修正</t>
         </is>
       </c>
       <c r="O29" s="16" t="inlineStr">
@@ -5742,17 +5742,17 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>成果目標の達成状況の確定</t>
+          <t>協議会資料（第9期評価・調査結果）の作成</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>第9期の見込みと実績の対比</t>
+          <t>第9期が第5章2(2)で自ら定める4点検項目に沿って評価</t>
         </is>
       </c>
       <c r="E30" s="16" t="inlineStr">
@@ -5762,12 +5762,13 @@
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>仕様書4(1)②</t>
+          <t>仕様書4(1)②・4(5)</t>
         </is>
       </c>
       <c r="G30" s="16" t="inlineStr">
         <is>
-          <t>【4(1)②】介護保険給付費等の分析。介護サービス費目ごとの介護給付費や地域支援事業の利用状況等を分析し、現在の状況や傾向の把握、また、制度改正に伴う影響等を分析し、今後の見通しや具体的施策を検討する。</t>
+          <t>【4(1)②】介護保険給付費等の分析。介護サービス費目ごとの介護給付費や地域支援事業の利用状況等を分析し、現在の状況や傾向の把握、また、制度改正に伴う影響等を分析し、今後の見通しや具体的施策を検討する。
+【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
       <c r="H30" s="17" t="inlineStr">
@@ -5777,33 +5778,33 @@
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="J30" s="17" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="K30" s="20" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K30" s="18" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L30" s="19" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="M30" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N30" s="16" t="inlineStr">
         <is>
-          <t>**「第9期計画の見込みと実績の対比」（10_給付費等分析・8章6表）を作成。**第9期が見込んだ標準給付費に対する実績は令和6年度98.6％、**令和7年度91.1％（▲106,199千円）。**特定入所者介護サービス費は101.8％・95.8％でほぼ計画どおりであり、下振れが施設利用の減少によるものではないことを確認した。成果品①第7章7、骨子案 参考1 に反映する</t>
+          <t>**協議会資料（08_協議会資料・42表・約23,500字）**</t>
         </is>
       </c>
       <c r="O30" s="16" t="inlineStr">
         <is>
-          <t>**地域支援事業費の実績（年報 様式4の令和6・7年度が未入力。依頼票H3）と成果指標の現状値（H1〜H15）。令和8年度は年度途中のため令和9年夏の年報を待つ**</t>
+          <t>―</t>
         </is>
       </c>
       <c r="P30" s="21" t="n"/>
@@ -5823,17 +5824,17 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>施設整備方針との不整合の確認</t>
+          <t>成果目標の達成状況の確定</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>第9期は新規整備を行わない方針だが、認知症対応型共同生活介護の定員が27人（38.0％）増</t>
+          <t>第9期の見込みと実績の対比</t>
         </is>
       </c>
       <c r="E31" s="16" t="inlineStr">
@@ -5853,7 +5854,7 @@
       </c>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="I31" s="17" t="inlineStr">
@@ -5863,28 +5864,28 @@
       </c>
       <c r="J31" s="17" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="K31" s="24" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K31" s="20" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="L31" s="19" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M31" s="20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N31" s="16" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**「第9期計画の見込みと実績の対比」（10_給付費等分析・8章6表）を作成。**第9期が見込んだ標準給付費に対する実績は令和6年度98.6％、**令和7年度91.1％（▲106,199千円）。**特定入所者介護サービス費は101.8％・95.8％でほぼ計画どおりであり、下振れが施設利用の減少によるものではないことを確認した。成果品①第7章7、骨子案 参考1 に反映する</t>
         </is>
       </c>
       <c r="O31" s="16" t="inlineStr">
         <is>
-          <t>整備の経緯の確認（依頼票H15）</t>
+          <t>**地域支援事業費の実績（年報 様式4の令和6・7年度が未入力。依頼票H3）と成果指標の現状値（H1〜H15）。令和8年度は年度途中のため令和9年夏の年報を待つ**</t>
         </is>
       </c>
       <c r="P31" s="21" t="n"/>
@@ -5899,74 +5900,73 @@
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>P6 骨子案</t>
+          <t>P5 第9期の評価</t>
         </is>
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>骨子案の作成</t>
+          <t>施設整備方針との不整合の確認</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>基本課題・施策方向・重点課題・施策体系</t>
+          <t>第9期は新規整備を行わない方針だが、認知症対応型共同生活介護の定員が27人（38.0％）増</t>
         </is>
       </c>
       <c r="E32" s="16" t="inlineStr">
         <is>
-          <t>B6 骨子案・素案の作成</t>
+          <t>B3 介護保険給付費等の分析</t>
         </is>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>仕様書4(3)・成果品③</t>
+          <t>仕様書4(1)②</t>
         </is>
       </c>
       <c r="G32" s="16" t="inlineStr">
         <is>
-          <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。
-【成果品③】（3）小野町高齢者保健福祉計画・第10期介護保険事業計画骨子案　※データ（CD-R）1部、冊子（簡易製本）3部</t>
+          <t>【4(1)②】介護保険給付費等の分析。介護サービス費目ごとの介護給付費や地域支援事業の利用状況等を分析し、現在の状況や傾向の把握、また、制度改正に伴う影響等を分析し、今後の見通しや具体的施策を検討する。</t>
         </is>
       </c>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="I32" s="17" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="J32" s="17" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="K32" s="20" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="L32" s="19" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M32" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N32" s="16" t="inlineStr">
         <is>
-          <t>**第3版（13表・9,241字）。**第9期の5章構成・3基本目標・14施策を反映し、地域福祉計画との重複を精査。第9期の見込みと実績の対比も収載</t>
+          <t>―</t>
         </is>
       </c>
       <c r="O32" s="16" t="inlineStr">
         <is>
-          <t>実績データによる数値の確定</t>
+          <t>整備の経緯の確認（依頼票H15）</t>
         </is>
       </c>
       <c r="P32" s="21" t="n"/>
@@ -5986,17 +5986,17 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>骨子案の協議（協議会）</t>
+          <t>骨子案の作成</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>基本理念・基本目標・施策体系の合意</t>
+          <t>基本課題・施策方向・重点課題・施策体系</t>
         </is>
       </c>
       <c r="E33" s="16" t="inlineStr">
@@ -6006,49 +6006,49 @@
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>仕様書4(3)・4(5)</t>
+          <t>仕様書4(3)・成果品③</t>
         </is>
       </c>
       <c r="G33" s="16" t="inlineStr">
         <is>
           <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。
-【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
+【成果品③】（3）小野町高齢者保健福祉計画・第10期介護保険事業計画骨子案　※データ（CD-R）1部、冊子（簡易製本）3部</t>
         </is>
       </c>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="I33" s="17" t="inlineStr">
         <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="J33" s="17" t="inlineStr">
+        <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="J33" s="17" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="K33" s="24" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K33" s="20" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="L33" s="19" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M33" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N33" s="16" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**第3版（13表・9,241字）。**第9期の5章構成・3基本目標・14施策を反映し、地域福祉計画との重複を精査。第9期の見込みと実績の対比も収載</t>
         </is>
       </c>
       <c r="O33" s="16" t="inlineStr">
         <is>
-          <t>**協議会の開催回数・時期が未定（依頼票C4）**</t>
+          <t>実績データによる数値の確定</t>
         </is>
       </c>
       <c r="P33" s="21" t="n"/>
@@ -6068,47 +6068,48 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="C34" s="16" t="inlineStr">
         <is>
-          <t>成果品③の製本・納品</t>
+          <t>骨子案の協議（協議会）</t>
         </is>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>データCD-R1部＋冊子（簡易製本）3部</t>
+          <t>基本理念・基本目標・施策体系の合意</t>
         </is>
       </c>
       <c r="E34" s="16" t="inlineStr">
         <is>
-          <t>B9 成果品の納品</t>
+          <t>B6 骨子案・素案の作成</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>仕様書4 成果品③</t>
+          <t>仕様書4(3)・4(5)</t>
         </is>
       </c>
       <c r="G34" s="16" t="inlineStr">
         <is>
-          <t>【成果品③】（3）小野町高齢者保健福祉計画・第10期介護保険事業計画骨子案　※データ（CD-R）1部、冊子（簡易製本）3部</t>
+          <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。
+【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="J34" s="17" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="K34" s="24" t="inlineStr">
@@ -6120,7 +6121,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N34" s="16" t="inlineStr">
         <is>
@@ -6129,7 +6130,7 @@
       </c>
       <c r="O34" s="16" t="inlineStr">
         <is>
-          <t>骨子案の確定</t>
+          <t>**協議会の開催回数・時期が未定（依頼票C4）**</t>
         </is>
       </c>
       <c r="P34" s="21" t="n"/>
@@ -6144,37 +6145,37 @@
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>P7 推計・算定</t>
+          <t>P6 骨子案</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>7-1</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>算定シートの構築</t>
+          <t>成果品③の製本・納品</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>サービス54区分の単価×量から給付費、標準給付費、保険料までを算式でつなぐ</t>
+          <t>データCD-R1部＋冊子（簡易製本）3部</t>
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>B5 事業量推計・保険料算出・介護財政</t>
+          <t>B9 成果品の納品</t>
         </is>
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t>仕様書4(2)</t>
+          <t>仕様書4 成果品③</t>
         </is>
       </c>
       <c r="G35" s="16" t="inlineStr">
         <is>
-          <t>【4(2)】サービス事業量推計、保険料の算出、介護財政の見通しの検討・調整。「見える化」システムを活用したサービス見込量を推計及び保険料の算出を行うこと。（「見える化」システムへの入力作業を含む。）なお、算定にあたっては、新たに介護施設を整備する場合や制度改正により条件が変わる場合等、様々なケースで勘案する必要があるため、想定されるケースごとに保険料の算定を行うものとする。</t>
+          <t>【成果品③】（3）小野町高齢者保健福祉計画・第10期介護保険事業計画骨子案　※データ（CD-R）1部、冊子（簡易製本）3部</t>
         </is>
       </c>
       <c r="H35" s="17" t="inlineStr">
@@ -6184,33 +6185,33 @@
       </c>
       <c r="I35" s="17" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="J35" s="17" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="K35" s="18" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="L35" s="19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M35" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N35" s="16" t="inlineStr">
         <is>
-          <t>**見込量保険料算定シート（04_算定・見込量・11シート）。**第9期の実数で検算済み（月額6,442円 対 実際6,600円。差2.4％は仮置き値による）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="O35" s="16" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>骨子案の確定</t>
         </is>
       </c>
       <c r="P35" s="21" t="n"/>
@@ -6230,17 +6231,17 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>7-1</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>保険料算定のケース設定の確定</t>
+          <t>算定シートの構築</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>標準（低位・高位）、施設整備あり、制度改正の影響、基金活用、保険料据置の逆算</t>
+          <t>サービス54区分の単価×量から給付費、標準給付費、保険料までを算式でつなぐ</t>
         </is>
       </c>
       <c r="E36" s="16" t="inlineStr">
@@ -6282,11 +6283,11 @@
         <v>100</v>
       </c>
       <c r="M36" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N36" s="16" t="inlineStr">
         <is>
-          <t>**C1〜C6。引継ぎ時点の3ケースは基金の扱いのみで、仕様書が例示する施設整備・制度改正に対応していなかった**</t>
+          <t>**見込量保険料算定シート（04_算定・見込量・11シート）。**第9期の実数で検算済み（月額6,442円 対 実際6,600円。差2.4％は仮置き値による）</t>
         </is>
       </c>
       <c r="O36" s="16" t="inlineStr">
@@ -6311,17 +6312,17 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>7-2</t>
         </is>
       </c>
       <c r="C37" s="16" t="inlineStr">
         <is>
-          <t>被保険者数・認定者数の推計</t>
+          <t>保険料算定のケース設定の確定</t>
         </is>
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>人口推計に年齢階層別の認定率を乗じる自然体推計</t>
+          <t>標準（低位・高位）、施設整備あり、制度改正の影響、基金活用、保険料据置の逆算</t>
         </is>
       </c>
       <c r="E37" s="16" t="inlineStr">
@@ -6346,33 +6347,33 @@
       </c>
       <c r="I37" s="17" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="J37" s="17" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="K37" s="20" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K37" s="18" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L37" s="19" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="M37" s="20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N37" s="16" t="inlineStr">
         <is>
-          <t>**算定シートに実績を投入済み。**第10期将来推計用推計人口（令和9〜11年）と、令和7年度の年齢階層別認定率（65〜74歳3.92％／75〜84歳18.72％／85歳以上71.63％）を入力した。85歳以上の認定率は令和6年度82.8％から11.2ポイント下がっている。**認定者数の見込みは令和9年度782人・令和10年度781人・令和11年度780人。見える化ワークシートの849人・850人・841人より8.4％低い。**見える化の基点は令和7年9月の865人（断層の直後）で、その後866人→794人へ減っていく動きを織り込んでいない。計画書には令和8年3月末の実績783人と接続する当方の系列を載せる。**なお見込量そのものへの影響は小さい。**見える化の見込量は第1号被保険者数×認定率×利用率の3段の掛け算で、利用率の分母は認定者数（在宅は認定者数から施設・居住系の利用者数を引いたもの）であり、認定率が高く出れば利用率が同じだけ低く出るため積は変わらない</t>
+          <t>**C1〜C6。引継ぎ時点の3ケースは基金の扱いのみで、仕様書が例示する施設整備・制度改正に対応していなかった**</t>
         </is>
       </c>
       <c r="O37" s="16" t="inlineStr">
         <is>
-          <t>**認定率をどの水準で置くか（令和7年度実績か、計上変更前の令和6年度水準か）。2-4の確認結果しだいで前提が変わる。**あわせて、認定率の分子に第2号被保険者の認定者を含むかを見える化の画面で確認する（確認事項No.125）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="P37" s="21" t="n"/>
@@ -6392,17 +6393,17 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>7-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="C38" s="16" t="inlineStr">
         <is>
-          <t>サービス見込量の推計</t>
+          <t>被保険者数・認定者数の推計</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>サービス種類別の利用者数・量・給付費</t>
+          <t>人口推計に年齢階層別の認定率を乗じる自然体推計</t>
         </is>
       </c>
       <c r="E38" s="16" t="inlineStr">
@@ -6432,70 +6433,38 @@
       </c>
       <c r="J38" s="17" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="K38" s="18" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K38" s="20" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="L38" s="19" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="M38" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N38" s="16" t="inlineStr">
         <is>
-          <t>**サービス別単価・見込量試算（04_算定・見込量・10シート）を作成し、算定シートの05・06に投入済み。**年報 様式2から29区分の令和3〜7年度の件数・単位数・費用額・給付費を取り出し（正規化後の合計は様式2の総計と全年度一致）、第1号被保険者1人当たりの利用率で令和9〜11年度を試算した。総給付費は3年計3,048,418千円、標準給付費は3,286,398千円（第9期見込の92.1％）。**分母の変動係数は第1号被保険者数1.63％に対し認定者数5.18％で、認定者ベースだと基準期間が断層をまたぐため10.5％低く出る。****9月15日に、量と利用者数の水準を見える化ワークシートの令和7年度実績（給付実績情報の回数・受給者数）に切り替えた。**国保連月報の実日数を回数に読み替えていたため、訪問介護で26％、訪問看護で32％、回数を少なく見ていた。給付費は年報 様式2 のまま（施設サービスは月報・見える化の額に特定入所者介護サービス費が乗っているため採らない）。**サービス見込量（11シート）と算定結果（成果品②の素材）にまとめた**</t>
+          <t>**算定シートに実績を投入済み。**第10期将来推計用推計人口（令和9〜11年）と、令和7年度の年齢階層別認定率（65〜74歳3.92％／75〜84歳18.72％／85歳以上71.63％）を入力した。85歳以上の認定率は令和6年度82.8％から11.2ポイント下がっている。**認定者数の見込みは令和9年度782人・令和10年度781人・令和11年度780人。見える化ワークシートの849人・850人・841人より8.4％低い。**見える化の基点は令和7年9月の865人（断層の直後）で、その後866人→794人へ減っていく動きを織り込んでいない。計画書には令和8年3月末の実績783人と接続する当方の系列を載せる。**なお見込量そのものへの影響は小さい。**見える化の見込量は第1号被保険者数×認定率×利用率の3段の掛け算で、利用率の分母は認定者数（在宅は認定者数から施設・居住系の利用者数を引いたもの）であり、認定率が高く出れば利用率が同じだけ低く出るため積は変わらない</t>
         </is>
       </c>
       <c r="O38" s="16" t="inlineStr">
         <is>
-          <t>**基準期間の切替を月報の前年同期比で判定する形に改めた。**①令和7年度の件数が3年平均から5％以上離れ、②令和8年度の前年同期比がその向きを裏づけるサービスだけ令和7年度単年にする。訪問看護・介護予防通所リハビリテーション・介護予防福祉用具貸与・介護予防支援・認知症対応型共同生活介護（介護・予防）の6件が該当。判定は check_base() が月報から再計算し、07_基準期間の判定 に載せている</t>
-        </is>
-      </c>
-      <c r="P38" s="17" t="inlineStr">
-        <is>
-          <t>**9月15日に、推計方法そのものをバックテストで検証した（推計方法のバックテスト・04_算定・見込量）。**令和5年度・令和6年度を起点に1〜2年先を予測し、実績との絶対誤差を給付費で加重して比べた。総給付費の誤差は、当方の方式（利用率・分母＝第1号被保険者数・窓3年）が3.31％で最も小さい。窓2年3.54％、分母を75歳以上とすると4.24％、直近年度の据え置き5.26％、全サービス一律の伸び5.28％、**大雪地区広域連合の手引きの偏り補正（φ0.5・上限±3％）は5.39％で一律に劣る。**同手引きの判定基準「一律より良いことを示せなければ補正しない」により採らない。分母を認定者数とすると6.39％で、起点年度によって2.20％〜9.60％と振れ幅が大きい</t>
-        </is>
-      </c>
-      <c r="Q38" s="17" t="inlineStr">
-        <is>
-          <t>**9月24日に、他町村の手引きの14段階で自己点検した（見込量算定の手引き適合点検・04_算定・見込量）。**済んでいなかった6段階（内的整合・季節性・施策反映・趨勢外の要因・記載事項・自己点検）を埋めた。**新たに分かったことが3つある。**①**単価は報酬改定のない年でも年率＋1.09％伸びており、改定のあった令和6年度の＋1.25％と差がない。**当方は単価を令和7年度で固定しているため、実績の趨勢（年率＋1.13％）で置くと標準給付費が3.43％・保険料が月額211円上がる。固定は過小側の置き方である。②**季節性は、居宅・地域密着型が年度で向きが逆になり再現しない。**施設（冬季が高い）と受給者計（冬季が低い）は再現するが差は2％前後で向きが逆であり相殺される。基準年度が完結年度のため補正は不要。③**施策反映は、当方の式で変数になっているのが第1号被保険者数だけであり、成果指標40件のうち目標値が確定しているものが0件であるため、現時点で反映できるものがない。**歯止めを先に定めた。**自己点検12項目を算定に組み込み、変異試験3件すべてで止まることを確かめた。**</t>
-        </is>
-      </c>
-      <c r="R38" s="17" t="inlineStr">
-        <is>
-          <t>**川崎町の方式（基準年度の要介護度別給付費に要介護度別の認定者数の伸びを乗じる）を小野町のデータで測った。**断層をまたがない令和5年度→令和6年度では誤差▲1.06％と全方式のなかで最も当たる一方、令和7年度を予測先に置く2通りでは▲14.66％・▲13.47％となり、3通りの平均では50設定中49位に落ちる。**令和6年度→令和7年度の認定者数は要介護4が0.755倍・要介護5が0.626倍で、給付費の実績が7.4％しか下がっていないのと合わない。**断層の原因が確認できるまでは採らない。解消すれば要介護度の構成の変化を織り込める点で当方より優れる可能性がある</t>
-        </is>
-      </c>
-      <c r="S38" s="17" t="inlineStr">
-        <is>
-          <t>**9月24日に、地域支援事業の「量」の見込みを追加した（介護保険法117条2項2号。11_地域支援事業の量）。**費用の見込みとは別の必須記載事項であり、第9期計画にもなかった。国保連月報から量を出せるのは介護予防・生活支援サービス事業の3事業だけで、**一般介護予防事業・包括的支援事業・任意事業の13事業は町の事業実績を要する**</t>
-        </is>
-      </c>
-      <c r="T38" s="17" t="inlineStr">
-        <is>
-          <t>**9月16日に、認知症基本法の点検にあわせて必要利用定員総数を追加した（介護保険法117条2項1号。10_必要利用定員総数）。**認知症対応型共同生活介護・地域密着型特定施設入居者生活介護・地域密着型介護老人福祉施設入所者生活介護の3サービスについて各年度の必要利用定員総数を定めることは**努力義務ではなく必須記載事項**であり、第9期計画にも当初の見込量算定にもなかった。**いずれも見込量に対し定員に余力があるため現行定員を維持する案（認知症対応型共同生活介護98人・地域密着型特養58人・地域密着型特定施設0人）**</t>
-        </is>
-      </c>
-      <c r="U38" s="17" t="inlineStr">
-        <is>
-          <t>**9月25日に、令和8年度の置き方を4通りで比べ、国保連月報で裏づけた（12_令和8年度の置き方）。**令和7年度の実績に対する比は、据え置き1.0000／令和6→令和7の動きを1年延長0.9255／当方の現行方式1.0171／**月報3か月の実績0.9598**。**当方の現行方式は実績より6.0％高い。**令和5〜7年度の3年平均が、下がり続けている系列を上に引いているため。令和8年度を月報の実績で置き人口で延ばす自然体推計ケースでは、総給付費の3年計が2,876,614千円（▲5.6％）、保険料が月額6,224円（100円未満切上げで6,300円）となる。**見える化システムの自然体推計と同じ構造であり、保険料のケース比較に加えた。**令和8年度は3か月分しかなく完結年度ではないため、残りの月の実績を見たうえで協議会にお諮りして確定する</t>
-        </is>
-      </c>
-      <c r="V38" s="17" t="inlineStr">
-        <is>
-          <t>**認定者数の見込みを算式に置き換えた。**従前は785／782／781／780とハードコードしていたが、記載の方法（年齢階層別認定率×将来推計人口）で計算すると**787／782／777／772**となり、令和10・11年度で4人・8人ずれていた。**令和6年度→令和7年度の認定率の変化を一定として延ばす置き方は採れない。**65〜74歳▲1.38ポイント・75〜84歳▲1.66ポイント・85歳以上▲11.20ポイントで、毎年加えると令和10年度に65〜74歳の認定率が負になり、令和11年度の認定者数は329人まで落ちる。断層がこの変化に入っているため</t>
-        </is>
-      </c>
-      <c r="W38" s="17" t="inlineStr">
-        <is>
-          <t>**報酬改定率（令和9年度）の確定。**あわせて、訪問介護の基準期間（3年平均だと令和9年度の見込件数が令和7年度実績の1.27倍。令和7年度単年なら月額▲47円）を協議会にお諮りする。**必要利用定員総数は、認知症対応型共同生活介護の定員が令和4年度71人から令和6年度98人へ増えた経緯と町外の方の利用割合を町に確認したうえで確定する。****あわせて、単価を令和7年度で固定していることを協議会にお諮りする（実績の趨勢で置くと月額＋211円）**</t>
-        </is>
-      </c>
+          <t>**認定率をどの水準で置くか（令和7年度実績か、計上変更前の令和6年度水準か）。2-4の確認結果しだいで前提が変わる。**あわせて、認定率の分子に第2号被保険者の認定者を含むかを見える化の画面で確認する（確認事項No.125）</t>
+        </is>
+      </c>
+      <c r="P38" s="21" t="n"/>
+      <c r="Q38" s="21" t="n"/>
+      <c r="R38" s="21" t="n"/>
+      <c r="S38" s="21" t="n"/>
+      <c r="T38" s="21" t="n"/>
+      <c r="U38" s="21" t="n"/>
+      <c r="V38" s="21" t="n"/>
+      <c r="W38" s="21" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
@@ -6505,17 +6474,17 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>7-5</t>
+          <t>7-4</t>
         </is>
       </c>
       <c r="C39" s="16" t="inlineStr">
         <is>
-          <t>見える化システムへの入力作業</t>
+          <t>サービス見込量の推計</t>
         </is>
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>将来推計機能への入力と総括表の出力。出力の分析だけでなく入力が業務に含まれる</t>
+          <t>サービス種類別の利用者数・量・給付費</t>
         </is>
       </c>
       <c r="E39" s="16" t="inlineStr">
@@ -6545,42 +6514,70 @@
       </c>
       <c r="J39" s="17" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="K39" s="22" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="K39" s="18" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L39" s="19" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="M39" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N39" s="16" t="inlineStr">
         <is>
-          <t>**川崎町・金ケ崎町の両ブランチを確認し、入力時の設定と落とし穴を整理した（見込量算定の方針と不足資料・04_算定・見込量）。**①介護保険事業状況報告の設定で令和8年度のチェックを外す（外さないと令和8年5月の1か月が年度として扱われる）②伸びは令和6年度→令和7年度（完結年度どうし）③1人1月あたり給付費は令和7年度④**施策反映の3画面は編集せず通過する（一度編集すると自然体推計に戻せない）**</t>
+          <t>**サービス別単価・見込量試算（04_算定・見込量・10シート）を作成し、算定シートの05・06に投入済み。**年報 様式2から29区分の令和3〜7年度の件数・単位数・費用額・給付費を取り出し（正規化後の合計は様式2の総計と全年度一致）、第1号被保険者1人当たりの利用率で令和9〜11年度を試算した。総給付費は3年計3,048,418千円、標準給付費は3,286,398千円（第9期見込の92.1％）。**分母の変動係数は第1号被保険者数1.63％に対し認定者数5.18％で、認定者ベースだと基準期間が断層をまたぐため10.5％低く出る。****9月15日に、量と利用者数の水準を見える化ワークシートの令和7年度実績（給付実績情報の回数・受給者数）に切り替えた。**国保連月報の実日数を回数に読み替えていたため、訪問介護で26％、訪問看護で32％、回数を少なく見ていた。給付費は年報 様式2 のまま（施設サービスは月報・見える化の額に特定入所者介護サービス費が乗っているため採らない）。**サービス見込量（11シート）と算定結果（成果品②の素材）にまとめた**</t>
         </is>
       </c>
       <c r="O39" s="16" t="inlineStr">
         <is>
-          <t>**9月24日に、受領したワークシートを1行ずつ読んで入力値を確定した（見える化システム入力値一覧・入力の手順。11_見える化出力依頼）。****入力の前に直す設定が2件ある。**①1人1月あたり給付費の実績値が令和8年度になっている。令和8年度の列は1か月分で、人数・回数・日数の非ゼロ36件のうち31件（86.1％）が整数である（令和6年度は46件中5件、令和7年度は40件中8件で、いずれも12分の1単位の小数）。令和7年度に切り替える。②認定率の伸びが令和6年度→令和7年度になっている。**見える化の認定者数は各年9月末の値で、令和7年度の865人は令和7年9月の断層の直後にあたる。**令和6年度937人は国保連の令和6年10月審査分と一致し、令和7年度865人と令和8年度865人は同値で令和8年度に実績がないことを示す。計上方法の確認が取れるまでこの伸びは使えない。**入力欄は、当方で用意できるものが28欄、町の資料が要るものが26欄。**町の資料が要るのは一般介護予防事業5欄（計5,305千円）、包括的支援事業・任意事業8欄（計29,335千円）、審査支払手数料等2欄（計531千円）、準備基金、令和8年度の当初予算など。**所得段階別加入割合13段階を入れると調整交付金見込交付割合が自動で出るため、当方の逆算値6.148％と突き合わせる**</t>
+          <t>**基準期間の切替を月報の前年同期比で判定する形に改めた。**①令和7年度の件数が3年平均から5％以上離れ、②令和8年度の前年同期比がその向きを裏づけるサービスだけ令和7年度単年にする。訪問看護・介護予防通所リハビリテーション・介護予防福祉用具貸与・介護予防支援・認知症対応型共同生活介護（介護・予防）の6件が該当。判定は check_base() が月報から再計算し、07_基準期間の判定 に載せている</t>
         </is>
       </c>
       <c r="P39" s="17" t="inlineStr">
         <is>
-          <t>**アカウント・権限・作業範囲・時期の確認（依頼票C5）。これが決まらないと総括表が出せず、対計画比・供給実現性の検証に進めない。****あわせて、令和7年8〜9月の認定者数の計上方法の確認が最優先。これが決まらないと認定率の伸びを置けない**</t>
-        </is>
-      </c>
-      <c r="Q39" s="21" t="n"/>
-      <c r="R39" s="21" t="n"/>
-      <c r="S39" s="21" t="n"/>
-      <c r="T39" s="21" t="n"/>
-      <c r="U39" s="21" t="n"/>
-      <c r="V39" s="21" t="n"/>
-      <c r="W39" s="21" t="n"/>
+          <t>**9月15日に、推計方法そのものをバックテストで検証した（推計方法のバックテスト・04_算定・見込量）。**令和5年度・令和6年度を起点に1〜2年先を予測し、実績との絶対誤差を給付費で加重して比べた。総給付費の誤差は、当方の方式（利用率・分母＝第1号被保険者数・窓3年）が3.31％で最も小さい。窓2年3.54％、分母を75歳以上とすると4.24％、直近年度の据え置き5.26％、全サービス一律の伸び5.28％、**大雪地区広域連合の手引きの偏り補正（φ0.5・上限±3％）は5.39％で一律に劣る。**同手引きの判定基準「一律より良いことを示せなければ補正しない」により採らない。分母を認定者数とすると6.39％で、起点年度によって2.20％〜9.60％と振れ幅が大きい</t>
+        </is>
+      </c>
+      <c r="Q39" s="17" t="inlineStr">
+        <is>
+          <t>**9月24日に、他町村の手引きの14段階で自己点検した（見込量算定の手引き適合点検・04_算定・見込量）。**済んでいなかった6段階（内的整合・季節性・施策反映・趨勢外の要因・記載事項・自己点検）を埋めた。**新たに分かったことが3つある。**①**単価は報酬改定のない年でも年率＋1.09％伸びており、改定のあった令和6年度の＋1.25％と差がない。**当方は単価を令和7年度で固定しているため、実績の趨勢（年率＋1.13％）で置くと標準給付費が3.43％・保険料が月額211円上がる。固定は過小側の置き方である。②**季節性は、居宅・地域密着型が年度で向きが逆になり再現しない。**施設（冬季が高い）と受給者計（冬季が低い）は再現するが差は2％前後で向きが逆であり相殺される。基準年度が完結年度のため補正は不要。③**施策反映は、当方の式で変数になっているのが第1号被保険者数だけであり、成果指標40件のうち目標値が確定しているものが0件であるため、現時点で反映できるものがない。**歯止めを先に定めた。**自己点検12項目を算定に組み込み、変異試験3件すべてで止まることを確かめた。**</t>
+        </is>
+      </c>
+      <c r="R39" s="17" t="inlineStr">
+        <is>
+          <t>**川崎町の方式（基準年度の要介護度別給付費に要介護度別の認定者数の伸びを乗じる）を小野町のデータで測った。**断層をまたがない令和5年度→令和6年度では誤差▲1.06％と全方式のなかで最も当たる一方、令和7年度を予測先に置く2通りでは▲14.66％・▲13.47％となり、3通りの平均では50設定中49位に落ちる。**令和6年度→令和7年度の認定者数は要介護4が0.755倍・要介護5が0.626倍で、給付費の実績が7.4％しか下がっていないのと合わない。**断層の原因が確認できるまでは採らない。解消すれば要介護度の構成の変化を織り込める点で当方より優れる可能性がある</t>
+        </is>
+      </c>
+      <c r="S39" s="17" t="inlineStr">
+        <is>
+          <t>**9月24日に、地域支援事業の「量」の見込みを追加した（介護保険法117条2項2号。11_地域支援事業の量）。**費用の見込みとは別の必須記載事項であり、第9期計画にもなかった。国保連月報から量を出せるのは介護予防・生活支援サービス事業の3事業だけで、**一般介護予防事業・包括的支援事業・任意事業の13事業は町の事業実績を要する**</t>
+        </is>
+      </c>
+      <c r="T39" s="17" t="inlineStr">
+        <is>
+          <t>**9月16日に、認知症基本法の点検にあわせて必要利用定員総数を追加した（介護保険法117条2項1号。10_必要利用定員総数）。**認知症対応型共同生活介護・地域密着型特定施設入居者生活介護・地域密着型介護老人福祉施設入所者生活介護の3サービスについて各年度の必要利用定員総数を定めることは**努力義務ではなく必須記載事項**であり、第9期計画にも当初の見込量算定にもなかった。**いずれも見込量に対し定員に余力があるため現行定員を維持する案（認知症対応型共同生活介護98人・地域密着型特養58人・地域密着型特定施設0人）**</t>
+        </is>
+      </c>
+      <c r="U39" s="17" t="inlineStr">
+        <is>
+          <t>**9月25日に、令和8年度の置き方を4通りで比べ、国保連月報で裏づけた（12_令和8年度の置き方）。**令和7年度の実績に対する比は、据え置き1.0000／令和6→令和7の動きを1年延長0.9255／当方の現行方式1.0171／**月報3か月の実績0.9598**。**当方の現行方式は実績より6.0％高い。**令和5〜7年度の3年平均が、下がり続けている系列を上に引いているため。**9月25日に、この自然体推計ケースを標準ケースに切り替えた（素案 第5版、見込量の算定結果 令和8年9月25日版）。**令和8年度を月報の実績で置き、そこから人口で延ばす。総給付費の3年計は2,876,614千円（従前の方式から▲5.6％）、標準給付費3,101,160千円、保険料は月額6,224円（100円未満切上げで6,300円。第9期の6,600円から▲376円・▲5.7％）。**見える化システムの自然体推計と同じ構造であり、システムの出力と素案の数値が突き合う。**従前の方式（3年平均の伸び）によるケースは月額6,570円で、比較のケースとして残した。令和8年度は3か月分しかなく完結年度ではないため、残りの月の実績を見たうえで協議会にお諮りして確定する</t>
+        </is>
+      </c>
+      <c r="V39" s="17" t="inlineStr">
+        <is>
+          <t>**認定者数の見込みを算式に置き換えた。**従前は785／782／781／780とハードコードしていたが、記載の方法（年齢階層別認定率×将来推計人口）で計算すると**787／782／777／772**となり、令和10・11年度で4人・8人ずれていた。**令和6年度→令和7年度の認定率の変化を一定として延ばす置き方は採れない。**65〜74歳▲1.38ポイント・75〜84歳▲1.66ポイント・85歳以上▲11.20ポイントで、毎年加えると令和10年度に65〜74歳の認定率が負になり、令和11年度の認定者数は329人まで落ちる。断層がこの変化に入っているため</t>
+        </is>
+      </c>
+      <c r="W39" s="17" t="inlineStr">
+        <is>
+          <t>**報酬改定率（令和9年度）の確定。**あわせて、訪問介護の基準期間（3年平均だと令和9年度の見込件数が令和7年度実績の1.27倍。令和7年度単年なら月額▲47円）を協議会にお諮りする。**必要利用定員総数は、認知症対応型共同生活介護の定員が令和4年度71人から令和6年度98人へ増えた経緯と町外の方の利用割合を町に確認したうえで確定する。****あわせて、単価を令和7年度で固定していることを協議会にお諮りする（実績の趨勢で置くと月額＋211円）**</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
@@ -6590,17 +6587,17 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>7-6</t>
+          <t>7-5</t>
         </is>
       </c>
       <c r="C40" s="16" t="inlineStr">
         <is>
-          <t>保険料のケース別算定</t>
+          <t>見える化システムへの入力作業</t>
         </is>
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>ケースC1〜C6ごとの保険料基準額の算定</t>
+          <t>将来推計機能への入力と総括表の出力。出力の分析だけでなく入力が業務に含まれる</t>
         </is>
       </c>
       <c r="E40" s="16" t="inlineStr">
@@ -6625,36 +6622,40 @@
       </c>
       <c r="I40" s="17" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="J40" s="17" t="inlineStr">
+        <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="J40" s="17" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="K40" s="20" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="K40" s="22" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="L40" s="19" t="n">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="M40" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N40" s="16" t="inlineStr">
         <is>
-          <t>**所得段階別被保険者数（13段階）、小野町が定める保険料率（第1〜3段階は0.285／0.486／0.685で国の標準より低い）、収納率99.35％、基金保有額12,000千円を投入済み。地域支援事業費は年報 様式4 の令和6年度決算63,916千円（3年計191,749千円）を事業別に割り付けて投入した。総合事業の内訳は国保連月報の総合事業コード（A2・A6・AF）による。**7-4の見込量で算式を通したところ、保険料基準額は月額6,570円（基金取崩なし）、6,467円（保有額12,000千円を全額取崩）、6,270円（第9期と同じ35,000千円を取崩）となった。第9期は6,600円。負担割合が24％になると6,867円。**調整交付金の見込交付割合は第9期計画の公表値から逆算して6.148％。標準の5％ではない（小野町は後期高齢者加入割合が高く低所得層が厚い）**※ 逆算される調整交付金見込額219,272千円は基数の取り方によらない。見える化システムは標準給付費見込額のみを基数とするため6.148％、総合事業費を含めると5.963％となる（本件は前者にそろえた）</t>
+          <t>**川崎町・金ケ崎町の両ブランチを確認し、入力時の設定と落とし穴を整理した（見込量算定の方針と不足資料・04_算定・見込量）。**①介護保険事業状況報告の設定で令和8年度のチェックを外す（外さないと令和8年5月の1か月が年度として扱われる）②伸びは令和6年度→令和7年度（完結年度どうし）③1人1月あたり給付費は令和7年度④**施策反映の3画面は編集せず通過する（一度編集すると自然体推計に戻せない）**</t>
         </is>
       </c>
       <c r="O40" s="16" t="inlineStr">
         <is>
-          <t>**一般介護予防事業費と包括的支援事業・任意事業費の事業別内訳、令和7年度の決算額（年報が未入力）、調整交付金見込額、第10期の第1号被保険者負担割合。あわせて、第9期が見込んだ基金取崩35,000千円に対し基金保有額が12,000千円しかない点の確認が要る（しかも年報の残高の系列に矛盾がある）**</t>
-        </is>
-      </c>
-      <c r="P40" s="21" t="n"/>
+          <t>**9月24日に、受領したワークシートを1行ずつ読んで入力値を確定した（見える化システム入力値一覧・入力の手順。11_見える化出力依頼）。****入力の前に直す設定が2件ある。**①1人1月あたり給付費の実績値が令和8年度になっている。令和8年度の列は1か月分で、人数・回数・日数の非ゼロ36件のうち31件（86.1％）が整数である（令和6年度は46件中5件、令和7年度は40件中8件で、いずれも12分の1単位の小数）。令和7年度に切り替える。②認定率の伸びが令和6年度→令和7年度になっている。**見える化の認定者数は各年9月末の値で、令和7年度の865人は令和7年9月の断層の直後にあたる。**令和6年度937人は国保連の令和6年10月審査分と一致し、令和7年度865人と令和8年度865人は同値で令和8年度に実績がないことを示す。計上方法の確認が取れるまでこの伸びは使えない。**入力欄は、当方で用意できるものが28欄、町の資料が要るものが26欄。**町の資料が要るのは一般介護予防事業5欄（計5,305千円）、包括的支援事業・任意事業8欄（計29,335千円）、審査支払手数料等2欄（計531千円）、準備基金、令和8年度の当初予算など。**所得段階別加入割合13段階を入れると調整交付金見込交付割合が自動で出るため、当方の逆算値6.148％と突き合わせる**</t>
+        </is>
+      </c>
+      <c r="P40" s="17" t="inlineStr">
+        <is>
+          <t>**アカウント・権限・作業範囲・時期の確認（依頼票C5）。これが決まらないと総括表が出せず、対計画比・供給実現性の検証に進めない。****あわせて、令和7年8〜9月の認定者数の計上方法の確認が最優先。これが決まらないと認定率の伸びを置けない**</t>
+        </is>
+      </c>
       <c r="Q40" s="21" t="n"/>
       <c r="R40" s="21" t="n"/>
       <c r="S40" s="21" t="n"/>
@@ -6671,32 +6672,32 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>7-6</t>
         </is>
       </c>
       <c r="C41" s="16" t="inlineStr">
         <is>
-          <t>サービス見込量推計結果報告書の作成</t>
+          <t>保険料のケース別算定</t>
         </is>
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>成果品②の本体</t>
+          <t>ケースC1〜C6ごとの保険料基準額の算定</t>
         </is>
       </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
-          <t>B9 成果品の納品</t>
+          <t>B5 事業量推計・保険料算出・介護財政</t>
         </is>
       </c>
       <c r="F41" s="17" t="inlineStr">
         <is>
-          <t>仕様書4 成果品②</t>
+          <t>仕様書4(2)</t>
         </is>
       </c>
       <c r="G41" s="16" t="inlineStr">
         <is>
-          <t>【成果品②】（2）サービス見込量推計結果報告書　※データ（CD-R）1部、冊子（簡易製本）3部</t>
+          <t>【4(2)】サービス事業量推計、保険料の算出、介護財政の見通しの検討・調整。「見える化」システムを活用したサービス見込量を推計及び保険料の算出を行うこと。（「見える化」システムへの入力作業を含む。）なお、算定にあたっては、新たに介護施設を整備する場合や制度改正により条件が変わる場合等、様々なケースで勘案する必要があるため、想定されるケースごとに保険料の算定を行うものとする。</t>
         </is>
       </c>
       <c r="H41" s="17" t="inlineStr">
@@ -6706,33 +6707,33 @@
       </c>
       <c r="I41" s="17" t="inlineStr">
         <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="J41" s="17" t="inlineStr">
+        <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="J41" s="17" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
       <c r="K41" s="20" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
       <c r="L41" s="19" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M41" s="20" t="n">
         <v>4</v>
       </c>
       <c r="N41" s="16" t="inlineStr">
         <is>
-          <t>**サービス見込量の算定結果（04_算定・見込量・10章・11表）を作成した。**算定の方法、基準期間の置き方、サービス見込量、給付費と標準給付費、地域支援事業費、供給実現性（定員との突合）、保険料の試算、据え置いた前提と動く幅、町への確認事項までを収めている</t>
+          <t>**所得段階別被保険者数（13段階）、小野町が定める保険料率（第1〜3段階は0.285／0.486／0.685で国の標準より低い）、収納率99.35％、基金保有額12,000千円を投入済み。地域支援事業費は年報 様式4 の令和6年度決算63,916千円（3年計191,749千円）を事業別に割り付けて投入した。総合事業の内訳は国保連月報の総合事業コード（A2・A6・AF）による。****9月25日に標準ケースを自然体推計に切り替えた結果、保険料基準額は月額6,224円（基金取崩なし）、6,121円（保有額12,000千円を全額取崩）、5,924円（第9期と同じ35,000千円を取崩）となった。**第9期は6,600円。負担割合が24％になると6,505円。従前の方式（令和5〜7年度の3年平均の伸び）では6,570円であり、比較のケースとして残している。**調整交付金の見込交付割合は第9期計画の公表値から逆算して6.148％。標準の5％ではない（小野町は後期高齢者加入割合が高く低所得層が厚い）**※ 逆算される調整交付金見込額219,272千円は基数の取り方によらない。見える化システムは標準給付費見込額のみを基数とするため6.148％、総合事業費を含めると5.963％となる（本件は前者にそろえた）</t>
         </is>
       </c>
       <c r="O41" s="16" t="inlineStr">
         <is>
-          <t>**報酬改定率と第1号被保険者負担割合が確定したら数値を差し替える。**あわせて、協議会での議論を踏まえた記述の追加</t>
+          <t>**一般介護予防事業費と包括的支援事業・任意事業費の事業別内訳、令和7年度の決算額（年報が未入力）、調整交付金見込額、第10期の第1号被保険者負担割合。あわせて、第9期が見込んだ基金取崩35,000千円に対し基金保有額が12,000千円しかない点の確認が要る（しかも年報の残高の系列に矛盾がある）**</t>
         </is>
       </c>
       <c r="P41" s="21" t="n"/>
@@ -6752,17 +6753,17 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>7-7</t>
         </is>
       </c>
       <c r="C42" s="16" t="inlineStr">
         <is>
-          <t>成果品②の製本・納品</t>
+          <t>サービス見込量推計結果報告書の作成</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>データCD-R1部＋冊子（簡易製本）3部</t>
+          <t>成果品②の本体</t>
         </is>
       </c>
       <c r="E42" s="16" t="inlineStr">
@@ -6787,33 +6788,33 @@
       </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="J42" s="17" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="K42" s="24" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="K42" s="20" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="L42" s="19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M42" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N42" s="16" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**サービス見込量の算定結果（04_算定・見込量・10章・11表）を作成した。**算定の方法、基準期間の置き方、サービス見込量、給付費と標準給付費、地域支援事業費、供給実現性（定員との突合）、保険料の試算、据え置いた前提と動く幅、町への確認事項までを収めている</t>
         </is>
       </c>
       <c r="O42" s="16" t="inlineStr">
         <is>
-          <t>報告書の確定</t>
+          <t>**報酬改定率と第1号被保険者負担割合が確定したら数値を差し替える。**あわせて、協議会での議論を踏まえた記述の追加</t>
         </is>
       </c>
       <c r="P42" s="21" t="n"/>
@@ -6828,38 +6829,37 @@
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P7 推計・算定</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>8-1</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="C43" s="16" t="inlineStr">
         <is>
-          <t>素案の作成</t>
+          <t>成果品②の製本・納品</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>骨子案を踏まえた計画素案。12施策の本文</t>
+          <t>データCD-R1部＋冊子（簡易製本）3部</t>
         </is>
       </c>
       <c r="E43" s="16" t="inlineStr">
         <is>
-          <t>B6 骨子案・素案の作成</t>
+          <t>B9 成果品の納品</t>
         </is>
       </c>
       <c r="F43" s="17" t="inlineStr">
         <is>
-          <t>仕様書4(3)・成果品④</t>
+          <t>仕様書4 成果品②</t>
         </is>
       </c>
       <c r="G43" s="16" t="inlineStr">
         <is>
-          <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。
-【成果品④】（4）小野町高齢者保健福祉計画・第10期介護保険事業計画素案　※データ（CD-R）1部、冊子（簡易製本）3部</t>
+          <t>【成果品②】（2）サービス見込量推計結果報告書　※データ（CD-R）1部、冊子（簡易製本）3部</t>
         </is>
       </c>
       <c r="H43" s="17" t="inlineStr">
@@ -6869,40 +6869,36 @@
       </c>
       <c r="I43" s="17" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="J43" s="17" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="K43" s="20" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="K43" s="24" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="L43" s="19" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M43" s="20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N43" s="16" t="inlineStr">
         <is>
-          <t>**第4版（5章＋資料編・74表）。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定158箇所のうち61箇所が解消し97箇所となった。**第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量・給付費・標準給付費・地域支援事業費の事業別内訳・保険料基準額（月額6,570円）を入れた</t>
+          <t>―</t>
         </is>
       </c>
       <c r="O43" s="16" t="inlineStr">
         <is>
-          <t>**9月24日に、受託者が算定すべき未確定箇所をすべて解消した。**所得段階別保険料率を13段階すべてについて算定し（乗率・年額・被保険者数・構成比）、必要利用定員総数・地域支援事業の量・認知症高齢者数を加えた。**未確定は158箇所→94箇所となり、【算定後に記載】は0件になった。****あわせて数値の誤りを2件正した。**①所得第2段階の乗率を0.485としていたが、年報 様式1 所得段階別および第9期の年額38,500円（＝0.486×79,200円）から0.486が正しい（素案・骨子案・給付費等分析の3点）。②所得第1〜3段階の割合を28％としていたが、1,094人÷3,443人で31.8％が正しい。**第2章1の人口（見える化の将来推計・暦年）と第2章6の被保険者数（第10期将来推計用推計人口・年度）が別系列であることを注記した。**従前の注は「保険料算定との整合のため見える化の推計を用いる」と書いていたが、保険料算定は後者を用いており誤りであった</t>
-        </is>
-      </c>
-      <c r="P43" s="17" t="inlineStr">
-        <is>
-          <t>**残る94箇所の内訳は、協議会で設定する目標値39、町データ待ち39、町・国の決定12、見える化出力4。****受託者の算定によるものは残っていない。**町データ待ちの筆頭は成果指標の現状値、一般介護予防事業費・包括的支援事業・任意事業費の事業別内訳、地域支援事業の量（13事業）、認知症対応型共同生活介護の増床の経緯**</t>
-        </is>
-      </c>
+          <t>報告書の確定</t>
+        </is>
+      </c>
+      <c r="P43" s="21" t="n"/>
       <c r="Q43" s="21" t="n"/>
       <c r="R43" s="21" t="n"/>
       <c r="S43" s="21" t="n"/>
@@ -6919,17 +6915,17 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
         <is>
-          <t>成果指標の目標値案の作成</t>
+          <t>素案の作成</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>40指標の目標値案と根拠の型</t>
+          <t>骨子案を踏まえた計画素案。12施策の本文</t>
         </is>
       </c>
       <c r="E44" s="16" t="inlineStr">
@@ -6939,12 +6935,13 @@
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>仕様書4(3)</t>
+          <t>仕様書4(3)・成果品④</t>
         </is>
       </c>
       <c r="G44" s="16" t="inlineStr">
         <is>
-          <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。</t>
+          <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。
+【成果品④】（4）小野町高齢者保健福祉計画・第10期介護保険事業計画素案　※データ（CD-R）1部、冊子（簡易製本）3部</t>
         </is>
       </c>
       <c r="H44" s="17" t="inlineStr">
@@ -6959,31 +6956,35 @@
       </c>
       <c r="J44" s="17" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="K44" s="18" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="K44" s="20" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="L44" s="19" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="M44" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N44" s="16" t="inlineStr">
         <is>
-          <t>**成果指標目標値案（03_計画素案・40指標）。**現状値が未受領の20指標は算定規則として案を置いた</t>
+          <t>**第5版（5章＋資料編・74表）。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定158箇所のうち61箇所が解消し97箇所となった。**第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量・給付費・標準給付費・地域支援事業費の事業別内訳・保険料基準額を入れた。**第5版（9月25日）で令和8年度の置き方を自然体推計に改め、保険料基準額は月額6,570円から6,224円（切上げ6,300円）となった。**従前の方式による算定は比較のケースとして残している。**第5章2の進行管理に、保険者機能強化推進交付金等の評価結果を点検項目として加えた**（評価結果を外部の議論の場で検証すること自体が評価指標の要件であるため）</t>
         </is>
       </c>
       <c r="O44" s="16" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="P44" s="21" t="n"/>
+          <t>**9月24日に、受託者が算定すべき未確定箇所をすべて解消した。**所得段階別保険料率を13段階すべてについて算定し（乗率・年額・被保険者数・構成比）、必要利用定員総数・地域支援事業の量・認知症高齢者数を加えた。**未確定は158箇所→94箇所となり、【算定後に記載】は0件になった。****あわせて数値の誤りを2件正した。**①所得第2段階の乗率を0.485としていたが、年報 様式1 所得段階別および第9期の年額38,500円（＝0.486×79,200円）から0.486が正しい（素案・骨子案・給付費等分析の3点）。②所得第1〜3段階の割合を28％としていたが、1,094人÷3,443人で31.8％が正しい。**第2章1の人口（見える化の将来推計・暦年）と第2章6の被保険者数（第10期将来推計用推計人口・年度）が別系列であることを注記した。**従前の注は「保険料算定との整合のため見える化の推計を用いる」と書いていたが、保険料算定は後者を用いており誤りであった</t>
+        </is>
+      </c>
+      <c r="P44" s="17" t="inlineStr">
+        <is>
+          <t>**残る94箇所の内訳は、協議会で設定する目標値39、町データ待ち39、町・国の決定12、見える化出力4。****受託者の算定によるものは残っていない。**町データ待ちの筆頭は成果指標の現状値、一般介護予防事業費・包括的支援事業・任意事業費の事業別内訳、地域支援事業の量（13事業）、認知症対応型共同生活介護の増床の経緯**</t>
+        </is>
+      </c>
       <c r="Q44" s="21" t="n"/>
       <c r="R44" s="21" t="n"/>
       <c r="S44" s="21" t="n"/>
@@ -7000,32 +7001,32 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>8-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="C45" s="16" t="inlineStr">
         <is>
-          <t>認知症施策推進基本計画の包含方針</t>
+          <t>成果指標の目標値案の作成</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>基本的施策12項目との対応表、包含の形式</t>
+          <t>40指標の目標値案と根拠の型</t>
         </is>
       </c>
       <c r="E45" s="16" t="inlineStr">
         <is>
-          <t>B10 業務管理・計画の基本的な考え方</t>
+          <t>B6 骨子案・素案の作成</t>
         </is>
       </c>
       <c r="F45" s="17" t="inlineStr">
         <is>
-          <t>仕様書2(3)</t>
+          <t>仕様書4(3)</t>
         </is>
       </c>
       <c r="G45" s="16" t="inlineStr">
         <is>
-          <t>【2(3)】国の「認知症施策推進基本計画」に基づく市町村計画も包含する計画とする。</t>
+          <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。</t>
         </is>
       </c>
       <c r="H45" s="17" t="inlineStr">
@@ -7052,16 +7053,16 @@
         <v>100</v>
       </c>
       <c r="M45" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N45" s="16" t="inlineStr">
         <is>
-          <t>計画策定業務設計書 第1章（02_キックオフ・業務計画）。分散＋対応表方式を提案。**9月16日に認知症基本法の条文により市町村計画の根拠を第13条第1項（努力義務）、調和規定を第2項、策定手続（意見聴取・公表・評価・5年ごとの検討）を第3項が準用する第12条第3〜7項と確定し、素案に反映した（認知症基本法への対応の点検・03_計画素案）。****施策の柱を認知症施策推進大綱の5本柱から法の基本的施策（第14〜21条）に組み替え、大綱では落ちていた若年性認知症・移動のための交通手段の確保・消費生活被害の防止・孤立の防止を追加した。**北塩原村の法定記載事項チェックと川崎町の骨子案を参照している</t>
+          <t>**成果指標目標値案（03_計画素案・40指標）。**現状値が未受領の20指標は算定規則として案を置いた</t>
         </is>
       </c>
       <c r="O45" s="16" t="inlineStr">
         <is>
-          <t>**認知症の人及びその家族等の意見をどう聴くか（同法13条3項→12条3項）。記述の追加では埋まらず策定過程に関わるため、協議会の委員構成を確認したうえで家族会・認知症カフェでの意見聴取の機会を設けるかを町と協議する。**あわせて福島県の認知症施策推進計画の策定状況、町の意思決定（方式A／B）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="P45" s="21" t="n"/>
@@ -7081,32 +7082,32 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>8-4</t>
+          <t>8-3</t>
         </is>
       </c>
       <c r="C46" s="16" t="inlineStr">
         <is>
-          <t>見込量・保険料・成果指標の反映</t>
+          <t>認知症施策推進基本計画の包含方針</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>素案の未確定156箇所の解消</t>
+          <t>基本的施策12項目との対応表、包含の形式</t>
         </is>
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
-          <t>B6 骨子案・素案の作成</t>
+          <t>B10 業務管理・計画の基本的な考え方</t>
         </is>
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>仕様書4(3)</t>
+          <t>仕様書2(3)</t>
         </is>
       </c>
       <c r="G46" s="16" t="inlineStr">
         <is>
-          <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。</t>
+          <t>【2(3)】国の「認知症施策推進基本計画」に基づく市町村計画も包含する計画とする。</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
@@ -7116,33 +7117,33 @@
       </c>
       <c r="I46" s="17" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="J46" s="17" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="K46" s="24" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K46" s="18" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L46" s="19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M46" s="20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N46" s="16" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>計画策定業務設計書 第1章（02_キックオフ・業務計画）。分散＋対応表方式を提案。**9月16日に認知症基本法の条文により市町村計画の根拠を第13条第1項（努力義務）、調和規定を第2項、策定手続（意見聴取・公表・評価・5年ごとの検討）を第3項が準用する第12条第3〜7項と確定し、素案に反映した（認知症基本法への対応の点検・03_計画素案）。****施策の柱を認知症施策推進大綱の5本柱から法の基本的施策（第14〜21条）に組み替え、大綱では落ちていた若年性認知症・移動のための交通手段の確保・消費生活被害の防止・孤立の防止を追加した。**北塩原村の法定記載事項チェックと川崎町の骨子案を参照している</t>
         </is>
       </c>
       <c r="O46" s="16" t="inlineStr">
         <is>
-          <t>**P7の完了、町データの受領**</t>
+          <t>**認知症の人及びその家族等の意見をどう聴くか（同法13条3項→12条3項）。記述の追加では埋まらず策定過程に関わるため、協議会の委員構成を確認したうえで家族会・認知症カフェでの意見聴取の機会を設けるかを町と協議する。**あわせて福島県の認知症施策推進計画の策定状況、町の意思決定（方式A／B）</t>
         </is>
       </c>
       <c r="P46" s="21" t="n"/>
@@ -7162,17 +7163,17 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>8-5</t>
+          <t>8-4</t>
         </is>
       </c>
       <c r="C47" s="16" t="inlineStr">
         <is>
-          <t>素案の協議（協議会）</t>
+          <t>見込量・保険料・成果指標の反映</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>素案の内容の合意</t>
+          <t>素案の未確定156箇所の解消</t>
         </is>
       </c>
       <c r="E47" s="16" t="inlineStr">
@@ -7182,23 +7183,22 @@
       </c>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>仕様書4(3)・4(5)</t>
+          <t>仕様書4(3)</t>
         </is>
       </c>
       <c r="G47" s="16" t="inlineStr">
         <is>
-          <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。
-【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
+          <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。</t>
         </is>
       </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="I47" s="17" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="J47" s="17" t="inlineStr">
@@ -7215,7 +7215,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N47" s="16" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="O47" s="16" t="inlineStr">
         <is>
-          <t>協議会の開催時期</t>
+          <t>**P7の完了、町データの受領**</t>
         </is>
       </c>
       <c r="P47" s="21" t="n"/>
@@ -7244,47 +7244,48 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>8-6</t>
+          <t>8-5</t>
         </is>
       </c>
       <c r="C48" s="16" t="inlineStr">
         <is>
-          <t>成果品④の製本・納品</t>
+          <t>素案の協議（協議会）</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>データCD-R1部＋冊子（簡易製本）3部</t>
+          <t>素案の内容の合意</t>
         </is>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
-          <t>B9 成果品の納品</t>
+          <t>B6 骨子案・素案の作成</t>
         </is>
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>仕様書4 成果品④</t>
+          <t>仕様書4(3)・4(5)</t>
         </is>
       </c>
       <c r="G48" s="16" t="inlineStr">
         <is>
-          <t>【成果品④】（4）小野町高齢者保健福祉計画・第10期介護保険事業計画素案　※データ（CD-R）1部、冊子（簡易製本）3部</t>
+          <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。
+【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="I48" s="17" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="J48" s="17" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="K48" s="24" t="inlineStr">
@@ -7296,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N48" s="16" t="inlineStr">
         <is>
@@ -7305,7 +7306,7 @@
       </c>
       <c r="O48" s="16" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>協議会の開催時期</t>
         </is>
       </c>
       <c r="P48" s="21" t="n"/>
@@ -7320,57 +7321,57 @@
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>P9 意見聴取</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>8-6</t>
         </is>
       </c>
       <c r="C49" s="16" t="inlineStr">
         <is>
-          <t>協議会の開催回数・時期の確定</t>
+          <t>成果品④の製本・納品</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>小野町高齢者福祉サービス推進協議会</t>
+          <t>データCD-R1部＋冊子（簡易製本）3部</t>
         </is>
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
-          <t>B8 協議会・パブリックコメントの支援</t>
+          <t>B9 成果品の納品</t>
         </is>
       </c>
       <c r="F49" s="17" t="inlineStr">
         <is>
-          <t>仕様書4(5)</t>
+          <t>仕様書4 成果品④</t>
         </is>
       </c>
       <c r="G49" s="16" t="inlineStr">
         <is>
-          <t>【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
+          <t>【成果品④】（4）小野町高齢者保健福祉計画・第10期介護保険事業計画素案　※データ（CD-R）1部、冊子（簡易製本）3部</t>
         </is>
       </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="I49" s="17" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="J49" s="17" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="K49" s="22" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="K49" s="24" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="L49" s="19" t="n">
@@ -7381,12 +7382,12 @@
       </c>
       <c r="N49" s="16" t="inlineStr">
         <is>
-          <t>**仕様書に回数の指定がない。**受託者案は4回</t>
+          <t>―</t>
         </is>
       </c>
       <c r="O49" s="16" t="inlineStr">
         <is>
-          <t>**町との協議（依頼票C4）。これが決まらないと工程が引けない**</t>
+          <t>素案の確定</t>
         </is>
       </c>
       <c r="P49" s="21" t="n"/>
@@ -7406,17 +7407,17 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
         <is>
-          <t>協議会 第1回（第9期の評価・調査結果）</t>
+          <t>協議会の開催回数・時期の確定</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>評価と調査結果の報告</t>
+          <t>小野町高齢者福祉サービス推進協議会</t>
         </is>
       </c>
       <c r="E50" s="16" t="inlineStr">
@@ -7436,7 +7437,7 @@
       </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>町</t>
         </is>
       </c>
       <c r="I50" s="17" t="inlineStr">
@@ -7446,7 +7447,7 @@
       </c>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K50" s="22" t="inlineStr">
@@ -7455,19 +7456,19 @@
         </is>
       </c>
       <c r="L50" s="19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M50" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N50" s="16" t="inlineStr">
         <is>
-          <t>**資料は作成済み（08_協議会資料・42表）**</t>
+          <t>**仕様書に回数の指定がない。**受託者案は4回</t>
         </is>
       </c>
       <c r="O50" s="16" t="inlineStr">
         <is>
-          <t>**開催日が未定**</t>
+          <t>**町との協議（依頼票C4）。これが決まらないと工程が引けない**</t>
         </is>
       </c>
       <c r="P50" s="21" t="n"/>
@@ -7487,17 +7488,17 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C51" s="16" t="inlineStr">
         <is>
-          <t>協議会 第2回（骨子案・見込量・保険料・成果指標）</t>
+          <t>協議会 第1回（第9期の評価・調査結果）</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>計画の骨格の合意</t>
+          <t>評価と調査結果の報告</t>
         </is>
       </c>
       <c r="E51" s="16" t="inlineStr">
@@ -7522,33 +7523,33 @@
       </c>
       <c r="I51" s="17" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="J51" s="17" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="K51" s="24" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K51" s="22" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="L51" s="19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M51" s="20" t="n">
         <v>2</v>
       </c>
       <c r="N51" s="16" t="inlineStr">
         <is>
-          <t>骨子案第3版・成果指標目標値案は作成済み</t>
+          <t>**資料は作成済み（08_協議会資料・42表）**</t>
         </is>
       </c>
       <c r="O51" s="16" t="inlineStr">
         <is>
-          <t>P7の完了、開催日の確定</t>
+          <t>**開催日が未定**</t>
         </is>
       </c>
       <c r="P51" s="21" t="n"/>
@@ -7568,17 +7569,17 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>9-4</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="C52" s="16" t="inlineStr">
         <is>
-          <t>協議会 第3回（素案）</t>
+          <t>協議会 第2回（骨子案・見込量・保険料・成果指標）</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>素案の合意</t>
+          <t>計画の骨格の合意</t>
         </is>
       </c>
       <c r="E52" s="16" t="inlineStr">
@@ -7603,12 +7604,12 @@
       </c>
       <c r="I52" s="17" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="K52" s="24" t="inlineStr">
@@ -7624,12 +7625,12 @@
       </c>
       <c r="N52" s="16" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>骨子案第3版・成果指標目標値案は作成済み</t>
         </is>
       </c>
       <c r="O52" s="16" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>P7の完了、開催日の確定</t>
         </is>
       </c>
       <c r="P52" s="21" t="n"/>
@@ -7649,17 +7650,17 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>9-4</t>
         </is>
       </c>
       <c r="C53" s="16" t="inlineStr">
         <is>
-          <t>パブリックコメントの様式作成</t>
+          <t>協議会 第3回（素案）</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>実施要領、意見提出様式、意見と町の考え方の対応表</t>
+          <t>素案の合意</t>
         </is>
       </c>
       <c r="E53" s="16" t="inlineStr">
@@ -7679,38 +7680,38 @@
       </c>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="I53" s="17" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="J53" s="17" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="K53" s="18" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="K53" s="24" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="L53" s="19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M53" s="20" t="n">
         <v>2</v>
       </c>
       <c r="N53" s="16" t="inlineStr">
         <is>
-          <t>計画策定業務設計書 第4章（02_キックオフ・業務計画）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="O53" s="16" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>素案の確定</t>
         </is>
       </c>
       <c r="P53" s="21" t="n"/>
@@ -7730,17 +7731,17 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C54" s="16" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>パブリックコメントの様式作成</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>意見提出期間1か月</t>
+          <t>実施要領、意見提出様式、意見と町の考え方の対応表</t>
         </is>
       </c>
       <c r="E54" s="16" t="inlineStr">
@@ -7760,38 +7761,38 @@
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="J54" s="17" t="inlineStr">
         <is>
-          <t>2027-01</t>
-        </is>
-      </c>
-      <c r="K54" s="24" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K54" s="18" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L54" s="19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M54" s="20" t="n">
         <v>2</v>
       </c>
       <c r="N54" s="16" t="inlineStr">
         <is>
+          <t>計画策定業務設計書 第4章（02_キックオフ・業務計画）</t>
+        </is>
+      </c>
+      <c r="O54" s="16" t="inlineStr">
+        <is>
           <t>―</t>
-        </is>
-      </c>
-      <c r="O54" s="16" t="inlineStr">
-        <is>
-          <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
       <c r="P54" s="21" t="n"/>
@@ -7811,17 +7812,17 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C55" s="16" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>意見の整理、対応案の作成、計画への反映</t>
+          <t>意見提出期間1か月</t>
         </is>
       </c>
       <c r="E55" s="16" t="inlineStr">
@@ -7841,17 +7842,17 @@
       </c>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="I55" s="17" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="J55" s="17" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="K55" s="24" t="inlineStr">
@@ -7867,12 +7868,12 @@
       </c>
       <c r="N55" s="16" t="inlineStr">
         <is>
-          <t>対応表の様式は作成済み</t>
+          <t>―</t>
         </is>
       </c>
       <c r="O55" s="16" t="inlineStr">
         <is>
-          <t>パブコメの実施</t>
+          <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
       <c r="P55" s="21" t="n"/>
@@ -7892,17 +7893,17 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>9-8</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="C56" s="16" t="inlineStr">
         <is>
-          <t>協議会 第4回（最終案）</t>
+          <t>意見への対応</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>最終案の確認</t>
+          <t>意見の整理、対応案の作成、計画への反映</t>
         </is>
       </c>
       <c r="E56" s="16" t="inlineStr">
@@ -7922,7 +7923,7 @@
       </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="I56" s="17" t="inlineStr">
@@ -7944,16 +7945,16 @@
         <v>0</v>
       </c>
       <c r="M56" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N56" s="16" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>対応表の様式は作成済み</t>
         </is>
       </c>
       <c r="O56" s="16" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>パブコメの実施</t>
         </is>
       </c>
       <c r="P56" s="21" t="n"/>
@@ -7968,42 +7969,42 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>P10 完成・納品</t>
+          <t>P9 意見聴取</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>10-1</t>
+          <t>9-8</t>
         </is>
       </c>
       <c r="C57" s="16" t="inlineStr">
         <is>
-          <t>計画書の原稿確定</t>
+          <t>協議会 第4回（最終案）</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>パブリックコメント対応後の原稿</t>
+          <t>最終案の確認</t>
         </is>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
-          <t>B7 最終調整及び計画書の作成</t>
+          <t>B8 協議会・パブリックコメントの支援</t>
         </is>
       </c>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>仕様書4(4)</t>
+          <t>仕様書4(5)</t>
         </is>
       </c>
       <c r="G57" s="16" t="inlineStr">
         <is>
-          <t>【4(4)】最終調整及び計画書の作成・取りまとめ。（1）から（3）の結果を踏まえ、小野町高齢者保健福祉計画・第10期介護保険事業計画書を作成するものとする。</t>
+          <t>【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
       <c r="H57" s="17" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="I57" s="17" t="inlineStr">
@@ -8025,7 +8026,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N57" s="16" t="inlineStr">
         <is>
@@ -8054,32 +8055,32 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>10-2</t>
+          <t>10-1</t>
         </is>
       </c>
       <c r="C58" s="16" t="inlineStr">
         <is>
-          <t>レイアウト・組版</t>
+          <t>計画書の原稿確定</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>A4・4色刷り・80頁程度</t>
+          <t>パブリックコメント対応後の原稿</t>
         </is>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
-          <t>B9 成果品の納品</t>
+          <t>B7 最終調整及び計画書の作成</t>
         </is>
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>仕様書4 成果品⑤</t>
+          <t>仕様書4(4)</t>
         </is>
       </c>
       <c r="G58" s="16" t="inlineStr">
         <is>
-          <t>【成果品⑤】（5）小野町高齢者保健福祉計画・第10期介護保険事業計画　※データ（CD-R）1部、計画書印刷50部＜仕様＞A4版、4色刷り、80頁程度</t>
+          <t>【4(4)】最終調整及び計画書の作成・取りまとめ。（1）から（3）の結果を踏まえ、小野町高齢者保健福祉計画・第10期介護保険事業計画書を作成するものとする。</t>
         </is>
       </c>
       <c r="H58" s="17" t="inlineStr">
@@ -8115,7 +8116,7 @@
       </c>
       <c r="O58" s="16" t="inlineStr">
         <is>
-          <t>原稿の確定</t>
+          <t>意見への対応</t>
         </is>
       </c>
       <c r="P58" s="21" t="n"/>
@@ -8135,17 +8136,17 @@
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>10-3</t>
+          <t>10-2</t>
         </is>
       </c>
       <c r="C59" s="16" t="inlineStr">
         <is>
-          <t>校正（初校・再校・校了）</t>
+          <t>レイアウト・組版</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>町の確認を経て校了</t>
+          <t>A4・4色刷り・80頁程度</t>
         </is>
       </c>
       <c r="E59" s="16" t="inlineStr">
@@ -8165,7 +8166,7 @@
       </c>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="I59" s="17" t="inlineStr">
@@ -8187,16 +8188,16 @@
         <v>0</v>
       </c>
       <c r="M59" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N59" s="16" t="inlineStr">
         <is>
-          <t>**逆算表を作成済み（令和9年2月下旬の校了が動かせない期限）**</t>
+          <t>―</t>
         </is>
       </c>
       <c r="O59" s="16" t="inlineStr">
         <is>
-          <t>組版</t>
+          <t>原稿の確定</t>
         </is>
       </c>
       <c r="P59" s="21" t="n"/>
@@ -8216,17 +8217,17 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>10-4</t>
+          <t>10-3</t>
         </is>
       </c>
       <c r="C60" s="16" t="inlineStr">
         <is>
-          <t>概要版の構成案</t>
+          <t>校正（初校・再校・校了）</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>A4・4色刷り・8頁のページ割り</t>
+          <t>町の確認を経て校了</t>
         </is>
       </c>
       <c r="E60" s="16" t="inlineStr">
@@ -8236,48 +8237,48 @@
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>仕様書4 成果品⑥</t>
+          <t>仕様書4 成果品⑤</t>
         </is>
       </c>
       <c r="G60" s="16" t="inlineStr">
         <is>
-          <t>【成果品⑥】（6）小野町高齢者保健福祉計画・第10期介護保険事業計画概要版　※データ（CD-R）1部、概要版印刷50部＜仕様＞A4版、4色刷り、8頁</t>
+          <t>【成果品⑤】（5）小野町高齢者保健福祉計画・第10期介護保険事業計画　※データ（CD-R）1部、計画書印刷50部＜仕様＞A4版、4色刷り、80頁程度</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="J60" s="17" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="K60" s="18" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="K60" s="24" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="L60" s="19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M60" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N60" s="16" t="inlineStr">
         <is>
-          <t>計画策定業務設計書 第2章（02_キックオフ・業務計画）</t>
+          <t>**逆算表を作成済み（令和9年2月下旬の校了が動かせない期限）**</t>
         </is>
       </c>
       <c r="O60" s="16" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>組版</t>
         </is>
       </c>
       <c r="P60" s="21" t="n"/>
@@ -8297,17 +8298,17 @@
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>10-5</t>
+          <t>10-4</t>
         </is>
       </c>
       <c r="C61" s="16" t="inlineStr">
         <is>
-          <t>概要版の作成</t>
+          <t>概要版の構成案</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>計画書からの抽出とリライト、図表8点程度</t>
+          <t>A4・4色刷り・8頁のページ割り</t>
         </is>
       </c>
       <c r="E61" s="16" t="inlineStr">
@@ -8332,33 +8333,33 @@
       </c>
       <c r="I61" s="17" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="J61" s="17" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="K61" s="24" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K61" s="18" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L61" s="19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M61" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N61" s="16" t="inlineStr">
         <is>
-          <t>構成案は作成済み</t>
+          <t>計画策定業務設計書 第2章（02_キックオフ・業務計画）</t>
         </is>
       </c>
       <c r="O61" s="16" t="inlineStr">
         <is>
-          <t>計画書の確定</t>
+          <t>―</t>
         </is>
       </c>
       <c r="P61" s="21" t="n"/>
@@ -8378,17 +8379,17 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>10-6</t>
+          <t>10-5</t>
         </is>
       </c>
       <c r="C62" s="16" t="inlineStr">
         <is>
-          <t>印刷・製本</t>
+          <t>概要版の作成</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>計画書50部、概要版50部。色校正を含む</t>
+          <t>計画書からの抽出とリライト、図表8点程度</t>
         </is>
       </c>
       <c r="E62" s="16" t="inlineStr">
@@ -8398,13 +8399,12 @@
       </c>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>仕様書4 成果品⑤・仕様書4 成果品⑥</t>
+          <t>仕様書4 成果品⑥</t>
         </is>
       </c>
       <c r="G62" s="16" t="inlineStr">
         <is>
-          <t>【成果品⑤】（5）小野町高齢者保健福祉計画・第10期介護保険事業計画　※データ（CD-R）1部、計画書印刷50部＜仕様＞A4版、4色刷り、80頁程度
-【成果品⑥】（6）小野町高齢者保健福祉計画・第10期介護保険事業計画概要版　※データ（CD-R）1部、概要版印刷50部＜仕様＞A4版、4色刷り、8頁</t>
+          <t>【成果品⑥】（6）小野町高齢者保健福祉計画・第10期介護保険事業計画概要版　※データ（CD-R）1部、概要版印刷50部＜仕様＞A4版、4色刷り、8頁</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="J62" s="17" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="N62" s="16" t="inlineStr">
         <is>
-          <t>**逆算表を作成済み。12月までに印刷業者を押さえる必要がある**</t>
+          <t>構成案は作成済み</t>
         </is>
       </c>
       <c r="O62" s="16" t="inlineStr">
         <is>
-          <t>校了</t>
+          <t>計画書の確定</t>
         </is>
       </c>
       <c r="P62" s="21" t="n"/>
@@ -8460,17 +8460,17 @@
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>10-7</t>
+          <t>10-6</t>
         </is>
       </c>
       <c r="C63" s="16" t="inlineStr">
         <is>
-          <t>データCD-Rの作成</t>
+          <t>印刷・製本</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>成果品①〜⑥のデータ</t>
+          <t>計画書50部、概要版50部。色校正を含む</t>
         </is>
       </c>
       <c r="E63" s="16" t="inlineStr">
@@ -8480,12 +8480,13 @@
       </c>
       <c r="F63" s="17" t="inlineStr">
         <is>
-          <t>仕様書4 成果品</t>
+          <t>仕様書4 成果品⑤・仕様書4 成果品⑥</t>
         </is>
       </c>
       <c r="G63" s="16" t="inlineStr">
         <is>
-          <t>【成果品】（1）〜（4）のデータ（CD-R）1部、冊子（簡易製本）各3部／（5）（6）のデータ（CD-R）1部、計画書印刷50部／概要版印刷50部</t>
+          <t>【成果品⑤】（5）小野町高齢者保健福祉計画・第10期介護保険事業計画　※データ（CD-R）1部、計画書印刷50部＜仕様＞A4版、4色刷り、80頁程度
+【成果品⑥】（6）小野町高齢者保健福祉計画・第10期介護保険事業計画概要版　※データ（CD-R）1部、概要版印刷50部＜仕様＞A4版、4色刷り、8頁</t>
         </is>
       </c>
       <c r="H63" s="17" t="inlineStr">
@@ -8512,16 +8513,16 @@
         <v>0</v>
       </c>
       <c r="M63" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N63" s="16" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**逆算表を作成済み。12月までに印刷業者を押さえる必要がある**</t>
         </is>
       </c>
       <c r="O63" s="16" t="inlineStr">
         <is>
-          <t>各成果品の確定</t>
+          <t>校了</t>
         </is>
       </c>
       <c r="P63" s="21" t="n"/>
@@ -8541,37 +8542,37 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>10-8</t>
+          <t>10-7</t>
         </is>
       </c>
       <c r="C64" s="16" t="inlineStr">
         <is>
-          <t>納品・検収</t>
+          <t>データCD-Rの作成</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>令和9年3月31日まで</t>
+          <t>成果品①〜⑥のデータ</t>
         </is>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
-          <t>B10 業務管理・計画の基本的な考え方</t>
+          <t>B9 成果品の納品</t>
         </is>
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>仕様書3（業務期間）</t>
+          <t>仕様書4 成果品</t>
         </is>
       </c>
       <c r="G64" s="16" t="inlineStr">
         <is>
-          <t>【3】契約締結の日から令和9年3月31日まで</t>
+          <t>【成果品】（1）〜（4）のデータ（CD-R）1部、冊子（簡易製本）各3部／（5）（6）のデータ（CD-R）1部、計画書印刷50部／概要版印刷50部</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="I64" s="17" t="inlineStr">
@@ -8602,7 +8603,7 @@
       </c>
       <c r="O64" s="16" t="inlineStr">
         <is>
-          <t>全成果品の完成</t>
+          <t>各成果品の確定</t>
         </is>
       </c>
       <c r="P64" s="21" t="n"/>
@@ -8614,9 +8615,90 @@
       <c r="V64" s="21" t="n"/>
       <c r="W64" s="21" t="n"/>
     </row>
+    <row r="65">
+      <c r="A65" s="16" t="inlineStr">
+        <is>
+          <t>P10 完成・納品</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>10-8</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="inlineStr">
+        <is>
+          <t>納品・検収</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="inlineStr">
+        <is>
+          <t>令和9年3月31日まで</t>
+        </is>
+      </c>
+      <c r="E65" s="16" t="inlineStr">
+        <is>
+          <t>B10 業務管理・計画の基本的な考え方</t>
+        </is>
+      </c>
+      <c r="F65" s="17" t="inlineStr">
+        <is>
+          <t>仕様書3（業務期間）</t>
+        </is>
+      </c>
+      <c r="G65" s="16" t="inlineStr">
+        <is>
+          <t>【3】契約締結の日から令和9年3月31日まで</t>
+        </is>
+      </c>
+      <c r="H65" s="17" t="inlineStr">
+        <is>
+          <t>受託者・町</t>
+        </is>
+      </c>
+      <c r="I65" s="17" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="J65" s="17" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="K65" s="24" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" s="16" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="O65" s="16" t="inlineStr">
+        <is>
+          <t>全成果品の完成</t>
+        </is>
+      </c>
+      <c r="P65" s="21" t="n"/>
+      <c r="Q65" s="21" t="n"/>
+      <c r="R65" s="21" t="n"/>
+      <c r="S65" s="21" t="n"/>
+      <c r="T65" s="21" t="n"/>
+      <c r="U65" s="21" t="n"/>
+      <c r="V65" s="21" t="n"/>
+      <c r="W65" s="21" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O64"/>
-  <conditionalFormatting sqref="L2:L64">
+  <autoFilter ref="A1:O65"/>
+  <conditionalFormatting sqref="L2:L65">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>100</formula>
     </cfRule>
@@ -8625,10 +8707,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="K2:K64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,進行中,要対応,データ待ち,未着手"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="L2:L65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -8723,31 +8805,31 @@
         </is>
       </c>
       <c r="B2" s="17">
-        <f>COUNTIF('01_WBS'!$A$2:$A$64,$A2)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$65,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A2,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="D2" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A2,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="E2" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A2,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="F2" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A2,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="G2" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A2,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="H2" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A2)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A2)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A2)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A2)*'01_WBS'!$M$2:$M$65)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A2)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A2)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="I2" s="17" t="inlineStr">
@@ -8773,31 +8855,31 @@
         </is>
       </c>
       <c r="B3" s="17">
-        <f>COUNTIF('01_WBS'!$A$2:$A$64,$A3)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$65,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A3,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="D3" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A3,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="E3" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A3,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="F3" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A3,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="G3" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A3,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="H3" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A3)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A3)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A3)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A3)*'01_WBS'!$M$2:$M$65)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A3)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A3)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="I3" s="17" t="inlineStr">
@@ -8807,7 +8889,7 @@
       </c>
       <c r="J3" s="17" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="K3" s="16" t="inlineStr">
@@ -8823,31 +8905,31 @@
         </is>
       </c>
       <c r="B4" s="17">
-        <f>COUNTIF('01_WBS'!$A$2:$A$64,$A4)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$65,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A4,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="D4" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A4,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="E4" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A4,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="F4" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A4,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="G4" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A4,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="H4" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A4)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A4)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A4)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A4)*'01_WBS'!$M$2:$M$65)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A4)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A4)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="I4" s="17" t="inlineStr">
@@ -8873,31 +8955,31 @@
         </is>
       </c>
       <c r="B5" s="17">
-        <f>COUNTIF('01_WBS'!$A$2:$A$64,$A5)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$65,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A5,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="D5" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A5,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="E5" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A5,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="F5" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A5,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="G5" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A5,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="H5" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A5)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A5)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A5)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A5)*'01_WBS'!$M$2:$M$65)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A5)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A5)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="I5" s="17" t="inlineStr">
@@ -8923,31 +9005,31 @@
         </is>
       </c>
       <c r="B6" s="17">
-        <f>COUNTIF('01_WBS'!$A$2:$A$64,$A6)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$65,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A6,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="D6" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A6,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="E6" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A6,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="F6" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A6,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="G6" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A6,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="H6" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A6)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A6)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A6)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A6)*'01_WBS'!$M$2:$M$65)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A6)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A6)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="I6" s="17" t="inlineStr">
@@ -8973,31 +9055,31 @@
         </is>
       </c>
       <c r="B7" s="17">
-        <f>COUNTIF('01_WBS'!$A$2:$A$64,$A7)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$65,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A7,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="D7" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A7,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="E7" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A7,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="F7" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A7,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="G7" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A7,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="H7" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A7)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A7)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A7)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A7)*'01_WBS'!$M$2:$M$65)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A7)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A7)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="I7" s="17" t="inlineStr">
@@ -9023,31 +9105,31 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>COUNTIF('01_WBS'!$A$2:$A$64,$A8)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$65,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A8,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A8,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A8,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A8,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="G8" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A8,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="H8" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A8)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A8)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A8)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A8)*'01_WBS'!$M$2:$M$65)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A8)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A8)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="I8" s="17" t="inlineStr">
@@ -9073,31 +9155,31 @@
         </is>
       </c>
       <c r="B9" s="17">
-        <f>COUNTIF('01_WBS'!$A$2:$A$64,$A9)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$65,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A9,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="D9" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A9,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="E9" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A9,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="F9" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A9,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="G9" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A9,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="H9" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A9)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A9)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A9)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A9)*'01_WBS'!$M$2:$M$65)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A9)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A9)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="I9" s="17" t="inlineStr">
@@ -9123,31 +9205,31 @@
         </is>
       </c>
       <c r="B10" s="17">
-        <f>COUNTIF('01_WBS'!$A$2:$A$64,$A10)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$65,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A10,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="D10" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A10,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="E10" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A10,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="F10" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A10,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="G10" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A10,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="H10" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A10)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A10)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A10)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A10)*'01_WBS'!$M$2:$M$65)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A10)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A10)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="I10" s="17" t="inlineStr">
@@ -9173,31 +9255,31 @@
         </is>
       </c>
       <c r="B11" s="17">
-        <f>COUNTIF('01_WBS'!$A$2:$A$64,$A11)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$65,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A11,'01_WBS'!$K$2:$K$65,"完了")</f>
         <v/>
       </c>
       <c r="D11" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A11,'01_WBS'!$K$2:$K$65,"進行中")</f>
         <v/>
       </c>
       <c r="E11" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A11,'01_WBS'!$K$2:$K$65,"要対応")</f>
         <v/>
       </c>
       <c r="F11" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A11,'01_WBS'!$K$2:$K$65,"データ待ち")</f>
         <v/>
       </c>
       <c r="G11" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$65,$A11,'01_WBS'!$K$2:$K$65,"未着手")</f>
         <v/>
       </c>
       <c r="H11" s="25">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A11)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A11)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A11)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A11)*'01_WBS'!$M$2:$M$65)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A11)*'01_WBS'!$L$2:$L$65*'01_WBS'!$M$2:$M$65)/SUMPRODUCT(('01_WBS'!$A$2:$A$65=$A11)*'01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="I11" s="17" t="inlineStr">
@@ -9247,7 +9329,7 @@
         <v/>
       </c>
       <c r="H12" s="28">
-        <f>IF(SUM('01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT('01_WBS'!$L$2:$L$64,'01_WBS'!$M$2:$M$64)/SUM('01_WBS'!$M$2:$M$64)/100)</f>
+        <f>IF(SUM('01_WBS'!$M$2:$M$65)=0,0,SUMPRODUCT('01_WBS'!$L$2:$L$65,'01_WBS'!$M$2:$M$65)/SUM('01_WBS'!$M$2:$M$65)/100)</f>
         <v/>
       </c>
       <c r="I12" s="17" t="inlineStr">

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
@@ -6565,7 +6565,7 @@
       </c>
       <c r="U39" s="17" t="inlineStr">
         <is>
-          <t>**9月25日に、令和8年度の置き方を4通りで比べ、国保連月報で裏づけた（12_令和8年度の置き方）。**令和7年度の実績に対する比は、据え置き1.0000／令和6→令和7の動きを1年延長0.9255／当方の現行方式1.0171／**月報3か月の実績0.9598**。**当方の現行方式は実績より6.0％高い。**令和5〜7年度の3年平均が、下がり続けている系列を上に引いているため。**9月25日に、この自然体推計ケースを標準ケースに切り替えた（素案 第5版、見込量の算定結果 令和8年9月25日版）。**令和8年度を月報の実績で置き、そこから人口で延ばす。総給付費の3年計は2,876,614千円（従前の方式から▲5.6％）、標準給付費3,101,160千円、保険料は月額6,224円（100円未満切上げで6,300円。第9期の6,600円から▲376円・▲5.7％）。**見える化システムの自然体推計と同じ構造であり、システムの出力と素案の数値が突き合う。**従前の方式（3年平均の伸び）によるケースは月額6,570円で、比較のケースとして残した。令和8年度は3か月分しかなく完結年度ではないため、残りの月の実績を見たうえで協議会にお諮りして確定する</t>
+          <t>**9月25日に、令和8年度の置き方を4通りで比べ、国保連月報で裏づけた（12_令和8年度の置き方）。**令和7年度の実績に対する比は、据え置き1.0000／令和6→令和7の動きを1年延長0.9255／当方の現行方式1.0171／**月報3か月の実績0.9598**。**当方の現行方式は実績より6.0％高い。**令和5〜7年度の3年平均が、下がり続けている系列を上に引いているため。**9月25日に、この自然体推計ケースを標準ケースに切り替えた（素案 第5版、見込量の算定結果 令和8年9月25日版）。**令和8年度を月報の実績で置き、そこから人口で延ばす。総給付費の3年計は2,869,936千円（従前の方式から▲5.9％）、標準給付費3,093,948千円、保険料は月額6,210円（100円未満切上げで6,300円。第9期の6,600円から▲376円・▲5.7％）。**見える化システムの自然体推計と総額の置き方が同じであり、システムの出力と素案の数値が突き合う。**従前の方式（3年平均の伸び）によるケースは月額6,570円で、比較のケースとして残した。令和8年度は3か月分しかなく完結年度ではないため、残りの月の実績を見たうえで協議会にお諮りして確定する</t>
         </is>
       </c>
       <c r="V39" s="17" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="N40" s="16" t="inlineStr">
         <is>
-          <t>**川崎町・金ケ崎町の両ブランチを確認し、入力時の設定と落とし穴を整理した（見込量算定の方針と不足資料・04_算定・見込量）。**①介護保険事業状況報告の設定で令和8年度のチェックを外す（外さないと令和8年5月の1か月が年度として扱われる）②伸びは令和6年度→令和7年度（完結年度どうし）③1人1月あたり給付費は令和7年度④**施策反映の3画面は編集せず通過する（一度編集すると自然体推計に戻せない）**</t>
+          <t>**川崎町・金ケ崎町の両ブランチを確認し、入力時の設定と落とし穴を整理した（見込量算定の方針と不足資料・04_算定・見込量）。**①介護保険事業状況報告の設定で令和8年度のチェックを外す（外さないと令和8年5月の1か月が年度として扱われる）②伸びは令和6年度→令和7年度（完結年度どうし）③1人1月あたり給付費は令和7年度④**施策反映の3画面は編集せず通過する。**編集するとセルがピンクになり「自然体推計に全て戻す」が押せる状態になる。**この状態のまま総括表を出すと、伸びの窓を変えても見込量が動かない**</t>
         </is>
       </c>
       <c r="O40" s="16" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="N41" s="16" t="inlineStr">
         <is>
-          <t>**所得段階別被保険者数（13段階）、小野町が定める保険料率（第1〜3段階は0.285／0.486／0.685で国の標準より低い）、収納率99.35％、基金保有額12,000千円を投入済み。地域支援事業費は年報 様式4 の令和6年度決算63,916千円（3年計191,749千円）を事業別に割り付けて投入した。総合事業の内訳は国保連月報の総合事業コード（A2・A6・AF）による。****9月25日に標準ケースを自然体推計に切り替えた結果、保険料基準額は月額6,224円（基金取崩なし）、6,121円（保有額12,000千円を全額取崩）、5,924円（第9期と同じ35,000千円を取崩）となった。**第9期は6,600円。負担割合が24％になると6,505円。従前の方式（令和5〜7年度の3年平均の伸び）では6,570円であり、比較のケースとして残している。**調整交付金の見込交付割合は第9期計画の公表値から逆算して6.148％。標準の5％ではない（小野町は後期高齢者加入割合が高く低所得層が厚い）**※ 逆算される調整交付金見込額219,272千円は基数の取り方によらない。見える化システムは標準給付費見込額のみを基数とするため6.148％、総合事業費を含めると5.963％となる（本件は前者にそろえた）</t>
+          <t>**所得段階別被保険者数（13段階）、小野町が定める保険料率（第1〜3段階は0.285／0.486／0.685で国の標準より低い）、収納率99.35％、基金保有額12,000千円を投入済み。地域支援事業費は年報 様式4 の令和6年度決算63,916千円（3年計191,749千円）を事業別に割り付けて投入した。総合事業の内訳は国保連月報の総合事業コード（A2・A6・AF）による。****9月25日に標準ケースを自然体推計に切り替えた結果、保険料基準額は月額6,210円（基金取崩なし）、6,107円（保有額12,000千円を全額取崩）、5,910円（第9期と同じ35,000千円を取崩）となった。**第9期は6,600円。負担割合が24％になると6,491円。従前の方式（令和5〜7年度の3年平均の伸び）では6,570円であり、比較のケースとして残している。**調整交付金の見込交付割合は第9期計画の公表値から逆算して6.148％。標準の5％ではない（小野町は後期高齢者加入割合が高く低所得層が厚い）**※ 逆算される調整交付金見込額219,272千円は基数の取り方によらない。見える化システムは標準給付費見込額のみを基数とするため6.148％、総合事業費を含めると5.963％となる（本件は前者にそろえた）</t>
         </is>
       </c>
       <c r="O41" s="16" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="N44" s="16" t="inlineStr">
         <is>
-          <t>**第5版（5章＋資料編・74表）。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定158箇所のうち61箇所が解消し97箇所となった。**第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量・給付費・標準給付費・地域支援事業費の事業別内訳・保険料基準額を入れた。**第5版（9月25日）で令和8年度の置き方を自然体推計に改め、保険料基準額は月額6,570円から6,224円（切上げ6,300円）となった。**従前の方式による算定は比較のケースとして残している。**第5章2の進行管理に、保険者機能強化推進交付金等の評価結果を点検項目として加えた**（評価結果を外部の議論の場で検証すること自体が評価指標の要件であるため）</t>
+          <t>**第5版（5章＋資料編・74表）。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定158箇所のうち61箇所が解消し97箇所となった。**第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量・給付費・標準給付費・地域支援事業費の事業別内訳・保険料基準額を入れた。**第5版（9月25日）で令和8年度の置き方を自然体推計に改め、保険料基準額は月額6,570円から6,210円（切上げ6,300円）となった。****9月25日の再検証で、延ばし方を見える化システムの仕様にそろえた**（施設は利用者数一定、居住系・在宅は認定者数で延ばす。月額▲13円）。従前の方式による算定は比較のケースとして残している。**第5章2の進行管理に、保険者機能強化推進交付金等の評価結果を点検項目として加えた**（評価結果を外部の議論の場で検証すること自体が評価指標の要件であるため）</t>
         </is>
       </c>
       <c r="O44" s="16" t="inlineStr">

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
@@ -6565,7 +6565,7 @@
       </c>
       <c r="U39" s="17" t="inlineStr">
         <is>
-          <t>**9月25日に、令和8年度の置き方を4通りで比べ、国保連月報で裏づけた（12_令和8年度の置き方）。**令和7年度の実績に対する比は、据え置き1.0000／令和6→令和7の動きを1年延長0.9255／当方の現行方式1.0171／**月報3か月の実績0.9598**。**当方の現行方式は実績より6.0％高い。**令和5〜7年度の3年平均が、下がり続けている系列を上に引いているため。**9月25日に、この自然体推計ケースを標準ケースに切り替えた（素案 第5版、見込量の算定結果 令和8年9月25日版）。**令和8年度を月報の実績で置き、そこから人口で延ばす。総給付費の3年計は2,869,936千円（従前の方式から▲5.9％）、標準給付費3,093,948千円、保険料は月額6,210円（100円未満切上げで6,300円。第9期の6,600円から▲376円・▲5.7％）。**見える化システムの自然体推計と総額の置き方が同じであり、システムの出力と素案の数値が突き合う。**従前の方式（3年平均の伸び）によるケースは月額6,570円で、比較のケースとして残した。令和8年度は3か月分しかなく完結年度ではないため、残りの月の実績を見たうえで協議会にお諮りして確定する</t>
+          <t>**9月25日に、令和8年度の置き方を4通りで比べ、国保連月報で裏づけた（12_令和8年度の置き方）。**令和7年度の実績に対する比は、据え置き1.0000／令和6→令和7の動きを1年延長0.9255／当方の現行方式1.0171／**月報3か月の実績0.9598**。**当方の現行方式は実績より6.0％高い。**令和5〜7年度の3年平均が、下がり続けている系列を上に引いているため。**9月25日に、この自然体推計ケースを標準ケースに切り替えた（素案 第5版、見込量の算定結果 令和8年9月25日版）。**令和8年度を月報の実績で置き、そこから人口で延ばす。総給付費の3年計は2,869,936千円（従前の方式から▲5.9％）、標準給付費3,093,948千円、保険料は月額6,095円（100円未満切上げで6,100円。第9期の6,600円から▲505円・▲7.7％）。**見える化システムの自然体推計と総額の置き方が同じであり、システムの出力と素案の数値が突き合う。**従前の方式（3年平均の伸び）によるケースは月額6,449円で、比較のケースとして残した。令和8年度は3か月分しかなく完結年度ではないため、残りの月の実績を見たうえで協議会にお諮りして確定する</t>
         </is>
       </c>
       <c r="V39" s="17" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="O40" s="16" t="inlineStr">
         <is>
-          <t>**9月24日に、受領したワークシートを1行ずつ読んで入力値を確定した（見える化システム入力値一覧・入力の手順。11_見える化出力依頼）。****入力の前に直す設定が2件ある。**①1人1月あたり給付費の実績値が令和8年度になっている。令和8年度の列は1か月分で、人数・回数・日数の非ゼロ36件のうち31件（86.1％）が整数である（令和6年度は46件中5件、令和7年度は40件中8件で、いずれも12分の1単位の小数）。令和7年度に切り替える。②認定率の伸びが令和6年度→令和7年度になっている。**見える化の認定者数は各年9月末の値で、令和7年度の865人は令和7年9月の断層の直後にあたる。**令和6年度937人は国保連の令和6年10月審査分と一致し、令和7年度865人と令和8年度865人は同値で令和8年度に実績がないことを示す。計上方法の確認が取れるまでこの伸びは使えない。**入力欄は、当方で用意できるものが28欄、町の資料が要るものが26欄。**町の資料が要るのは一般介護予防事業5欄（計5,305千円）、包括的支援事業・任意事業8欄（計29,335千円）、審査支払手数料等2欄（計531千円）、準備基金、令和8年度の当初予算など。**所得段階別加入割合13段階を入れると調整交付金見込交付割合が自動で出るため、当方の逆算値6.148％と突き合わせる**</t>
+          <t>**9月24日に、受領したワークシートを1行ずつ読んで入力値を確定した（見える化システム入力値一覧・入力の手順。11_見える化出力依頼）。****入力の前に直す設定が2件ある。**①1人1月あたり給付費の実績値が令和8年度になっている。令和8年度の列は1か月分で、人数・回数・日数の非ゼロ36件のうち31件（86.1％）が整数である（令和6年度は46件中5件、令和7年度は40件中8件で、いずれも12分の1単位の小数）。令和7年度に切り替える。②認定率の伸びが令和6年度→令和7年度になっている。**見える化の認定者数は各年9月末の値で、令和7年度の865人は令和7年9月の断層の直後にあたる。**令和6年度937人は国保連の令和6年10月審査分と一致し、令和7年度865人と令和8年度865人は同値で令和8年度に実績がないことを示す。計上方法の確認が取れるまでこの伸びは使えない。**入力欄は、当方で用意できるものが28欄、町の資料が要るものが26欄。**町の資料が要るのは一般介護予防事業5欄（計5,305千円）、包括的支援事業・任意事業8欄（計29,335千円）、審査支払手数料等2欄（計531千円）、準備基金、令和8年度の当初予算など。**所得段階別加入割合13段階を入れると調整交付金見込交付割合が自動で出るため、当方の算式値（令和9年度6.107％・令和10年度5.548％・令和11年度4.945％）と突き合わせる**</t>
         </is>
       </c>
       <c r="P40" s="17" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="N41" s="16" t="inlineStr">
         <is>
-          <t>**所得段階別被保険者数（13段階）、小野町が定める保険料率（第1〜3段階は0.285／0.486／0.685で国の標準より低い）、収納率99.35％、基金保有額12,000千円を投入済み。地域支援事業費は年報 様式4 の令和6年度決算63,916千円（3年計191,749千円）を事業別に割り付けて投入した。総合事業の内訳は国保連月報の総合事業コード（A2・A6・AF）による。****9月25日に標準ケースを自然体推計に切り替えた結果、保険料基準額は月額6,210円（基金取崩なし）、6,107円（保有額12,000千円を全額取崩）、5,910円（第9期と同じ35,000千円を取崩）となった。**第9期は6,600円。負担割合が24％になると6,491円。従前の方式（令和5〜7年度の3年平均の伸び）では6,570円であり、比較のケースとして残している。**調整交付金の見込交付割合は第9期計画の公表値から逆算して6.148％。標準の5％ではない（小野町は後期高齢者加入割合が高く低所得層が厚い）**※ 逆算される調整交付金見込額219,272千円は基数の取り方によらない。見える化システムは標準給付費見込額のみを基数とするため6.148％、総合事業費を含めると5.963％となる（本件は前者にそろえた）</t>
+          <t>**所得段階別被保険者数（13段階）、小野町が定める保険料率（第1〜3段階は0.285／0.485／0.685で国の標準より低い）、収納率99.35％、基金保有額12,000千円を投入済み。地域支援事業費は年報 様式4 の令和6年度決算63,916千円（3年計191,749千円）を事業別に割り付けて投入した。総合事業の内訳は国保連月報の総合事業コード（A2・A6・AF）による。****9月25日に標準ケースを自然体推計に切り替え、あわせて所得段階別の割合を軽減前の標準割合に訂正した結果、保険料基準額は月額6,095円（基金取崩なし）、5,997円（保有額12,000千円を全額取崩）、5,808円（第9期と同じ35,000千円を取崩）となった。**第9期は6,600円。負担割合が24％になると6,364円。従前の方式（令和5〜7年度の3年平均の伸び）では6,449円であり、比較のケースとして残している。**9月25日に、保険料基準額の算定に用いる所得段階別の割合を軽減後の賦課割合（0.285／0.485／0.685）から軽減前の標準割合（0.455／0.685／0.690）に訂正した。**軽減相当額は別枠の公費（国1/2・県1/4・町1/4）で補填され、保険料収納必要額から控除されないためである。第9期計画の補正後被保険者数10,136人÷第1号被保険者数10,409人＝0.974も軽減前でしか再現できない（軽減後だと0.93台）。見える化システムの「①標準段階区分・割合」の画面でも0.4550／0.6850／0.6900が固定表示されることを同日の画面で確認した。**あわせて調整交付金の見込交付割合を、第9期からの逆算6.148％から算式（（第1号負担割合＋5％）－第1号負担割合×後期高齢者加入割合補正係数×所得段階別加入割合補正係数）による5.533％に改めた。**2つの訂正は互いに打ち消し合い、保険料基準額は月額115円下がった※ 逆算される調整交付金見込額219,272千円は基数の取り方によらない。見える化システムは標準給付費見込額のみを基数とするため6.148％、総合事業費を含めると5.963％となる（本件は前者にそろえた）</t>
         </is>
       </c>
       <c r="O41" s="16" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="N44" s="16" t="inlineStr">
         <is>
-          <t>**第5版（5章＋資料編・74表）。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定158箇所のうち61箇所が解消し97箇所となった。**第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量・給付費・標準給付費・地域支援事業費の事業別内訳・保険料基準額を入れた。**第5版（9月25日）で令和8年度の置き方を自然体推計に改め、保険料基準額は月額6,570円から6,210円（切上げ6,300円）となった。****9月25日の再検証で、延ばし方を見える化システムの仕様にそろえた**（施設は利用者数一定、居住系・在宅は認定者数で延ばす。月額▲13円）。従前の方式による算定は比較のケースとして残している。**第5章2の進行管理に、保険者機能強化推進交付金等の評価結果を点検項目として加えた**（評価結果を外部の議論の場で検証すること自体が評価指標の要件であるため）</t>
+          <t>**第5版（5章＋資料編・74表）。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定158箇所のうち61箇所が解消し97箇所となった。**第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量・給付費・標準給付費・地域支援事業費の事業別内訳・保険料基準額を入れた。**第5版（9月25日）で令和8年度の置き方を自然体推計に改め、保険料基準額は月額6,449円から6,095円（切上げ6,100円）となった。****9月25日の再検証で、延ばし方を見える化システムの仕様にそろえた**（施設は利用者数一定、居住系・在宅は認定者数で延ばす。月額▲13円）。従前の方式による算定は比較のケースとして残している。**第5章2の進行管理に、保険者機能強化推進交付金等の評価結果を点検項目として加えた**（評価結果を外部の議論の場で検証すること自体が評価指標の要件であるため）</t>
         </is>
       </c>
       <c r="O44" s="16" t="inlineStr">
         <is>
-          <t>**9月24日に、受託者が算定すべき未確定箇所をすべて解消した。**所得段階別保険料率を13段階すべてについて算定し（乗率・年額・被保険者数・構成比）、必要利用定員総数・地域支援事業の量・認知症高齢者数を加えた。**未確定は158箇所→94箇所となり、【算定後に記載】は0件になった。****あわせて数値の誤りを2件正した。**①所得第2段階の乗率を0.485としていたが、年報 様式1 所得段階別および第9期の年額38,500円（＝0.486×79,200円）から0.486が正しい（素案・骨子案・給付費等分析の3点）。②所得第1〜3段階の割合を28％としていたが、1,094人÷3,443人で31.8％が正しい。**第2章1の人口（見える化の将来推計・暦年）と第2章6の被保険者数（第10期将来推計用推計人口・年度）が別系列であることを注記した。**従前の注は「保険料算定との整合のため見える化の推計を用いる」と書いていたが、保険料算定は後者を用いており誤りであった</t>
+          <t>**9月24日に、受託者が算定すべき未確定箇所をすべて解消した。**所得段階別保険料率を13段階すべてについて算定し（乗率・年額・被保険者数・構成比）、必要利用定員総数・地域支援事業の量・認知症高齢者数を加えた。**未確定は158箇所→94箇所となり、【算定後に記載】は0件になった。****あわせて数値の誤りを2件正した。**①所得第2段階の乗率を年報 様式1 所得段階別の令和7年度の値により0.486としたが、**これは誤りで0.485が正しい**（9月25日に再訂正）。第9期計画本文が「基準額×0.485」「年額38,500円」と明記しており、79,200円×0.485＝38,412円の100円未満切上げで38,500円になる。年報の令和6年度は485であり、令和7年度の486が入力誤りである。②所得第1〜3段階の割合を28％としていたが、1,094人÷3,443人で31.8％が正しい。**第2章1の人口（見える化の将来推計・暦年）と第2章6の被保険者数（第10期将来推計用推計人口・年度）が別系列であることを注記した。**従前の注は「保険料算定との整合のため見える化の推計を用いる」と書いていたが、保険料算定は後者を用いており誤りであった</t>
         </is>
       </c>
       <c r="P44" s="17" t="inlineStr">

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
@@ -6565,7 +6565,7 @@
       </c>
       <c r="U39" s="17" t="inlineStr">
         <is>
-          <t>**9月25日に、令和8年度の置き方を4通りで比べ、国保連月報で裏づけた（12_令和8年度の置き方）。**令和7年度の実績に対する比は、据え置き1.0000／令和6→令和7の動きを1年延長0.9255／当方の現行方式1.0171／**月報3か月の実績0.9598**。**当方の現行方式は実績より6.0％高い。**令和5〜7年度の3年平均が、下がり続けている系列を上に引いているため。**9月25日に、この自然体推計ケースを標準ケースに切り替えた（素案 第5版、見込量の算定結果 令和8年9月25日版）。**令和8年度を月報の実績で置き、そこから人口で延ばす。総給付費の3年計は2,869,936千円（従前の方式から▲5.9％）、標準給付費3,093,948千円、保険料は月額6,095円（100円未満切上げで6,100円。第9期の6,600円から▲505円・▲7.7％）。**見える化システムの自然体推計と総額の置き方が同じであり、システムの出力と素案の数値が突き合う。**従前の方式（3年平均の伸び）によるケースは月額6,449円で、比較のケースとして残した。令和8年度は3か月分しかなく完結年度ではないため、残りの月の実績を見たうえで協議会にお諮りして確定する</t>
+          <t>**9月25日に、令和8年度の置き方を4通りで比べ、国保連月報で裏づけた（12_令和8年度の置き方）。**令和7年度の実績に対する比は、据え置き1.0000／令和6→令和7の動きを1年延長0.9255／当方の現行方式1.0171／**月報3か月の実績0.9598**。**当方の現行方式は実績より6.0％高い。**令和5〜7年度の3年平均が、下がり続けている系列を上に引いているため。**9月25日に、この自然体推計ケースを標準ケースに切り替えた（素案 第5版、見込量の算定結果 令和8年9月25日版）。**令和8年度を月報の実績で置き、そこから人口で延ばす。総給付費の3年計は2,869,936千円（従前の方式から▲5.9％）、標準給付費3,093,948千円、保険料は月額6,048円（100円未満切上げで6,100円。第9期の6,600円から▲500円・▲7.6％）。**見える化システムの自然体推計と総額の置き方が同じであり、システムの出力と素案の数値が突き合う。**従前の方式（3年平均の伸び）によるケースは月額6,402円で、比較のケースとして残した。令和8年度は3か月分しかなく完結年度ではないため、残りの月の実績を見たうえで協議会にお諮りして確定する</t>
         </is>
       </c>
       <c r="V39" s="17" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="N41" s="16" t="inlineStr">
         <is>
-          <t>**所得段階別被保険者数（13段階）、小野町が定める保険料率（第1〜3段階は0.285／0.485／0.685で国の標準より低い）、収納率99.35％、基金保有額12,000千円を投入済み。地域支援事業費は年報 様式4 の令和6年度決算63,916千円（3年計191,749千円）を事業別に割り付けて投入した。総合事業の内訳は国保連月報の総合事業コード（A2・A6・AF）による。****9月25日に標準ケースを自然体推計に切り替え、あわせて所得段階別の割合を軽減前の標準割合に訂正した結果、保険料基準額は月額6,095円（基金取崩なし）、5,997円（保有額12,000千円を全額取崩）、5,808円（第9期と同じ35,000千円を取崩）となった。**第9期は6,600円。負担割合が24％になると6,364円。従前の方式（令和5〜7年度の3年平均の伸び）では6,449円であり、比較のケースとして残している。**9月25日に、保険料基準額の算定に用いる所得段階別の割合を軽減後の賦課割合（0.285／0.485／0.685）から軽減前の標準割合（0.455／0.685／0.690）に訂正した。**軽減相当額は別枠の公費（国1/2・県1/4・町1/4）で補填され、保険料収納必要額から控除されないためである。第9期計画の補正後被保険者数10,136人÷第1号被保険者数10,409人＝0.974も軽減前でしか再現できない（軽減後だと0.93台）。見える化システムの「①標準段階区分・割合」の画面でも0.4550／0.6850／0.6900が固定表示されることを同日の画面で確認した。**あわせて調整交付金の見込交付割合を、第9期からの逆算6.148％から算式（（第1号負担割合＋5％）－第1号負担割合×後期高齢者加入割合補正係数×所得段階別加入割合補正係数）による5.533％に改めた。**2つの訂正は互いに打ち消し合い、保険料基準額は月額115円下がった※ 逆算される調整交付金見込額219,272千円は基数の取り方によらない。見える化システムは標準給付費見込額のみを基数とするため6.148％、総合事業費を含めると5.963％となる（本件は前者にそろえた）</t>
+          <t>**所得段階別被保険者数（13段階）、小野町が定める保険料率（第1〜3段階は0.285／0.485／0.685で国の標準より低い）、収納率99.35％、基金保有額12,000千円を投入済み。地域支援事業費は年報 様式4 の令和6年度決算63,916千円（3年計191,749千円）を事業別に割り付けて投入した。総合事業の内訳は国保連月報の総合事業コード（A2・A6・AF）による。****9月25日に標準ケースを自然体推計に切り替え、あわせて所得段階別の割合を軽減前の標準割合に訂正した結果、保険料基準額は月額6,048円（基金取崩なし）、5,997円（保有額12,000千円を全額取崩）、5,808円（第9期と同じ35,000千円を取崩）となった。**第9期は6,600円。負担割合が24％になると6,364円。従前の方式（令和5〜7年度の3年平均の伸び）では6,402円であり、比較のケースとして残している。**9月25日に、保険料基準額の算定に用いる所得段階別の割合を軽減後の賦課割合（0.285／0.485／0.685）から軽減前の標準割合（0.455／0.685／0.690）に訂正した。**軽減相当額は別枠の公費（国1/2・県1/4・町1/4）で補填され、保険料収納必要額から控除されないためである。第9期計画の補正後被保険者数10,136人÷第1号被保険者数10,409人＝0.974も軽減前でしか再現できない（軽減後だと0.93台）。見える化システムの「①標準段階区分・割合」の画面でも0.4550／0.6850／0.6900が固定表示されることを同日の画面で確認した。**あわせて調整交付金の見込交付割合を、第9期からの逆算6.148％から算式（（第1号負担割合＋5％）－第1号負担割合×後期高齢者加入割合補正係数×所得段階別加入割合補正係数）による5.533％に改めた。**2つの訂正は互いに打ち消し合い、保険料基準額は月額115円下がった※ 逆算される調整交付金見込額219,272千円は基数の取り方によらない。見える化システムは標準給付費見込額のみを基数とするため6.148％、総合事業費を含めると5.963％となる（本件は前者にそろえた）</t>
         </is>
       </c>
       <c r="O41" s="16" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="N44" s="16" t="inlineStr">
         <is>
-          <t>**第5版（5章＋資料編・74表）。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定158箇所のうち61箇所が解消し97箇所となった。**第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量・給付費・標準給付費・地域支援事業費の事業別内訳・保険料基準額を入れた。**第5版（9月25日）で令和8年度の置き方を自然体推計に改め、保険料基準額は月額6,449円から6,095円（切上げ6,100円）となった。****9月25日の再検証で、延ばし方を見える化システムの仕様にそろえた**（施設は利用者数一定、居住系・在宅は認定者数で延ばす。月額▲13円）。従前の方式による算定は比較のケースとして残している。**第5章2の進行管理に、保険者機能強化推進交付金等の評価結果を点検項目として加えた**（評価結果を外部の議論の場で検証すること自体が評価指標の要件であるため）</t>
+          <t>**第5版（5章＋資料編・74表）。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定158箇所のうち61箇所が解消し97箇所となった。**第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量・給付費・標準給付費・地域支援事業費の事業別内訳・保険料基準額を入れた。**第5版（9月25日）で令和8年度の置き方を自然体推計に改め、保険料基準額は月額6,402円から6,048円（切上げ6,100円）となった。****9月25日の再検証で、延ばし方を見える化システムの仕様にそろえた**（施設は利用者数一定、居住系・在宅は認定者数で延ばす。月額▲13円）。従前の方式による算定は比較のケースとして残している。**第5章2の進行管理に、保険者機能強化推進交付金等の評価結果を点検項目として加えた**（評価結果を外部の議論の場で検証すること自体が評価指標の要件であるため）</t>
         </is>
       </c>
       <c r="O44" s="16" t="inlineStr">

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
@@ -6287,7 +6287,7 @@
       </c>
       <c r="N36" s="16" t="inlineStr">
         <is>
-          <t>**見込量保険料算定シート（04_算定・見込量・11シート）。**第9期の実数で検算済み（月額6,442円 対 実際6,600円。差2.4％は仮置き値による）</t>
+          <t>**見込量保険料算定シート（04_算定・見込量・11シート）。**第9期の実数で検算済み（月額6,865円 対 計画の算定値6,886円。差0.3％）</t>
         </is>
       </c>
       <c r="O36" s="16" t="inlineStr">

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260915.xlsx
@@ -4980,19 +4980,19 @@
         </is>
       </c>
       <c r="L20" s="19" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="M20" s="20" t="n">
         <v>2</v>
       </c>
       <c r="N20" s="16" t="inlineStr">
         <is>
-          <t>**9月25日に令和8年度の評価指標と全国集計（都道府県分）を受領し、協議会資料として整理した（08_協議会資料）。**福島県は令和7年度468点・42位から令和8年度530点・26位へ上がり、伸び幅＋62点は47都道府県で3位。ただし全国平均535.6点に届かず、東北6県では5番目。**全国の6割以上が得点していて福島県が0点の項目が21件あり、うち認知症施策に関する市町村支援（全国の93.6％が得点）、チームオレンジ設置状況（70.2％）、介護予防等と保健事業の一体的実施に向けた環境整備ウ・エ・オ（80〜83％）は小野町の施策に直に効く。****県の支援が薄い領域として、素案は町が自前で組み立てる前提で書く。****令和8年度に成果指向型配分枠（100点・800点とは別枠）が新設され、対象層の特定とアウトプット／アウトカム指標の分離、目標値の記載を求めている。第4章の成果指標42件のうち38件が目標値未設定であり、整理の仕方が交付金の配分に直に効く。**評価結果は計画本文には載せず毎年度の協議会資料として扱う（評価結果を外部の議論の場で検証すること自体が指標の要件であるため）</t>
+          <t>**9月28日に市町村分の集計表と評価指標を受領し、小野町の得点を項目ごとに整理した（21_給付適正化・交付金／取りまとめ9章・22表・図4点）。****令和8年度交付金は537点／800点で全国平均454.8点を82点上回り、全国258位／1,536・県内13位／59である。****介護給付適正化（推進Ⅱ）は84点で全国平均を上回る強みであり、体制・取組68点は配点満点。主要3事業はいずれも実施されており、医療情報との突合は全保険者の上位1割。0点はケアプラン点検の実施割合（配点16点）だけである。****8つの目標のうち全国平均を下回るのは支援Ⅲ（在宅医療・在宅介護連携）のみで、55点・県内39位。評価指標が求める4つの場面ごとの目指すべき姿が設定されていないことによる。****素案 第4章 基本目標2に「⑦ 在宅医療・介護連携の推進」を新設し、基本目標3① の適正化の記述を実際の得点に合わせて訂正した。****なお、それまで用いていた見える化システムの値（W126〜W137）は令和6年度交付金（233点）のものであり、2年前の状況だった。**9月25日に令和8年度の評価指標と全国集計（都道府県分）を受領し、協議会資料として整理している（08_協議会資料）。福島県は令和7年度468点・42位から令和8年度530点・26位へ上がり、伸び幅＋62点は47都道府県で3位。ただし全国平均535.6点に届かず、東北6県では5番目。**全国の6割以上が得点していて福島県が0点の項目が21件あり、うち認知症施策に関する市町村支援（全国の93.6％が得点）、チームオレンジ設置状況（70.2％）、介護予防等と保健事業の一体的実施に向けた環境整備ウ・エ・オ（80〜83％）は小野町の施策に直に効く。****県の支援が薄い領域として、素案は町が自前で組み立てる前提で書く。****令和8年度に成果指向型配分枠（100点・800点とは別枠）が新設され、対象層の特定とアウトプット／アウトカム指標の分離、目標値の記載を求めている。第4章の成果指標42件のうち38件が目標値未設定であり、整理の仕方が交付金の配分に直に効く。**評価結果は計画本文には載せず毎年度の協議会資料として扱う（評価結果を外部の議論の場で検証すること自体が指標の要件であるため）</t>
         </is>
       </c>
       <c r="O20" s="16" t="inlineStr">
         <is>
-          <t>**市町村分の評価指標と小野町の得点票（令和6〜8年度）。受領したのは都道府県分のみで、町自身の得点分析はできていない**</t>
+          <t>**令和6年度のケアプラン点検の実施件数（0点の理由の特定）と、令和8年度の該当状況調査票の控え（体制・取組で得点した項目の根拠資料）**</t>
         </is>
       </c>
       <c r="P20" s="21" t="n"/>
